--- a/RCC-Benchmark-Report.xlsx
+++ b/RCC-Benchmark-Report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gustavo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gustavo\OneDrive - The University of Chicago\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C825C1-4029-4303-8A58-7990662F544D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E4EF7F9-C87D-4BF2-8266-2D714653BFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1689,7 +1689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1792,6 +1792,17 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1802,6 +1813,36 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1809,6 +1850,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1847,24 +1915,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1880,63 +1930,12 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2175,13 +2174,13 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="52"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="57"/>
     </row>
     <row r="3" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="43"/>
@@ -2195,7 +2194,7 @@
       </c>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="98"/>
+      <c r="B4" s="52"/>
       <c r="C4" s="7" t="s">
         <v>3</v>
       </c>
@@ -2208,10 +2207,10 @@
       </c>
     </row>
     <row r="5" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="99" t="s">
+      <c r="B5" s="64" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="96">
+      <c r="C5" s="50">
         <v>1</v>
       </c>
       <c r="D5" s="10"/>
@@ -2219,8 +2218,8 @@
       <c r="F5" s="10"/>
     </row>
     <row r="6" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="100"/>
-      <c r="C6" s="97">
+      <c r="B6" s="65"/>
+      <c r="C6" s="51">
         <v>2</v>
       </c>
       <c r="D6" s="10"/>
@@ -2228,8 +2227,8 @@
       <c r="F6" s="10"/>
     </row>
     <row r="7" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="100"/>
-      <c r="C7" s="97">
+      <c r="B7" s="65"/>
+      <c r="C7" s="51">
         <v>4</v>
       </c>
       <c r="D7" s="10"/>
@@ -2237,8 +2236,8 @@
       <c r="F7" s="10"/>
     </row>
     <row r="8" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="100"/>
-      <c r="C8" s="96">
+      <c r="B8" s="65"/>
+      <c r="C8" s="50">
         <v>8</v>
       </c>
       <c r="D8" s="10"/>
@@ -2246,59 +2245,59 @@
       <c r="F8" s="10"/>
     </row>
     <row r="9" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="100"/>
-      <c r="C9" s="96">
+      <c r="B9" s="65"/>
+      <c r="C9" s="50">
         <v>16</v>
       </c>
       <c r="D9" s="10"/>
-      <c r="E9" s="92"/>
+      <c r="E9" s="1"/>
       <c r="F9" s="10"/>
     </row>
     <row r="10" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="102"/>
-      <c r="C10" s="101" t="s">
+      <c r="B10" s="54"/>
+      <c r="C10" s="53" t="s">
         <v>106</v>
       </c>
       <c r="D10" s="10"/>
-      <c r="E10" s="92"/>
+      <c r="E10" s="1"/>
       <c r="F10" s="10"/>
     </row>
     <row r="11" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="93" t="s">
+      <c r="B11" s="61" t="s">
         <v>112</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>107</v>
       </c>
       <c r="D11" s="10"/>
-      <c r="E11" s="92"/>
+      <c r="E11" s="1"/>
       <c r="F11" s="10"/>
     </row>
     <row r="12" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="94"/>
+      <c r="B12" s="62"/>
       <c r="C12" s="9" t="s">
         <v>108</v>
       </c>
       <c r="D12" s="10"/>
-      <c r="E12" s="92"/>
+      <c r="E12" s="1"/>
       <c r="F12" s="10"/>
     </row>
     <row r="13" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="94"/>
+      <c r="B13" s="62"/>
       <c r="C13" s="9" t="s">
         <v>109</v>
       </c>
       <c r="D13" s="10"/>
-      <c r="E13" s="92"/>
+      <c r="E13" s="1"/>
       <c r="F13" s="10"/>
     </row>
     <row r="14" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="95"/>
+      <c r="B14" s="63"/>
       <c r="C14" s="9" t="s">
         <v>110</v>
       </c>
       <c r="D14" s="10"/>
-      <c r="E14" s="92"/>
+      <c r="E14" s="1"/>
       <c r="F14" s="10"/>
     </row>
     <row r="15" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2315,7 +2314,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="53" t="s">
+      <c r="B16" s="58" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="14" t="s">
@@ -2326,7 +2325,7 @@
       <c r="F16" s="10"/>
     </row>
     <row r="17" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="54"/>
+      <c r="B17" s="59"/>
       <c r="C17" s="14" t="s">
         <v>8</v>
       </c>
@@ -2335,7 +2334,7 @@
       <c r="F17" s="10"/>
     </row>
     <row r="18" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="54"/>
+      <c r="B18" s="59"/>
       <c r="C18" s="14" t="s">
         <v>9</v>
       </c>
@@ -2344,7 +2343,7 @@
       <c r="F18" s="10"/>
     </row>
     <row r="19" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="54"/>
+      <c r="B19" s="59"/>
       <c r="C19" s="14" t="s">
         <v>10</v>
       </c>
@@ -2353,7 +2352,7 @@
       <c r="F19" s="10"/>
     </row>
     <row r="20" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="54"/>
+      <c r="B20" s="59"/>
       <c r="C20" s="14" t="s">
         <v>11</v>
       </c>
@@ -2362,7 +2361,7 @@
       <c r="F20" s="10"/>
     </row>
     <row r="21" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="54"/>
+      <c r="B21" s="59"/>
       <c r="C21" s="14" t="s">
         <v>12</v>
       </c>
@@ -2371,7 +2370,7 @@
       <c r="F21" s="10"/>
     </row>
     <row r="22" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="54"/>
+      <c r="B22" s="59"/>
       <c r="C22" s="14" t="s">
         <v>13</v>
       </c>
@@ -2380,7 +2379,7 @@
       <c r="F22" s="10"/>
     </row>
     <row r="23" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="54"/>
+      <c r="B23" s="59"/>
       <c r="C23" s="14" t="s">
         <v>14</v>
       </c>
@@ -2389,7 +2388,7 @@
       <c r="F23" s="10"/>
     </row>
     <row r="24" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="54"/>
+      <c r="B24" s="59"/>
       <c r="C24" s="14" t="s">
         <v>15</v>
       </c>
@@ -2398,7 +2397,7 @@
       <c r="F24" s="10"/>
     </row>
     <row r="25" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="54"/>
+      <c r="B25" s="59"/>
       <c r="C25" s="14" t="s">
         <v>16</v>
       </c>
@@ -2407,7 +2406,7 @@
       <c r="F25" s="10"/>
     </row>
     <row r="26" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="54"/>
+      <c r="B26" s="59"/>
       <c r="C26" s="14" t="s">
         <v>17</v>
       </c>
@@ -2416,7 +2415,7 @@
       <c r="F26" s="10"/>
     </row>
     <row r="27" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="54"/>
+      <c r="B27" s="59"/>
       <c r="C27" s="14" t="s">
         <v>18</v>
       </c>
@@ -2425,7 +2424,7 @@
       <c r="F27" s="10"/>
     </row>
     <row r="28" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="54"/>
+      <c r="B28" s="59"/>
       <c r="C28" s="14" t="s">
         <v>19</v>
       </c>
@@ -2434,7 +2433,7 @@
       <c r="F28" s="10"/>
     </row>
     <row r="29" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="55"/>
+      <c r="B29" s="60"/>
       <c r="C29" s="14" t="s">
         <v>20</v>
       </c>
@@ -3451,25 +3450,25 @@
       <c r="K1" s="15"/>
     </row>
     <row r="2" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="83" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="61"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="85"/>
       <c r="J2" s="15"/>
       <c r="K2" s="15"/>
     </row>
     <row r="3" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="64"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="88"/>
       <c r="G3" s="3" t="s">
         <v>1</v>
       </c>
@@ -3483,7 +3482,7 @@
       <c r="K3" s="15"/>
     </row>
     <row r="4" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="71" t="s">
         <v>81</v>
       </c>
       <c r="C4" s="20" t="s">
@@ -3509,14 +3508,14 @@
       <c r="K4" s="15"/>
     </row>
     <row r="5" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="57"/>
-      <c r="C5" s="77" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="71" t="s">
+      <c r="D5" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="71" t="s">
+      <c r="E5" s="67" t="s">
         <v>96</v>
       </c>
       <c r="F5" s="9">
@@ -3529,10 +3528,10 @@
       <c r="K5" s="15"/>
     </row>
     <row r="6" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="57"/>
-      <c r="C6" s="78"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
       <c r="F6" s="9">
         <v>2</v>
       </c>
@@ -3543,10 +3542,10 @@
       <c r="K6" s="15"/>
     </row>
     <row r="7" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="57"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
       <c r="F7" s="9">
         <v>4</v>
       </c>
@@ -3557,10 +3556,10 @@
       <c r="K7" s="15"/>
     </row>
     <row r="8" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="57"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
       <c r="F8" s="9">
         <v>8</v>
       </c>
@@ -3571,10 +3570,10 @@
       <c r="K8" s="15"/>
     </row>
     <row r="9" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="57"/>
-      <c r="C9" s="78"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
+      <c r="B9" s="72"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
       <c r="F9" s="9">
         <v>16</v>
       </c>
@@ -3585,10 +3584,10 @@
       <c r="K9" s="15"/>
     </row>
     <row r="10" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="57"/>
-      <c r="C10" s="78"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="73"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="74"/>
       <c r="F10" s="9">
         <v>32</v>
       </c>
@@ -3599,9 +3598,9 @@
       <c r="K10" s="15"/>
     </row>
     <row r="11" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="57"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="72"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="68"/>
       <c r="E11" s="26" t="s">
         <v>97</v>
       </c>
@@ -3617,10 +3616,10 @@
       <c r="K11" s="15"/>
     </row>
     <row r="12" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="57"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="65" t="s">
+      <c r="B12" s="72"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="89" t="s">
         <v>93</v>
       </c>
       <c r="F12" s="20">
@@ -3633,10 +3632,10 @@
       <c r="K12" s="15"/>
     </row>
     <row r="13" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="57"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="66"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="90"/>
       <c r="F13" s="20">
         <v>2</v>
       </c>
@@ -3647,10 +3646,10 @@
       <c r="K13" s="15"/>
     </row>
     <row r="14" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="57"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="67"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="91"/>
       <c r="F14" s="20">
         <v>4</v>
       </c>
@@ -3661,10 +3660,10 @@
       <c r="K14" s="15"/>
     </row>
     <row r="15" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="57"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="71" t="s">
+      <c r="B15" s="72"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="67" t="s">
         <v>92</v>
       </c>
       <c r="F15" s="20">
@@ -3676,10 +3675,10 @@
       <c r="K15" s="15"/>
     </row>
     <row r="16" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="57"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="72"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
       <c r="F16" s="20">
         <v>2</v>
       </c>
@@ -3689,10 +3688,10 @@
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="57"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
+      <c r="B17" s="72"/>
+      <c r="C17" s="96"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
       <c r="F17" s="20">
         <v>4</v>
       </c>
@@ -3702,9 +3701,9 @@
       <c r="K17" s="15"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="57"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="89" t="s">
+      <c r="B18" s="72"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="66" t="s">
         <v>90</v>
       </c>
       <c r="E18" s="45"/>
@@ -3718,10 +3717,10 @@
       <c r="K18" s="15"/>
     </row>
     <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="57"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="75" t="s">
+      <c r="B19" s="72"/>
+      <c r="C19" s="96"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="69" t="s">
         <v>96</v>
       </c>
       <c r="F19" s="9">
@@ -3734,10 +3733,10 @@
       <c r="K19" s="15"/>
     </row>
     <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="57"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="75"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="69"/>
       <c r="F20" s="9">
         <v>2</v>
       </c>
@@ -3748,10 +3747,10 @@
       <c r="K20" s="16"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="57"/>
-      <c r="C21" s="78"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="75"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="69"/>
       <c r="F21" s="9">
         <v>4</v>
       </c>
@@ -3760,10 +3759,10 @@
       <c r="I21" s="10"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="57"/>
-      <c r="C22" s="78"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="75"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="69"/>
       <c r="F22" s="9">
         <v>8</v>
       </c>
@@ -3772,10 +3771,10 @@
       <c r="I22" s="10"/>
     </row>
     <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="57"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="76"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="97"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="70"/>
       <c r="F23" s="9">
         <v>16</v>
       </c>
@@ -3784,8 +3783,8 @@
       <c r="I23" s="10"/>
     </row>
     <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="57"/>
-      <c r="C24" s="53" t="s">
+      <c r="B24" s="72"/>
+      <c r="C24" s="58" t="s">
         <v>98</v>
       </c>
       <c r="D24" s="42" t="s">
@@ -3804,12 +3803,12 @@
       <c r="K24" s="15"/>
     </row>
     <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="57"/>
-      <c r="C25" s="80"/>
-      <c r="D25" s="71" t="s">
+      <c r="B25" s="72"/>
+      <c r="C25" s="98"/>
+      <c r="D25" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="71" t="s">
+      <c r="E25" s="67" t="s">
         <v>96</v>
       </c>
       <c r="F25" s="9">
@@ -3822,10 +3821,10 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="57"/>
-      <c r="C26" s="80"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
+      <c r="B26" s="72"/>
+      <c r="C26" s="98"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
       <c r="F26" s="9">
         <v>2</v>
       </c>
@@ -3836,10 +3835,10 @@
       <c r="K26" s="15"/>
     </row>
     <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="57"/>
-      <c r="C27" s="80"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="72"/>
+      <c r="B27" s="72"/>
+      <c r="C27" s="98"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
       <c r="F27" s="9">
         <v>4</v>
       </c>
@@ -3850,10 +3849,10 @@
       <c r="K27" s="15"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="57"/>
-      <c r="C28" s="80"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="98"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
       <c r="F28" s="9">
         <v>8</v>
       </c>
@@ -3864,10 +3863,10 @@
       <c r="K28" s="15"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="57"/>
-      <c r="C29" s="80"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="72"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
       <c r="F29" s="9">
         <v>16</v>
       </c>
@@ -3878,10 +3877,10 @@
       <c r="K29" s="15"/>
     </row>
     <row r="30" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="57"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="73"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="98"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="74"/>
       <c r="F30" s="9">
         <v>32</v>
       </c>
@@ -3892,9 +3891,9 @@
       <c r="K30" s="15"/>
     </row>
     <row r="31" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="57"/>
-      <c r="C31" s="80"/>
-      <c r="D31" s="72"/>
+      <c r="B31" s="72"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="68"/>
       <c r="E31" s="26" t="s">
         <v>97</v>
       </c>
@@ -3910,10 +3909,10 @@
       <c r="K31" s="15"/>
     </row>
     <row r="32" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="57"/>
-      <c r="C32" s="80"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="65" t="s">
+      <c r="B32" s="72"/>
+      <c r="C32" s="98"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="89" t="s">
         <v>93</v>
       </c>
       <c r="F32" s="20">
@@ -3926,10 +3925,10 @@
       <c r="K32" s="15"/>
     </row>
     <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="57"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="72"/>
-      <c r="E33" s="66"/>
+      <c r="B33" s="72"/>
+      <c r="C33" s="98"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="90"/>
       <c r="F33" s="20">
         <v>2</v>
       </c>
@@ -3940,10 +3939,10 @@
       <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="57"/>
-      <c r="C34" s="80"/>
-      <c r="D34" s="72"/>
-      <c r="E34" s="67"/>
+      <c r="B34" s="72"/>
+      <c r="C34" s="98"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="91"/>
       <c r="F34" s="20">
         <v>4</v>
       </c>
@@ -3954,10 +3953,10 @@
       <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="57"/>
-      <c r="C35" s="80"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="71" t="s">
+      <c r="B35" s="72"/>
+      <c r="C35" s="98"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="67" t="s">
         <v>92</v>
       </c>
       <c r="F35" s="20">
@@ -3970,10 +3969,10 @@
       <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="57"/>
-      <c r="C36" s="80"/>
-      <c r="D36" s="72"/>
-      <c r="E36" s="72"/>
+      <c r="B36" s="72"/>
+      <c r="C36" s="98"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
       <c r="F36" s="20">
         <v>2</v>
       </c>
@@ -3984,10 +3983,10 @@
       <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="57"/>
-      <c r="C37" s="80"/>
-      <c r="D37" s="73"/>
-      <c r="E37" s="73"/>
+      <c r="B37" s="72"/>
+      <c r="C37" s="98"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="74"/>
       <c r="F37" s="20">
         <v>4</v>
       </c>
@@ -3998,9 +3997,9 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="57"/>
-      <c r="C38" s="80"/>
-      <c r="D38" s="89" t="s">
+      <c r="B38" s="72"/>
+      <c r="C38" s="98"/>
+      <c r="D38" s="66" t="s">
         <v>90</v>
       </c>
       <c r="F38" s="21" t="s">
@@ -4013,10 +4012,10 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="57"/>
-      <c r="C39" s="80"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="75" t="s">
+      <c r="B39" s="72"/>
+      <c r="C39" s="98"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="69" t="s">
         <v>96</v>
       </c>
       <c r="F39" s="9">
@@ -4029,10 +4028,10 @@
       <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="57"/>
-      <c r="C40" s="80"/>
-      <c r="D40" s="72"/>
-      <c r="E40" s="75"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="98"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="69"/>
       <c r="F40" s="9">
         <v>2</v>
       </c>
@@ -4043,10 +4042,10 @@
       <c r="K40" s="16"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="57"/>
-      <c r="C41" s="80"/>
-      <c r="D41" s="72"/>
-      <c r="E41" s="75"/>
+      <c r="B41" s="72"/>
+      <c r="C41" s="98"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="69"/>
       <c r="F41" s="9">
         <v>4</v>
       </c>
@@ -4055,10 +4054,10 @@
       <c r="I41" s="10"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="57"/>
-      <c r="C42" s="80"/>
-      <c r="D42" s="72"/>
-      <c r="E42" s="75"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="98"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="69"/>
       <c r="F42" s="9">
         <v>8</v>
       </c>
@@ -4067,10 +4066,10 @@
       <c r="I42" s="10"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="57"/>
-      <c r="C43" s="81"/>
-      <c r="D43" s="72"/>
-      <c r="E43" s="76"/>
+      <c r="B43" s="72"/>
+      <c r="C43" s="99"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="70"/>
       <c r="F43" s="9">
         <v>16</v>
       </c>
@@ -4080,8 +4079,8 @@
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
-      <c r="B44" s="57"/>
-      <c r="C44" s="53" t="s">
+      <c r="B44" s="72"/>
+      <c r="C44" s="58" t="s">
         <v>99</v>
       </c>
       <c r="D44" s="42" t="s">
@@ -4101,12 +4100,12 @@
     </row>
     <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="27"/>
-      <c r="B45" s="57"/>
-      <c r="C45" s="80"/>
-      <c r="D45" s="82" t="s">
+      <c r="B45" s="72"/>
+      <c r="C45" s="98"/>
+      <c r="D45" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="E45" s="82" t="s">
+      <c r="E45" s="76" t="s">
         <v>96</v>
       </c>
       <c r="F45" s="31">
@@ -4120,10 +4119,10 @@
     </row>
     <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
-      <c r="B46" s="57"/>
-      <c r="C46" s="80"/>
-      <c r="D46" s="83"/>
-      <c r="E46" s="83"/>
+      <c r="B46" s="72"/>
+      <c r="C46" s="98"/>
+      <c r="D46" s="77"/>
+      <c r="E46" s="77"/>
       <c r="F46" s="31">
         <v>2</v>
       </c>
@@ -4135,10 +4134,10 @@
     </row>
     <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="27"/>
-      <c r="B47" s="57"/>
-      <c r="C47" s="80"/>
-      <c r="D47" s="83"/>
-      <c r="E47" s="83"/>
+      <c r="B47" s="72"/>
+      <c r="C47" s="98"/>
+      <c r="D47" s="77"/>
+      <c r="E47" s="77"/>
       <c r="F47" s="31">
         <v>4</v>
       </c>
@@ -4150,10 +4149,10 @@
     </row>
     <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="27"/>
-      <c r="B48" s="57"/>
-      <c r="C48" s="80"/>
-      <c r="D48" s="83"/>
-      <c r="E48" s="83"/>
+      <c r="B48" s="72"/>
+      <c r="C48" s="98"/>
+      <c r="D48" s="77"/>
+      <c r="E48" s="77"/>
       <c r="F48" s="31">
         <v>8</v>
       </c>
@@ -4165,10 +4164,10 @@
     </row>
     <row r="49" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="27"/>
-      <c r="B49" s="57"/>
-      <c r="C49" s="80"/>
-      <c r="D49" s="83"/>
-      <c r="E49" s="83"/>
+      <c r="B49" s="72"/>
+      <c r="C49" s="98"/>
+      <c r="D49" s="77"/>
+      <c r="E49" s="77"/>
       <c r="F49" s="31">
         <v>16</v>
       </c>
@@ -4180,10 +4179,10 @@
     </row>
     <row r="50" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="27"/>
-      <c r="B50" s="57"/>
-      <c r="C50" s="80"/>
-      <c r="D50" s="83"/>
-      <c r="E50" s="84"/>
+      <c r="B50" s="72"/>
+      <c r="C50" s="98"/>
+      <c r="D50" s="77"/>
+      <c r="E50" s="78"/>
       <c r="F50" s="31">
         <v>32</v>
       </c>
@@ -4195,9 +4194,9 @@
     </row>
     <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="27"/>
-      <c r="B51" s="57"/>
-      <c r="C51" s="80"/>
-      <c r="D51" s="83"/>
+      <c r="B51" s="72"/>
+      <c r="C51" s="98"/>
+      <c r="D51" s="77"/>
       <c r="E51" s="34" t="s">
         <v>97</v>
       </c>
@@ -4214,10 +4213,10 @@
     </row>
     <row r="52" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="27"/>
-      <c r="B52" s="57"/>
-      <c r="C52" s="80"/>
-      <c r="D52" s="83"/>
-      <c r="E52" s="68" t="s">
+      <c r="B52" s="72"/>
+      <c r="C52" s="98"/>
+      <c r="D52" s="77"/>
+      <c r="E52" s="92" t="s">
         <v>93</v>
       </c>
       <c r="F52" s="31">
@@ -4231,10 +4230,10 @@
     </row>
     <row r="53" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="27"/>
-      <c r="B53" s="57"/>
-      <c r="C53" s="80"/>
-      <c r="D53" s="83"/>
-      <c r="E53" s="69"/>
+      <c r="B53" s="72"/>
+      <c r="C53" s="98"/>
+      <c r="D53" s="77"/>
+      <c r="E53" s="93"/>
       <c r="F53" s="31">
         <v>2</v>
       </c>
@@ -4246,10 +4245,10 @@
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="27"/>
-      <c r="B54" s="57"/>
-      <c r="C54" s="80"/>
-      <c r="D54" s="83"/>
-      <c r="E54" s="70"/>
+      <c r="B54" s="72"/>
+      <c r="C54" s="98"/>
+      <c r="D54" s="77"/>
+      <c r="E54" s="94"/>
       <c r="F54" s="31">
         <v>4</v>
       </c>
@@ -4261,10 +4260,10 @@
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="27"/>
-      <c r="B55" s="57"/>
-      <c r="C55" s="80"/>
-      <c r="D55" s="83"/>
-      <c r="E55" s="82" t="s">
+      <c r="B55" s="72"/>
+      <c r="C55" s="98"/>
+      <c r="D55" s="77"/>
+      <c r="E55" s="76" t="s">
         <v>92</v>
       </c>
       <c r="F55" s="31">
@@ -4278,10 +4277,10 @@
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="27"/>
-      <c r="B56" s="57"/>
-      <c r="C56" s="80"/>
-      <c r="D56" s="83"/>
-      <c r="E56" s="83"/>
+      <c r="B56" s="72"/>
+      <c r="C56" s="98"/>
+      <c r="D56" s="77"/>
+      <c r="E56" s="77"/>
       <c r="F56" s="31">
         <v>2</v>
       </c>
@@ -4293,10 +4292,10 @@
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="27"/>
-      <c r="B57" s="57"/>
-      <c r="C57" s="80"/>
-      <c r="D57" s="84"/>
-      <c r="E57" s="84"/>
+      <c r="B57" s="72"/>
+      <c r="C57" s="98"/>
+      <c r="D57" s="78"/>
+      <c r="E57" s="78"/>
       <c r="F57" s="31">
         <v>4</v>
       </c>
@@ -4308,9 +4307,9 @@
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="27"/>
-      <c r="B58" s="57"/>
-      <c r="C58" s="80"/>
-      <c r="D58" s="85" t="s">
+      <c r="B58" s="72"/>
+      <c r="C58" s="98"/>
+      <c r="D58" s="79" t="s">
         <v>90</v>
       </c>
       <c r="E58" s="36" t="s">
@@ -4327,10 +4326,10 @@
     </row>
     <row r="59" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="27"/>
-      <c r="B59" s="57"/>
-      <c r="C59" s="80"/>
-      <c r="D59" s="82"/>
-      <c r="E59" s="86" t="s">
+      <c r="B59" s="72"/>
+      <c r="C59" s="98"/>
+      <c r="D59" s="76"/>
+      <c r="E59" s="80" t="s">
         <v>96</v>
       </c>
       <c r="F59" s="31">
@@ -4344,10 +4343,10 @@
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="27"/>
-      <c r="B60" s="57"/>
-      <c r="C60" s="80"/>
-      <c r="D60" s="83"/>
-      <c r="E60" s="87"/>
+      <c r="B60" s="72"/>
+      <c r="C60" s="98"/>
+      <c r="D60" s="77"/>
+      <c r="E60" s="81"/>
       <c r="F60" s="31">
         <v>2</v>
       </c>
@@ -4359,10 +4358,10 @@
     </row>
     <row r="61" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="27"/>
-      <c r="B61" s="57"/>
-      <c r="C61" s="80"/>
-      <c r="D61" s="83"/>
-      <c r="E61" s="87"/>
+      <c r="B61" s="72"/>
+      <c r="C61" s="98"/>
+      <c r="D61" s="77"/>
+      <c r="E61" s="81"/>
       <c r="F61" s="31">
         <v>4</v>
       </c>
@@ -4374,10 +4373,10 @@
     </row>
     <row r="62" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="27"/>
-      <c r="B62" s="57"/>
-      <c r="C62" s="80"/>
-      <c r="D62" s="83"/>
-      <c r="E62" s="87"/>
+      <c r="B62" s="72"/>
+      <c r="C62" s="98"/>
+      <c r="D62" s="77"/>
+      <c r="E62" s="81"/>
       <c r="F62" s="31">
         <v>8</v>
       </c>
@@ -4389,10 +4388,10 @@
     </row>
     <row r="63" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="27"/>
-      <c r="B63" s="58"/>
-      <c r="C63" s="81"/>
-      <c r="D63" s="84"/>
-      <c r="E63" s="88"/>
+      <c r="B63" s="73"/>
+      <c r="C63" s="99"/>
+      <c r="D63" s="78"/>
+      <c r="E63" s="82"/>
       <c r="F63" s="31">
         <v>16</v>
       </c>
@@ -4403,7 +4402,7 @@
       <c r="K63" s="27"/>
     </row>
     <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="56" t="s">
+      <c r="B64" s="71" t="s">
         <v>82</v>
       </c>
       <c r="C64" s="20" t="s">
@@ -4429,14 +4428,14 @@
       <c r="K64" s="15"/>
     </row>
     <row r="65" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="57"/>
-      <c r="C65" s="77" t="s">
+      <c r="B65" s="72"/>
+      <c r="C65" s="95" t="s">
         <v>83</v>
       </c>
-      <c r="D65" s="71" t="s">
+      <c r="D65" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="E65" s="71" t="s">
+      <c r="E65" s="67" t="s">
         <v>100</v>
       </c>
       <c r="F65" s="9">
@@ -4449,10 +4448,10 @@
       <c r="K65" s="15"/>
     </row>
     <row r="66" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="57"/>
-      <c r="C66" s="78"/>
-      <c r="D66" s="72"/>
-      <c r="E66" s="72"/>
+      <c r="B66" s="72"/>
+      <c r="C66" s="96"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="68"/>
       <c r="F66" s="9">
         <v>2</v>
       </c>
@@ -4463,10 +4462,10 @@
       <c r="K66" s="15"/>
     </row>
     <row r="67" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="57"/>
-      <c r="C67" s="78"/>
-      <c r="D67" s="72"/>
-      <c r="E67" s="72"/>
+      <c r="B67" s="72"/>
+      <c r="C67" s="96"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="68"/>
       <c r="F67" s="9">
         <v>4</v>
       </c>
@@ -4477,10 +4476,10 @@
       <c r="K67" s="15"/>
     </row>
     <row r="68" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="57"/>
-      <c r="C68" s="78"/>
-      <c r="D68" s="72"/>
-      <c r="E68" s="72"/>
+      <c r="B68" s="72"/>
+      <c r="C68" s="96"/>
+      <c r="D68" s="68"/>
+      <c r="E68" s="68"/>
       <c r="F68" s="9">
         <v>8</v>
       </c>
@@ -4491,10 +4490,10 @@
       <c r="K68" s="15"/>
     </row>
     <row r="69" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="57"/>
-      <c r="C69" s="78"/>
-      <c r="D69" s="72"/>
-      <c r="E69" s="72"/>
+      <c r="B69" s="72"/>
+      <c r="C69" s="96"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="68"/>
       <c r="F69" s="9">
         <v>16</v>
       </c>
@@ -4505,10 +4504,10 @@
       <c r="K69" s="15"/>
     </row>
     <row r="70" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="57"/>
-      <c r="C70" s="78"/>
-      <c r="D70" s="72"/>
-      <c r="E70" s="73"/>
+      <c r="B70" s="72"/>
+      <c r="C70" s="96"/>
+      <c r="D70" s="68"/>
+      <c r="E70" s="74"/>
       <c r="F70" s="9">
         <v>32</v>
       </c>
@@ -4519,8 +4518,8 @@
       <c r="K70" s="15"/>
     </row>
     <row r="71" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="57"/>
-      <c r="C71" s="78"/>
+      <c r="B71" s="72"/>
+      <c r="C71" s="96"/>
       <c r="D71" s="42"/>
       <c r="E71" s="36" t="s">
         <v>95</v>
@@ -4535,12 +4534,12 @@
       <c r="K71" s="15"/>
     </row>
     <row r="72" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="57"/>
-      <c r="C72" s="78"/>
-      <c r="D72" s="71" t="s">
+      <c r="B72" s="72"/>
+      <c r="C72" s="96"/>
+      <c r="D72" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="E72" s="74" t="s">
+      <c r="E72" s="75" t="s">
         <v>100</v>
       </c>
       <c r="F72" s="9">
@@ -4553,10 +4552,10 @@
       <c r="K72" s="15"/>
     </row>
     <row r="73" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="57"/>
-      <c r="C73" s="78"/>
-      <c r="D73" s="72"/>
-      <c r="E73" s="75"/>
+      <c r="B73" s="72"/>
+      <c r="C73" s="96"/>
+      <c r="D73" s="68"/>
+      <c r="E73" s="69"/>
       <c r="F73" s="9">
         <v>2</v>
       </c>
@@ -4567,10 +4566,10 @@
       <c r="K73" s="16"/>
     </row>
     <row r="74" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="57"/>
-      <c r="C74" s="78"/>
-      <c r="D74" s="72"/>
-      <c r="E74" s="75"/>
+      <c r="B74" s="72"/>
+      <c r="C74" s="96"/>
+      <c r="D74" s="68"/>
+      <c r="E74" s="69"/>
       <c r="F74" s="9">
         <v>4</v>
       </c>
@@ -4579,10 +4578,10 @@
       <c r="I74" s="10"/>
     </row>
     <row r="75" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="57"/>
-      <c r="C75" s="78"/>
-      <c r="D75" s="72"/>
-      <c r="E75" s="75"/>
+      <c r="B75" s="72"/>
+      <c r="C75" s="96"/>
+      <c r="D75" s="68"/>
+      <c r="E75" s="69"/>
       <c r="F75" s="9">
         <v>8</v>
       </c>
@@ -4591,10 +4590,10 @@
       <c r="I75" s="10"/>
     </row>
     <row r="76" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="57"/>
-      <c r="C76" s="79"/>
-      <c r="D76" s="73"/>
-      <c r="E76" s="76"/>
+      <c r="B76" s="72"/>
+      <c r="C76" s="97"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="70"/>
       <c r="F76" s="9">
         <v>16</v>
       </c>
@@ -4603,14 +4602,14 @@
       <c r="I76" s="10"/>
     </row>
     <row r="77" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="57"/>
-      <c r="C77" s="77" t="s">
+      <c r="B77" s="72"/>
+      <c r="C77" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="D77" s="71" t="s">
+      <c r="D77" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="E77" s="71" t="s">
+      <c r="E77" s="67" t="s">
         <v>100</v>
       </c>
       <c r="F77" s="9">
@@ -4623,10 +4622,10 @@
       <c r="K77" s="15"/>
     </row>
     <row r="78" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="57"/>
-      <c r="C78" s="78"/>
-      <c r="D78" s="72"/>
-      <c r="E78" s="72"/>
+      <c r="B78" s="72"/>
+      <c r="C78" s="96"/>
+      <c r="D78" s="68"/>
+      <c r="E78" s="68"/>
       <c r="F78" s="9">
         <v>2</v>
       </c>
@@ -4637,10 +4636,10 @@
       <c r="K78" s="15"/>
     </row>
     <row r="79" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="57"/>
-      <c r="C79" s="78"/>
-      <c r="D79" s="72"/>
-      <c r="E79" s="72"/>
+      <c r="B79" s="72"/>
+      <c r="C79" s="96"/>
+      <c r="D79" s="68"/>
+      <c r="E79" s="68"/>
       <c r="F79" s="9">
         <v>4</v>
       </c>
@@ -4651,10 +4650,10 @@
       <c r="K79" s="15"/>
     </row>
     <row r="80" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="57"/>
-      <c r="C80" s="78"/>
-      <c r="D80" s="72"/>
-      <c r="E80" s="72"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="96"/>
+      <c r="D80" s="68"/>
+      <c r="E80" s="68"/>
       <c r="F80" s="9">
         <v>8</v>
       </c>
@@ -4665,10 +4664,10 @@
       <c r="K80" s="15"/>
     </row>
     <row r="81" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="57"/>
-      <c r="C81" s="78"/>
-      <c r="D81" s="72"/>
-      <c r="E81" s="72"/>
+      <c r="B81" s="72"/>
+      <c r="C81" s="96"/>
+      <c r="D81" s="68"/>
+      <c r="E81" s="68"/>
       <c r="F81" s="9">
         <v>16</v>
       </c>
@@ -4679,10 +4678,10 @@
       <c r="K81" s="15"/>
     </row>
     <row r="82" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="57"/>
-      <c r="C82" s="78"/>
-      <c r="D82" s="72"/>
-      <c r="E82" s="73"/>
+      <c r="B82" s="72"/>
+      <c r="C82" s="96"/>
+      <c r="D82" s="68"/>
+      <c r="E82" s="74"/>
       <c r="F82" s="9">
         <v>32</v>
       </c>
@@ -4693,8 +4692,8 @@
       <c r="K82" s="15"/>
     </row>
     <row r="83" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="57"/>
-      <c r="C83" s="78"/>
+      <c r="B83" s="72"/>
+      <c r="C83" s="96"/>
       <c r="D83" s="42"/>
       <c r="E83" s="36" t="s">
         <v>95</v>
@@ -4709,12 +4708,12 @@
       <c r="K83" s="15"/>
     </row>
     <row r="84" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="57"/>
-      <c r="C84" s="78"/>
-      <c r="D84" s="71" t="s">
+      <c r="B84" s="72"/>
+      <c r="C84" s="96"/>
+      <c r="D84" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="E84" s="74" t="s">
+      <c r="E84" s="75" t="s">
         <v>100</v>
       </c>
       <c r="F84" s="9">
@@ -4727,10 +4726,10 @@
       <c r="K84" s="15"/>
     </row>
     <row r="85" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="57"/>
-      <c r="C85" s="78"/>
-      <c r="D85" s="72"/>
-      <c r="E85" s="75"/>
+      <c r="B85" s="72"/>
+      <c r="C85" s="96"/>
+      <c r="D85" s="68"/>
+      <c r="E85" s="69"/>
       <c r="F85" s="9">
         <v>2</v>
       </c>
@@ -4741,10 +4740,10 @@
       <c r="K85" s="16"/>
     </row>
     <row r="86" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="57"/>
-      <c r="C86" s="78"/>
-      <c r="D86" s="72"/>
-      <c r="E86" s="75"/>
+      <c r="B86" s="72"/>
+      <c r="C86" s="96"/>
+      <c r="D86" s="68"/>
+      <c r="E86" s="69"/>
       <c r="F86" s="9">
         <v>4</v>
       </c>
@@ -4753,10 +4752,10 @@
       <c r="I86" s="10"/>
     </row>
     <row r="87" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="57"/>
-      <c r="C87" s="78"/>
-      <c r="D87" s="72"/>
-      <c r="E87" s="75"/>
+      <c r="B87" s="72"/>
+      <c r="C87" s="96"/>
+      <c r="D87" s="68"/>
+      <c r="E87" s="69"/>
       <c r="F87" s="9">
         <v>8</v>
       </c>
@@ -4765,10 +4764,10 @@
       <c r="I87" s="10"/>
     </row>
     <row r="88" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="58"/>
-      <c r="C88" s="79"/>
-      <c r="D88" s="73"/>
-      <c r="E88" s="76"/>
+      <c r="B88" s="73"/>
+      <c r="C88" s="97"/>
+      <c r="D88" s="74"/>
+      <c r="E88" s="70"/>
       <c r="F88" s="9">
         <v>16</v>
       </c>
@@ -5665,25 +5664,6 @@
     <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="D38:D43"/>
-    <mergeCell ref="E39:E43"/>
-    <mergeCell ref="B4:B63"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="E5:E10"/>
-    <mergeCell ref="E19:E23"/>
-    <mergeCell ref="D5:D17"/>
-    <mergeCell ref="D18:D23"/>
-    <mergeCell ref="D25:D37"/>
-    <mergeCell ref="E25:E30"/>
-    <mergeCell ref="E35:E37"/>
-    <mergeCell ref="D65:D70"/>
-    <mergeCell ref="E65:E70"/>
-    <mergeCell ref="E72:E76"/>
-    <mergeCell ref="D45:D57"/>
-    <mergeCell ref="E45:E50"/>
-    <mergeCell ref="E55:E57"/>
-    <mergeCell ref="D58:D63"/>
-    <mergeCell ref="E59:E63"/>
     <mergeCell ref="B64:B88"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:F3"/>
@@ -5700,6 +5680,25 @@
     <mergeCell ref="D72:D76"/>
     <mergeCell ref="D77:D82"/>
     <mergeCell ref="E77:E82"/>
+    <mergeCell ref="D65:D70"/>
+    <mergeCell ref="E65:E70"/>
+    <mergeCell ref="E72:E76"/>
+    <mergeCell ref="D45:D57"/>
+    <mergeCell ref="E45:E50"/>
+    <mergeCell ref="E55:E57"/>
+    <mergeCell ref="D58:D63"/>
+    <mergeCell ref="E59:E63"/>
+    <mergeCell ref="D38:D43"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="B4:B63"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="E5:E10"/>
+    <mergeCell ref="E19:E23"/>
+    <mergeCell ref="D5:D17"/>
+    <mergeCell ref="D18:D23"/>
+    <mergeCell ref="D25:D37"/>
+    <mergeCell ref="E25:E30"/>
+    <mergeCell ref="E35:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5724,34 +5723,34 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
     </row>
     <row r="3" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="91" t="s">
+      <c r="D3" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="51"/>
+      <c r="E3" s="56"/>
       <c r="F3" s="6"/>
-      <c r="G3" s="91" t="s">
+      <c r="G3" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="51"/>
+      <c r="H3" s="56"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="90" t="s">
+      <c r="B4" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="90" t="s">
+      <c r="C4" s="100" t="s">
         <v>22</v>
       </c>
       <c r="D4" s="47" t="s">
@@ -5769,8 +5768,8 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
       <c r="D5" s="7" t="s">
         <v>25</v>
       </c>
@@ -5786,7 +5785,7 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="53">
+      <c r="B6" s="58">
         <v>1</v>
       </c>
       <c r="C6" s="18" t="s">
@@ -5799,7 +5798,7 @@
       <c r="H6" s="19"/>
     </row>
     <row r="7" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="54"/>
+      <c r="B7" s="59"/>
       <c r="C7" s="18" t="s">
         <v>27</v>
       </c>
@@ -5810,7 +5809,7 @@
       <c r="H7" s="19"/>
     </row>
     <row r="8" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="54"/>
+      <c r="B8" s="59"/>
       <c r="C8" s="18" t="s">
         <v>28</v>
       </c>
@@ -5821,7 +5820,7 @@
       <c r="H8" s="19"/>
     </row>
     <row r="9" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="54"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="18" t="s">
         <v>29</v>
       </c>
@@ -5832,7 +5831,7 @@
       <c r="H9" s="19"/>
     </row>
     <row r="10" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="54"/>
+      <c r="B10" s="59"/>
       <c r="C10" s="18" t="s">
         <v>30</v>
       </c>
@@ -5843,7 +5842,7 @@
       <c r="H10" s="19"/>
     </row>
     <row r="11" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="54"/>
+      <c r="B11" s="59"/>
       <c r="C11" s="18" t="s">
         <v>31</v>
       </c>
@@ -5854,7 +5853,7 @@
       <c r="H11" s="19"/>
     </row>
     <row r="12" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="54"/>
+      <c r="B12" s="59"/>
       <c r="C12" s="18" t="s">
         <v>32</v>
       </c>
@@ -5865,7 +5864,7 @@
       <c r="H12" s="19"/>
     </row>
     <row r="13" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="54"/>
+      <c r="B13" s="59"/>
       <c r="C13" s="18" t="s">
         <v>33</v>
       </c>
@@ -5876,7 +5875,7 @@
       <c r="H13" s="19"/>
     </row>
     <row r="14" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="54"/>
+      <c r="B14" s="59"/>
       <c r="C14" s="18" t="s">
         <v>34</v>
       </c>
@@ -5887,7 +5886,7 @@
       <c r="H14" s="19"/>
     </row>
     <row r="15" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="54"/>
+      <c r="B15" s="59"/>
       <c r="C15" s="18" t="s">
         <v>35</v>
       </c>
@@ -5898,7 +5897,7 @@
       <c r="H15" s="19"/>
     </row>
     <row r="16" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="55"/>
+      <c r="B16" s="60"/>
       <c r="C16" s="18" t="s">
         <v>36</v>
       </c>
@@ -5909,7 +5908,7 @@
       <c r="H16" s="19"/>
     </row>
     <row r="17" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="53">
+      <c r="B17" s="58">
         <v>2</v>
       </c>
       <c r="C17" s="18" t="s">
@@ -5922,7 +5921,7 @@
       <c r="H17" s="19"/>
     </row>
     <row r="18" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="54"/>
+      <c r="B18" s="59"/>
       <c r="C18" s="18" t="s">
         <v>38</v>
       </c>
@@ -5933,7 +5932,7 @@
       <c r="H18" s="19"/>
     </row>
     <row r="19" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="54"/>
+      <c r="B19" s="59"/>
       <c r="C19" s="18" t="s">
         <v>39</v>
       </c>
@@ -5944,7 +5943,7 @@
       <c r="H19" s="19"/>
     </row>
     <row r="20" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="54"/>
+      <c r="B20" s="59"/>
       <c r="C20" s="18" t="s">
         <v>40</v>
       </c>
@@ -5955,7 +5954,7 @@
       <c r="H20" s="19"/>
     </row>
     <row r="21" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="54"/>
+      <c r="B21" s="59"/>
       <c r="C21" s="18" t="s">
         <v>41</v>
       </c>
@@ -5966,7 +5965,7 @@
       <c r="H21" s="19"/>
     </row>
     <row r="22" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="54"/>
+      <c r="B22" s="59"/>
       <c r="C22" s="18" t="s">
         <v>42</v>
       </c>
@@ -5977,7 +5976,7 @@
       <c r="H22" s="19"/>
     </row>
     <row r="23" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="54"/>
+      <c r="B23" s="59"/>
       <c r="C23" s="18" t="s">
         <v>43</v>
       </c>
@@ -5988,7 +5987,7 @@
       <c r="H23" s="19"/>
     </row>
     <row r="24" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="54"/>
+      <c r="B24" s="59"/>
       <c r="C24" s="18" t="s">
         <v>44</v>
       </c>
@@ -5999,7 +5998,7 @@
       <c r="H24" s="19"/>
     </row>
     <row r="25" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="54"/>
+      <c r="B25" s="59"/>
       <c r="C25" s="18" t="s">
         <v>45</v>
       </c>
@@ -6010,7 +6009,7 @@
       <c r="H25" s="19"/>
     </row>
     <row r="26" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="54"/>
+      <c r="B26" s="59"/>
       <c r="C26" s="18" t="s">
         <v>46</v>
       </c>
@@ -6021,7 +6020,7 @@
       <c r="H26" s="19"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="55"/>
+      <c r="B27" s="60"/>
       <c r="C27" s="18" t="s">
         <v>47</v>
       </c>
@@ -6032,7 +6031,7 @@
       <c r="H27" s="19"/>
     </row>
     <row r="28" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="53">
+      <c r="B28" s="58">
         <v>4</v>
       </c>
       <c r="C28" s="18" t="s">
@@ -6045,7 +6044,7 @@
       <c r="H28" s="19"/>
     </row>
     <row r="29" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="54"/>
+      <c r="B29" s="59"/>
       <c r="C29" s="18" t="s">
         <v>49</v>
       </c>
@@ -6056,7 +6055,7 @@
       <c r="H29" s="19"/>
     </row>
     <row r="30" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="54"/>
+      <c r="B30" s="59"/>
       <c r="C30" s="18" t="s">
         <v>50</v>
       </c>
@@ -6067,7 +6066,7 @@
       <c r="H30" s="19"/>
     </row>
     <row r="31" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="54"/>
+      <c r="B31" s="59"/>
       <c r="C31" s="18" t="s">
         <v>51</v>
       </c>
@@ -6078,7 +6077,7 @@
       <c r="H31" s="19"/>
     </row>
     <row r="32" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="54"/>
+      <c r="B32" s="59"/>
       <c r="C32" s="18" t="s">
         <v>52</v>
       </c>
@@ -6089,7 +6088,7 @@
       <c r="H32" s="19"/>
     </row>
     <row r="33" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="54"/>
+      <c r="B33" s="59"/>
       <c r="C33" s="18" t="s">
         <v>53</v>
       </c>
@@ -6100,7 +6099,7 @@
       <c r="H33" s="19"/>
     </row>
     <row r="34" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="54"/>
+      <c r="B34" s="59"/>
       <c r="C34" s="18" t="s">
         <v>54</v>
       </c>
@@ -6111,7 +6110,7 @@
       <c r="H34" s="19"/>
     </row>
     <row r="35" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="54"/>
+      <c r="B35" s="59"/>
       <c r="C35" s="18" t="s">
         <v>55</v>
       </c>
@@ -6122,7 +6121,7 @@
       <c r="H35" s="19"/>
     </row>
     <row r="36" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="54"/>
+      <c r="B36" s="59"/>
       <c r="C36" s="18" t="s">
         <v>56</v>
       </c>
@@ -6133,7 +6132,7 @@
       <c r="H36" s="19"/>
     </row>
     <row r="37" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="54"/>
+      <c r="B37" s="59"/>
       <c r="C37" s="18" t="s">
         <v>57</v>
       </c>
@@ -6144,7 +6143,7 @@
       <c r="H37" s="19"/>
     </row>
     <row r="38" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="55"/>
+      <c r="B38" s="60"/>
       <c r="C38" s="18" t="s">
         <v>58</v>
       </c>
@@ -6155,7 +6154,7 @@
       <c r="H38" s="19"/>
     </row>
     <row r="39" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="53">
+      <c r="B39" s="58">
         <v>8</v>
       </c>
       <c r="C39" s="18" t="s">
@@ -6168,7 +6167,7 @@
       <c r="H39" s="19"/>
     </row>
     <row r="40" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="54"/>
+      <c r="B40" s="59"/>
       <c r="C40" s="18" t="s">
         <v>60</v>
       </c>
@@ -6179,7 +6178,7 @@
       <c r="H40" s="19"/>
     </row>
     <row r="41" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="54"/>
+      <c r="B41" s="59"/>
       <c r="C41" s="18" t="s">
         <v>61</v>
       </c>
@@ -6190,7 +6189,7 @@
       <c r="H41" s="19"/>
     </row>
     <row r="42" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="54"/>
+      <c r="B42" s="59"/>
       <c r="C42" s="18" t="s">
         <v>62</v>
       </c>
@@ -6201,7 +6200,7 @@
       <c r="H42" s="19"/>
     </row>
     <row r="43" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="54"/>
+      <c r="B43" s="59"/>
       <c r="C43" s="18" t="s">
         <v>63</v>
       </c>
@@ -6212,7 +6211,7 @@
       <c r="H43" s="19"/>
     </row>
     <row r="44" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="54"/>
+      <c r="B44" s="59"/>
       <c r="C44" s="18" t="s">
         <v>64</v>
       </c>
@@ -6223,7 +6222,7 @@
       <c r="H44" s="19"/>
     </row>
     <row r="45" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="54"/>
+      <c r="B45" s="59"/>
       <c r="C45" s="18" t="s">
         <v>65</v>
       </c>
@@ -6234,7 +6233,7 @@
       <c r="H45" s="19"/>
     </row>
     <row r="46" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="54"/>
+      <c r="B46" s="59"/>
       <c r="C46" s="18" t="s">
         <v>66</v>
       </c>
@@ -6245,7 +6244,7 @@
       <c r="H46" s="19"/>
     </row>
     <row r="47" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="54"/>
+      <c r="B47" s="59"/>
       <c r="C47" s="18" t="s">
         <v>67</v>
       </c>
@@ -6256,7 +6255,7 @@
       <c r="H47" s="19"/>
     </row>
     <row r="48" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="54"/>
+      <c r="B48" s="59"/>
       <c r="C48" s="18" t="s">
         <v>68</v>
       </c>
@@ -6267,7 +6266,7 @@
       <c r="H48" s="19"/>
     </row>
     <row r="49" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="55"/>
+      <c r="B49" s="60"/>
       <c r="C49" s="18" t="s">
         <v>69</v>
       </c>
@@ -6278,7 +6277,7 @@
       <c r="H49" s="19"/>
     </row>
     <row r="50" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="53">
+      <c r="B50" s="58">
         <v>16</v>
       </c>
       <c r="C50" s="18" t="s">
@@ -6291,7 +6290,7 @@
       <c r="H50" s="19"/>
     </row>
     <row r="51" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="54"/>
+      <c r="B51" s="59"/>
       <c r="C51" s="18" t="s">
         <v>71</v>
       </c>
@@ -6302,7 +6301,7 @@
       <c r="H51" s="19"/>
     </row>
     <row r="52" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="54"/>
+      <c r="B52" s="59"/>
       <c r="C52" s="18" t="s">
         <v>72</v>
       </c>
@@ -6313,7 +6312,7 @@
       <c r="H52" s="19"/>
     </row>
     <row r="53" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="54"/>
+      <c r="B53" s="59"/>
       <c r="C53" s="18" t="s">
         <v>73</v>
       </c>
@@ -6324,7 +6323,7 @@
       <c r="H53" s="19"/>
     </row>
     <row r="54" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="54"/>
+      <c r="B54" s="59"/>
       <c r="C54" s="18" t="s">
         <v>74</v>
       </c>
@@ -6335,7 +6334,7 @@
       <c r="H54" s="19"/>
     </row>
     <row r="55" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="54"/>
+      <c r="B55" s="59"/>
       <c r="C55" s="18" t="s">
         <v>75</v>
       </c>
@@ -6346,7 +6345,7 @@
       <c r="H55" s="19"/>
     </row>
     <row r="56" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="54"/>
+      <c r="B56" s="59"/>
       <c r="C56" s="18" t="s">
         <v>76</v>
       </c>
@@ -6357,7 +6356,7 @@
       <c r="H56" s="19"/>
     </row>
     <row r="57" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="54"/>
+      <c r="B57" s="59"/>
       <c r="C57" s="18" t="s">
         <v>77</v>
       </c>
@@ -6368,7 +6367,7 @@
       <c r="H57" s="19"/>
     </row>
     <row r="58" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="54"/>
+      <c r="B58" s="59"/>
       <c r="C58" s="18" t="s">
         <v>78</v>
       </c>
@@ -6379,7 +6378,7 @@
       <c r="H58" s="19"/>
     </row>
     <row r="59" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="54"/>
+      <c r="B59" s="59"/>
       <c r="C59" s="18" t="s">
         <v>79</v>
       </c>
@@ -6390,7 +6389,7 @@
       <c r="H59" s="19"/>
     </row>
     <row r="60" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="55"/>
+      <c r="B60" s="60"/>
       <c r="C60" s="18" t="s">
         <v>80</v>
       </c>

--- a/RCC-Benchmark-Report.xlsx
+++ b/RCC-Benchmark-Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gustavo\OneDrive - The University of Chicago\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E4EF7F9-C87D-4BF2-8266-2D714653BFFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25DCF5C3-AB1B-402D-B196-7BD8C15A2DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="113">
   <si>
     <t>Standard Compute Benchmarks</t>
   </si>
@@ -1828,21 +1828,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1850,33 +1835,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1915,6 +1873,24 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1928,6 +1904,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2258,9 +2258,13 @@
       <c r="C10" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="10"/>
+      <c r="D10" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="7" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="61" t="s">
@@ -3450,25 +3454,25 @@
       <c r="K1" s="15"/>
     </row>
     <row r="2" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="85"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="71"/>
       <c r="J2" s="15"/>
       <c r="K2" s="15"/>
     </row>
     <row r="3" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="86"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="88"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="74"/>
       <c r="G3" s="3" t="s">
         <v>1</v>
       </c>
@@ -3482,7 +3486,7 @@
       <c r="K3" s="15"/>
     </row>
     <row r="4" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="66" t="s">
         <v>81</v>
       </c>
       <c r="C4" s="20" t="s">
@@ -3508,14 +3512,14 @@
       <c r="K4" s="15"/>
     </row>
     <row r="5" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="72"/>
-      <c r="C5" s="95" t="s">
+      <c r="B5" s="67"/>
+      <c r="C5" s="87" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="67" t="s">
+      <c r="D5" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="81" t="s">
         <v>96</v>
       </c>
       <c r="F5" s="9">
@@ -3528,10 +3532,10 @@
       <c r="K5" s="15"/>
     </row>
     <row r="6" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="72"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
       <c r="F6" s="9">
         <v>2</v>
       </c>
@@ -3542,10 +3546,10 @@
       <c r="K6" s="15"/>
     </row>
     <row r="7" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="72"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="88"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
       <c r="F7" s="9">
         <v>4</v>
       </c>
@@ -3556,10 +3560,10 @@
       <c r="K7" s="15"/>
     </row>
     <row r="8" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="72"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
       <c r="F8" s="9">
         <v>8</v>
       </c>
@@ -3570,10 +3574,10 @@
       <c r="K8" s="15"/>
     </row>
     <row r="9" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="72"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="88"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
       <c r="F9" s="9">
         <v>16</v>
       </c>
@@ -3584,10 +3588,10 @@
       <c r="K9" s="15"/>
     </row>
     <row r="10" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="72"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="74"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="83"/>
       <c r="F10" s="9">
         <v>32</v>
       </c>
@@ -3598,9 +3602,9 @@
       <c r="K10" s="15"/>
     </row>
     <row r="11" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="72"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="68"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="82"/>
       <c r="E11" s="26" t="s">
         <v>97</v>
       </c>
@@ -3616,10 +3620,10 @@
       <c r="K11" s="15"/>
     </row>
     <row r="12" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="72"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="68"/>
-      <c r="E12" s="89" t="s">
+      <c r="B12" s="67"/>
+      <c r="C12" s="88"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="75" t="s">
         <v>93</v>
       </c>
       <c r="F12" s="20">
@@ -3632,10 +3636,10 @@
       <c r="K12" s="15"/>
     </row>
     <row r="13" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="72"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="90"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="76"/>
       <c r="F13" s="20">
         <v>2</v>
       </c>
@@ -3646,10 +3650,10 @@
       <c r="K13" s="15"/>
     </row>
     <row r="14" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="72"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="91"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="77"/>
       <c r="F14" s="20">
         <v>4</v>
       </c>
@@ -3660,10 +3664,10 @@
       <c r="K14" s="15"/>
     </row>
     <row r="15" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="72"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="67" t="s">
+      <c r="B15" s="67"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="81" t="s">
         <v>92</v>
       </c>
       <c r="F15" s="20">
@@ -3675,10 +3679,10 @@
       <c r="K15" s="15"/>
     </row>
     <row r="16" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="72"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
       <c r="F16" s="20">
         <v>2</v>
       </c>
@@ -3688,10 +3692,10 @@
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="72"/>
-      <c r="C17" s="96"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="88"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
       <c r="F17" s="20">
         <v>4</v>
       </c>
@@ -3701,9 +3705,9 @@
       <c r="K17" s="15"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="72"/>
-      <c r="C18" s="96"/>
-      <c r="D18" s="66" t="s">
+      <c r="B18" s="67"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="99" t="s">
         <v>90</v>
       </c>
       <c r="E18" s="45"/>
@@ -3717,10 +3721,10 @@
       <c r="K18" s="15"/>
     </row>
     <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="72"/>
-      <c r="C19" s="96"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="69" t="s">
+      <c r="B19" s="67"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="85" t="s">
         <v>96</v>
       </c>
       <c r="F19" s="9">
@@ -3733,10 +3737,10 @@
       <c r="K19" s="15"/>
     </row>
     <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="72"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="69"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="85"/>
       <c r="F20" s="9">
         <v>2</v>
       </c>
@@ -3747,10 +3751,10 @@
       <c r="K20" s="16"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="72"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="69"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="88"/>
+      <c r="D21" s="82"/>
+      <c r="E21" s="85"/>
       <c r="F21" s="9">
         <v>4</v>
       </c>
@@ -3759,10 +3763,10 @@
       <c r="I21" s="10"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="72"/>
-      <c r="C22" s="96"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="69"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="85"/>
       <c r="F22" s="9">
         <v>8</v>
       </c>
@@ -3771,10 +3775,10 @@
       <c r="I22" s="10"/>
     </row>
     <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="72"/>
-      <c r="C23" s="97"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="70"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="86"/>
       <c r="F23" s="9">
         <v>16</v>
       </c>
@@ -3783,7 +3787,7 @@
       <c r="I23" s="10"/>
     </row>
     <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="72"/>
+      <c r="B24" s="67"/>
       <c r="C24" s="58" t="s">
         <v>98</v>
       </c>
@@ -3803,12 +3807,12 @@
       <c r="K24" s="15"/>
     </row>
     <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="72"/>
-      <c r="C25" s="98"/>
-      <c r="D25" s="67" t="s">
+      <c r="B25" s="67"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="67" t="s">
+      <c r="E25" s="81" t="s">
         <v>96</v>
       </c>
       <c r="F25" s="9">
@@ -3821,10 +3825,10 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="72"/>
-      <c r="C26" s="98"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="68"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="90"/>
+      <c r="D26" s="82"/>
+      <c r="E26" s="82"/>
       <c r="F26" s="9">
         <v>2</v>
       </c>
@@ -3835,10 +3839,10 @@
       <c r="K26" s="15"/>
     </row>
     <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="72"/>
-      <c r="C27" s="98"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="68"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="90"/>
+      <c r="D27" s="82"/>
+      <c r="E27" s="82"/>
       <c r="F27" s="9">
         <v>4</v>
       </c>
@@ -3849,10 +3853,10 @@
       <c r="K27" s="15"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="72"/>
-      <c r="C28" s="98"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="68"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="82"/>
+      <c r="E28" s="82"/>
       <c r="F28" s="9">
         <v>8</v>
       </c>
@@ -3863,10 +3867,10 @@
       <c r="K28" s="15"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="72"/>
-      <c r="C29" s="98"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="68"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="90"/>
+      <c r="D29" s="82"/>
+      <c r="E29" s="82"/>
       <c r="F29" s="9">
         <v>16</v>
       </c>
@@ -3877,10 +3881,10 @@
       <c r="K29" s="15"/>
     </row>
     <row r="30" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="72"/>
-      <c r="C30" s="98"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="74"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="90"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="83"/>
       <c r="F30" s="9">
         <v>32</v>
       </c>
@@ -3891,9 +3895,9 @@
       <c r="K30" s="15"/>
     </row>
     <row r="31" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="72"/>
-      <c r="C31" s="98"/>
-      <c r="D31" s="68"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="82"/>
       <c r="E31" s="26" t="s">
         <v>97</v>
       </c>
@@ -3909,10 +3913,10 @@
       <c r="K31" s="15"/>
     </row>
     <row r="32" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="72"/>
-      <c r="C32" s="98"/>
-      <c r="D32" s="68"/>
-      <c r="E32" s="89" t="s">
+      <c r="B32" s="67"/>
+      <c r="C32" s="90"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="75" t="s">
         <v>93</v>
       </c>
       <c r="F32" s="20">
@@ -3925,10 +3929,10 @@
       <c r="K32" s="15"/>
     </row>
     <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="72"/>
-      <c r="C33" s="98"/>
-      <c r="D33" s="68"/>
-      <c r="E33" s="90"/>
+      <c r="B33" s="67"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="76"/>
       <c r="F33" s="20">
         <v>2</v>
       </c>
@@ -3939,10 +3943,10 @@
       <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="72"/>
-      <c r="C34" s="98"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="91"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="77"/>
       <c r="F34" s="20">
         <v>4</v>
       </c>
@@ -3953,10 +3957,10 @@
       <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="72"/>
-      <c r="C35" s="98"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="67" t="s">
+      <c r="B35" s="67"/>
+      <c r="C35" s="90"/>
+      <c r="D35" s="82"/>
+      <c r="E35" s="81" t="s">
         <v>92</v>
       </c>
       <c r="F35" s="20">
@@ -3969,10 +3973,10 @@
       <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="72"/>
-      <c r="C36" s="98"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="82"/>
+      <c r="E36" s="82"/>
       <c r="F36" s="20">
         <v>2</v>
       </c>
@@ -3983,10 +3987,10 @@
       <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="72"/>
-      <c r="C37" s="98"/>
-      <c r="D37" s="74"/>
-      <c r="E37" s="74"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="90"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
       <c r="F37" s="20">
         <v>4</v>
       </c>
@@ -3997,9 +4001,9 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="72"/>
-      <c r="C38" s="98"/>
-      <c r="D38" s="66" t="s">
+      <c r="B38" s="67"/>
+      <c r="C38" s="90"/>
+      <c r="D38" s="99" t="s">
         <v>90</v>
       </c>
       <c r="F38" s="21" t="s">
@@ -4012,10 +4016,10 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="72"/>
-      <c r="C39" s="98"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="69" t="s">
+      <c r="B39" s="67"/>
+      <c r="C39" s="90"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="85" t="s">
         <v>96</v>
       </c>
       <c r="F39" s="9">
@@ -4028,10 +4032,10 @@
       <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="72"/>
-      <c r="C40" s="98"/>
-      <c r="D40" s="68"/>
-      <c r="E40" s="69"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="85"/>
       <c r="F40" s="9">
         <v>2</v>
       </c>
@@ -4042,10 +4046,10 @@
       <c r="K40" s="16"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="72"/>
-      <c r="C41" s="98"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="69"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="85"/>
       <c r="F41" s="9">
         <v>4</v>
       </c>
@@ -4054,10 +4058,10 @@
       <c r="I41" s="10"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="72"/>
-      <c r="C42" s="98"/>
-      <c r="D42" s="68"/>
-      <c r="E42" s="69"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="90"/>
+      <c r="D42" s="82"/>
+      <c r="E42" s="85"/>
       <c r="F42" s="9">
         <v>8</v>
       </c>
@@ -4066,10 +4070,10 @@
       <c r="I42" s="10"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="72"/>
-      <c r="C43" s="99"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="70"/>
+      <c r="B43" s="67"/>
+      <c r="C43" s="91"/>
+      <c r="D43" s="82"/>
+      <c r="E43" s="86"/>
       <c r="F43" s="9">
         <v>16</v>
       </c>
@@ -4079,7 +4083,7 @@
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
-      <c r="B44" s="72"/>
+      <c r="B44" s="67"/>
       <c r="C44" s="58" t="s">
         <v>99</v>
       </c>
@@ -4100,12 +4104,12 @@
     </row>
     <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="27"/>
-      <c r="B45" s="72"/>
-      <c r="C45" s="98"/>
-      <c r="D45" s="76" t="s">
+      <c r="B45" s="67"/>
+      <c r="C45" s="90"/>
+      <c r="D45" s="92" t="s">
         <v>87</v>
       </c>
-      <c r="E45" s="76" t="s">
+      <c r="E45" s="92" t="s">
         <v>96</v>
       </c>
       <c r="F45" s="31">
@@ -4119,10 +4123,10 @@
     </row>
     <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
-      <c r="B46" s="72"/>
-      <c r="C46" s="98"/>
-      <c r="D46" s="77"/>
-      <c r="E46" s="77"/>
+      <c r="B46" s="67"/>
+      <c r="C46" s="90"/>
+      <c r="D46" s="93"/>
+      <c r="E46" s="93"/>
       <c r="F46" s="31">
         <v>2</v>
       </c>
@@ -4134,10 +4138,10 @@
     </row>
     <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="27"/>
-      <c r="B47" s="72"/>
-      <c r="C47" s="98"/>
-      <c r="D47" s="77"/>
-      <c r="E47" s="77"/>
+      <c r="B47" s="67"/>
+      <c r="C47" s="90"/>
+      <c r="D47" s="93"/>
+      <c r="E47" s="93"/>
       <c r="F47" s="31">
         <v>4</v>
       </c>
@@ -4149,10 +4153,10 @@
     </row>
     <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="27"/>
-      <c r="B48" s="72"/>
-      <c r="C48" s="98"/>
-      <c r="D48" s="77"/>
-      <c r="E48" s="77"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="90"/>
+      <c r="D48" s="93"/>
+      <c r="E48" s="93"/>
       <c r="F48" s="31">
         <v>8</v>
       </c>
@@ -4164,10 +4168,10 @@
     </row>
     <row r="49" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="27"/>
-      <c r="B49" s="72"/>
-      <c r="C49" s="98"/>
-      <c r="D49" s="77"/>
-      <c r="E49" s="77"/>
+      <c r="B49" s="67"/>
+      <c r="C49" s="90"/>
+      <c r="D49" s="93"/>
+      <c r="E49" s="93"/>
       <c r="F49" s="31">
         <v>16</v>
       </c>
@@ -4179,10 +4183,10 @@
     </row>
     <row r="50" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="27"/>
-      <c r="B50" s="72"/>
-      <c r="C50" s="98"/>
-      <c r="D50" s="77"/>
-      <c r="E50" s="78"/>
+      <c r="B50" s="67"/>
+      <c r="C50" s="90"/>
+      <c r="D50" s="93"/>
+      <c r="E50" s="94"/>
       <c r="F50" s="31">
         <v>32</v>
       </c>
@@ -4194,9 +4198,9 @@
     </row>
     <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="27"/>
-      <c r="B51" s="72"/>
-      <c r="C51" s="98"/>
-      <c r="D51" s="77"/>
+      <c r="B51" s="67"/>
+      <c r="C51" s="90"/>
+      <c r="D51" s="93"/>
       <c r="E51" s="34" t="s">
         <v>97</v>
       </c>
@@ -4213,10 +4217,10 @@
     </row>
     <row r="52" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="27"/>
-      <c r="B52" s="72"/>
-      <c r="C52" s="98"/>
-      <c r="D52" s="77"/>
-      <c r="E52" s="92" t="s">
+      <c r="B52" s="67"/>
+      <c r="C52" s="90"/>
+      <c r="D52" s="93"/>
+      <c r="E52" s="78" t="s">
         <v>93</v>
       </c>
       <c r="F52" s="31">
@@ -4230,10 +4234,10 @@
     </row>
     <row r="53" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="27"/>
-      <c r="B53" s="72"/>
-      <c r="C53" s="98"/>
-      <c r="D53" s="77"/>
-      <c r="E53" s="93"/>
+      <c r="B53" s="67"/>
+      <c r="C53" s="90"/>
+      <c r="D53" s="93"/>
+      <c r="E53" s="79"/>
       <c r="F53" s="31">
         <v>2</v>
       </c>
@@ -4245,10 +4249,10 @@
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="27"/>
-      <c r="B54" s="72"/>
-      <c r="C54" s="98"/>
-      <c r="D54" s="77"/>
-      <c r="E54" s="94"/>
+      <c r="B54" s="67"/>
+      <c r="C54" s="90"/>
+      <c r="D54" s="93"/>
+      <c r="E54" s="80"/>
       <c r="F54" s="31">
         <v>4</v>
       </c>
@@ -4260,10 +4264,10 @@
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="27"/>
-      <c r="B55" s="72"/>
-      <c r="C55" s="98"/>
-      <c r="D55" s="77"/>
-      <c r="E55" s="76" t="s">
+      <c r="B55" s="67"/>
+      <c r="C55" s="90"/>
+      <c r="D55" s="93"/>
+      <c r="E55" s="92" t="s">
         <v>92</v>
       </c>
       <c r="F55" s="31">
@@ -4277,10 +4281,10 @@
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="27"/>
-      <c r="B56" s="72"/>
-      <c r="C56" s="98"/>
-      <c r="D56" s="77"/>
-      <c r="E56" s="77"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="90"/>
+      <c r="D56" s="93"/>
+      <c r="E56" s="93"/>
       <c r="F56" s="31">
         <v>2</v>
       </c>
@@ -4292,10 +4296,10 @@
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="27"/>
-      <c r="B57" s="72"/>
-      <c r="C57" s="98"/>
-      <c r="D57" s="78"/>
-      <c r="E57" s="78"/>
+      <c r="B57" s="67"/>
+      <c r="C57" s="90"/>
+      <c r="D57" s="94"/>
+      <c r="E57" s="94"/>
       <c r="F57" s="31">
         <v>4</v>
       </c>
@@ -4307,9 +4311,9 @@
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="27"/>
-      <c r="B58" s="72"/>
-      <c r="C58" s="98"/>
-      <c r="D58" s="79" t="s">
+      <c r="B58" s="67"/>
+      <c r="C58" s="90"/>
+      <c r="D58" s="95" t="s">
         <v>90</v>
       </c>
       <c r="E58" s="36" t="s">
@@ -4326,10 +4330,10 @@
     </row>
     <row r="59" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="27"/>
-      <c r="B59" s="72"/>
-      <c r="C59" s="98"/>
-      <c r="D59" s="76"/>
-      <c r="E59" s="80" t="s">
+      <c r="B59" s="67"/>
+      <c r="C59" s="90"/>
+      <c r="D59" s="92"/>
+      <c r="E59" s="96" t="s">
         <v>96</v>
       </c>
       <c r="F59" s="31">
@@ -4343,10 +4347,10 @@
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="27"/>
-      <c r="B60" s="72"/>
-      <c r="C60" s="98"/>
-      <c r="D60" s="77"/>
-      <c r="E60" s="81"/>
+      <c r="B60" s="67"/>
+      <c r="C60" s="90"/>
+      <c r="D60" s="93"/>
+      <c r="E60" s="97"/>
       <c r="F60" s="31">
         <v>2</v>
       </c>
@@ -4358,10 +4362,10 @@
     </row>
     <row r="61" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="27"/>
-      <c r="B61" s="72"/>
-      <c r="C61" s="98"/>
-      <c r="D61" s="77"/>
-      <c r="E61" s="81"/>
+      <c r="B61" s="67"/>
+      <c r="C61" s="90"/>
+      <c r="D61" s="93"/>
+      <c r="E61" s="97"/>
       <c r="F61" s="31">
         <v>4</v>
       </c>
@@ -4373,10 +4377,10 @@
     </row>
     <row r="62" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="27"/>
-      <c r="B62" s="72"/>
-      <c r="C62" s="98"/>
-      <c r="D62" s="77"/>
-      <c r="E62" s="81"/>
+      <c r="B62" s="67"/>
+      <c r="C62" s="90"/>
+      <c r="D62" s="93"/>
+      <c r="E62" s="97"/>
       <c r="F62" s="31">
         <v>8</v>
       </c>
@@ -4388,10 +4392,10 @@
     </row>
     <row r="63" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="27"/>
-      <c r="B63" s="73"/>
-      <c r="C63" s="99"/>
-      <c r="D63" s="78"/>
-      <c r="E63" s="82"/>
+      <c r="B63" s="68"/>
+      <c r="C63" s="91"/>
+      <c r="D63" s="94"/>
+      <c r="E63" s="98"/>
       <c r="F63" s="31">
         <v>16</v>
       </c>
@@ -4402,7 +4406,7 @@
       <c r="K63" s="27"/>
     </row>
     <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="71" t="s">
+      <c r="B64" s="66" t="s">
         <v>82</v>
       </c>
       <c r="C64" s="20" t="s">
@@ -4428,14 +4432,14 @@
       <c r="K64" s="15"/>
     </row>
     <row r="65" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="72"/>
-      <c r="C65" s="95" t="s">
+      <c r="B65" s="67"/>
+      <c r="C65" s="87" t="s">
         <v>83</v>
       </c>
-      <c r="D65" s="67" t="s">
+      <c r="D65" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="E65" s="67" t="s">
+      <c r="E65" s="81" t="s">
         <v>100</v>
       </c>
       <c r="F65" s="9">
@@ -4448,10 +4452,10 @@
       <c r="K65" s="15"/>
     </row>
     <row r="66" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="72"/>
-      <c r="C66" s="96"/>
-      <c r="D66" s="68"/>
-      <c r="E66" s="68"/>
+      <c r="B66" s="67"/>
+      <c r="C66" s="88"/>
+      <c r="D66" s="82"/>
+      <c r="E66" s="82"/>
       <c r="F66" s="9">
         <v>2</v>
       </c>
@@ -4462,10 +4466,10 @@
       <c r="K66" s="15"/>
     </row>
     <row r="67" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="72"/>
-      <c r="C67" s="96"/>
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
+      <c r="B67" s="67"/>
+      <c r="C67" s="88"/>
+      <c r="D67" s="82"/>
+      <c r="E67" s="82"/>
       <c r="F67" s="9">
         <v>4</v>
       </c>
@@ -4476,10 +4480,10 @@
       <c r="K67" s="15"/>
     </row>
     <row r="68" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="72"/>
-      <c r="C68" s="96"/>
-      <c r="D68" s="68"/>
-      <c r="E68" s="68"/>
+      <c r="B68" s="67"/>
+      <c r="C68" s="88"/>
+      <c r="D68" s="82"/>
+      <c r="E68" s="82"/>
       <c r="F68" s="9">
         <v>8</v>
       </c>
@@ -4490,10 +4494,10 @@
       <c r="K68" s="15"/>
     </row>
     <row r="69" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="72"/>
-      <c r="C69" s="96"/>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
+      <c r="B69" s="67"/>
+      <c r="C69" s="88"/>
+      <c r="D69" s="82"/>
+      <c r="E69" s="82"/>
       <c r="F69" s="9">
         <v>16</v>
       </c>
@@ -4504,10 +4508,10 @@
       <c r="K69" s="15"/>
     </row>
     <row r="70" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="72"/>
-      <c r="C70" s="96"/>
-      <c r="D70" s="68"/>
-      <c r="E70" s="74"/>
+      <c r="B70" s="67"/>
+      <c r="C70" s="88"/>
+      <c r="D70" s="82"/>
+      <c r="E70" s="83"/>
       <c r="F70" s="9">
         <v>32</v>
       </c>
@@ -4518,8 +4522,8 @@
       <c r="K70" s="15"/>
     </row>
     <row r="71" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="72"/>
-      <c r="C71" s="96"/>
+      <c r="B71" s="67"/>
+      <c r="C71" s="88"/>
       <c r="D71" s="42"/>
       <c r="E71" s="36" t="s">
         <v>95</v>
@@ -4534,12 +4538,12 @@
       <c r="K71" s="15"/>
     </row>
     <row r="72" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="72"/>
-      <c r="C72" s="96"/>
-      <c r="D72" s="67" t="s">
+      <c r="B72" s="67"/>
+      <c r="C72" s="88"/>
+      <c r="D72" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="E72" s="75" t="s">
+      <c r="E72" s="84" t="s">
         <v>100</v>
       </c>
       <c r="F72" s="9">
@@ -4552,10 +4556,10 @@
       <c r="K72" s="15"/>
     </row>
     <row r="73" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="72"/>
-      <c r="C73" s="96"/>
-      <c r="D73" s="68"/>
-      <c r="E73" s="69"/>
+      <c r="B73" s="67"/>
+      <c r="C73" s="88"/>
+      <c r="D73" s="82"/>
+      <c r="E73" s="85"/>
       <c r="F73" s="9">
         <v>2</v>
       </c>
@@ -4566,10 +4570,10 @@
       <c r="K73" s="16"/>
     </row>
     <row r="74" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="72"/>
-      <c r="C74" s="96"/>
-      <c r="D74" s="68"/>
-      <c r="E74" s="69"/>
+      <c r="B74" s="67"/>
+      <c r="C74" s="88"/>
+      <c r="D74" s="82"/>
+      <c r="E74" s="85"/>
       <c r="F74" s="9">
         <v>4</v>
       </c>
@@ -4578,10 +4582,10 @@
       <c r="I74" s="10"/>
     </row>
     <row r="75" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="72"/>
-      <c r="C75" s="96"/>
-      <c r="D75" s="68"/>
-      <c r="E75" s="69"/>
+      <c r="B75" s="67"/>
+      <c r="C75" s="88"/>
+      <c r="D75" s="82"/>
+      <c r="E75" s="85"/>
       <c r="F75" s="9">
         <v>8</v>
       </c>
@@ -4590,10 +4594,10 @@
       <c r="I75" s="10"/>
     </row>
     <row r="76" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="72"/>
-      <c r="C76" s="97"/>
-      <c r="D76" s="74"/>
-      <c r="E76" s="70"/>
+      <c r="B76" s="67"/>
+      <c r="C76" s="89"/>
+      <c r="D76" s="83"/>
+      <c r="E76" s="86"/>
       <c r="F76" s="9">
         <v>16</v>
       </c>
@@ -4602,14 +4606,14 @@
       <c r="I76" s="10"/>
     </row>
     <row r="77" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="72"/>
-      <c r="C77" s="95" t="s">
+      <c r="B77" s="67"/>
+      <c r="C77" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="D77" s="67" t="s">
+      <c r="D77" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="E77" s="67" t="s">
+      <c r="E77" s="81" t="s">
         <v>100</v>
       </c>
       <c r="F77" s="9">
@@ -4622,10 +4626,10 @@
       <c r="K77" s="15"/>
     </row>
     <row r="78" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="72"/>
-      <c r="C78" s="96"/>
-      <c r="D78" s="68"/>
-      <c r="E78" s="68"/>
+      <c r="B78" s="67"/>
+      <c r="C78" s="88"/>
+      <c r="D78" s="82"/>
+      <c r="E78" s="82"/>
       <c r="F78" s="9">
         <v>2</v>
       </c>
@@ -4636,10 +4640,10 @@
       <c r="K78" s="15"/>
     </row>
     <row r="79" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="72"/>
-      <c r="C79" s="96"/>
-      <c r="D79" s="68"/>
-      <c r="E79" s="68"/>
+      <c r="B79" s="67"/>
+      <c r="C79" s="88"/>
+      <c r="D79" s="82"/>
+      <c r="E79" s="82"/>
       <c r="F79" s="9">
         <v>4</v>
       </c>
@@ -4650,10 +4654,10 @@
       <c r="K79" s="15"/>
     </row>
     <row r="80" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="72"/>
-      <c r="C80" s="96"/>
-      <c r="D80" s="68"/>
-      <c r="E80" s="68"/>
+      <c r="B80" s="67"/>
+      <c r="C80" s="88"/>
+      <c r="D80" s="82"/>
+      <c r="E80" s="82"/>
       <c r="F80" s="9">
         <v>8</v>
       </c>
@@ -4664,10 +4668,10 @@
       <c r="K80" s="15"/>
     </row>
     <row r="81" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="72"/>
-      <c r="C81" s="96"/>
-      <c r="D81" s="68"/>
-      <c r="E81" s="68"/>
+      <c r="B81" s="67"/>
+      <c r="C81" s="88"/>
+      <c r="D81" s="82"/>
+      <c r="E81" s="82"/>
       <c r="F81" s="9">
         <v>16</v>
       </c>
@@ -4678,10 +4682,10 @@
       <c r="K81" s="15"/>
     </row>
     <row r="82" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="72"/>
-      <c r="C82" s="96"/>
-      <c r="D82" s="68"/>
-      <c r="E82" s="74"/>
+      <c r="B82" s="67"/>
+      <c r="C82" s="88"/>
+      <c r="D82" s="82"/>
+      <c r="E82" s="83"/>
       <c r="F82" s="9">
         <v>32</v>
       </c>
@@ -4692,8 +4696,8 @@
       <c r="K82" s="15"/>
     </row>
     <row r="83" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="72"/>
-      <c r="C83" s="96"/>
+      <c r="B83" s="67"/>
+      <c r="C83" s="88"/>
       <c r="D83" s="42"/>
       <c r="E83" s="36" t="s">
         <v>95</v>
@@ -4708,12 +4712,12 @@
       <c r="K83" s="15"/>
     </row>
     <row r="84" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="72"/>
-      <c r="C84" s="96"/>
-      <c r="D84" s="67" t="s">
+      <c r="B84" s="67"/>
+      <c r="C84" s="88"/>
+      <c r="D84" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="E84" s="75" t="s">
+      <c r="E84" s="84" t="s">
         <v>100</v>
       </c>
       <c r="F84" s="9">
@@ -4726,10 +4730,10 @@
       <c r="K84" s="15"/>
     </row>
     <row r="85" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="72"/>
-      <c r="C85" s="96"/>
-      <c r="D85" s="68"/>
-      <c r="E85" s="69"/>
+      <c r="B85" s="67"/>
+      <c r="C85" s="88"/>
+      <c r="D85" s="82"/>
+      <c r="E85" s="85"/>
       <c r="F85" s="9">
         <v>2</v>
       </c>
@@ -4740,10 +4744,10 @@
       <c r="K85" s="16"/>
     </row>
     <row r="86" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="72"/>
-      <c r="C86" s="96"/>
-      <c r="D86" s="68"/>
-      <c r="E86" s="69"/>
+      <c r="B86" s="67"/>
+      <c r="C86" s="88"/>
+      <c r="D86" s="82"/>
+      <c r="E86" s="85"/>
       <c r="F86" s="9">
         <v>4</v>
       </c>
@@ -4752,10 +4756,10 @@
       <c r="I86" s="10"/>
     </row>
     <row r="87" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="72"/>
-      <c r="C87" s="96"/>
-      <c r="D87" s="68"/>
-      <c r="E87" s="69"/>
+      <c r="B87" s="67"/>
+      <c r="C87" s="88"/>
+      <c r="D87" s="82"/>
+      <c r="E87" s="85"/>
       <c r="F87" s="9">
         <v>8</v>
       </c>
@@ -4764,10 +4768,10 @@
       <c r="I87" s="10"/>
     </row>
     <row r="88" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="73"/>
-      <c r="C88" s="97"/>
-      <c r="D88" s="74"/>
-      <c r="E88" s="70"/>
+      <c r="B88" s="68"/>
+      <c r="C88" s="89"/>
+      <c r="D88" s="83"/>
+      <c r="E88" s="86"/>
       <c r="F88" s="9">
         <v>16</v>
       </c>
@@ -5664,6 +5668,25 @@
     <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="D38:D43"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="B4:B63"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="E5:E10"/>
+    <mergeCell ref="E19:E23"/>
+    <mergeCell ref="D5:D17"/>
+    <mergeCell ref="D18:D23"/>
+    <mergeCell ref="D25:D37"/>
+    <mergeCell ref="E25:E30"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="D65:D70"/>
+    <mergeCell ref="E65:E70"/>
+    <mergeCell ref="E72:E76"/>
+    <mergeCell ref="D45:D57"/>
+    <mergeCell ref="E45:E50"/>
+    <mergeCell ref="E55:E57"/>
+    <mergeCell ref="D58:D63"/>
+    <mergeCell ref="E59:E63"/>
     <mergeCell ref="B64:B88"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:F3"/>
@@ -5680,25 +5703,6 @@
     <mergeCell ref="D72:D76"/>
     <mergeCell ref="D77:D82"/>
     <mergeCell ref="E77:E82"/>
-    <mergeCell ref="D65:D70"/>
-    <mergeCell ref="E65:E70"/>
-    <mergeCell ref="E72:E76"/>
-    <mergeCell ref="D45:D57"/>
-    <mergeCell ref="E45:E50"/>
-    <mergeCell ref="E55:E57"/>
-    <mergeCell ref="D58:D63"/>
-    <mergeCell ref="E59:E63"/>
-    <mergeCell ref="D38:D43"/>
-    <mergeCell ref="E39:E43"/>
-    <mergeCell ref="B4:B63"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="E5:E10"/>
-    <mergeCell ref="E19:E23"/>
-    <mergeCell ref="D5:D17"/>
-    <mergeCell ref="D18:D23"/>
-    <mergeCell ref="D25:D37"/>
-    <mergeCell ref="E25:E30"/>
-    <mergeCell ref="E35:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/RCC-Benchmark-Report.xlsx
+++ b/RCC-Benchmark-Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gustavo\OneDrive - The University of Chicago\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25DCF5C3-AB1B-402D-B196-7BD8C15A2DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D87CD72-8D93-4BA3-AAA5-7FDD36C91297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="114">
   <si>
     <t>Standard Compute Benchmarks</t>
   </si>
@@ -1358,6 +1358,9 @@
   <si>
     <t>HPCG
 GPU</t>
+  </si>
+  <si>
+    <t>Values</t>
   </si>
 </sst>
 </file>
@@ -2310,11 +2313,11 @@
         <v>5</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>4</v>
+        <v>113</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="7" t="s">
-        <v>4</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">

--- a/RCC-Benchmark-Report.xlsx
+++ b/RCC-Benchmark-Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gustavo\OneDrive - The University of Chicago\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D87CD72-8D93-4BA3-AAA5-7FDD36C91297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3211D17-C960-4F8E-A29D-0C308682E14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1831,6 +1831,21 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1838,6 +1853,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1876,24 +1918,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1907,30 +1931,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3457,25 +3457,25 @@
       <c r="K1" s="15"/>
     </row>
     <row r="2" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="83" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="71"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="85"/>
       <c r="J2" s="15"/>
       <c r="K2" s="15"/>
     </row>
     <row r="3" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="72"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="74"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="88"/>
       <c r="G3" s="3" t="s">
         <v>1</v>
       </c>
@@ -3489,7 +3489,7 @@
       <c r="K3" s="15"/>
     </row>
     <row r="4" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="71" t="s">
         <v>81</v>
       </c>
       <c r="C4" s="20" t="s">
@@ -3515,14 +3515,14 @@
       <c r="K4" s="15"/>
     </row>
     <row r="5" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="67"/>
-      <c r="C5" s="87" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="81" t="s">
+      <c r="D5" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="81" t="s">
+      <c r="E5" s="67" t="s">
         <v>96</v>
       </c>
       <c r="F5" s="9">
@@ -3535,10 +3535,10 @@
       <c r="K5" s="15"/>
     </row>
     <row r="6" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="67"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
+      <c r="B6" s="72"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
       <c r="F6" s="9">
         <v>2</v>
       </c>
@@ -3549,10 +3549,10 @@
       <c r="K6" s="15"/>
     </row>
     <row r="7" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="67"/>
-      <c r="C7" s="88"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
       <c r="F7" s="9">
         <v>4</v>
       </c>
@@ -3563,10 +3563,10 @@
       <c r="K7" s="15"/>
     </row>
     <row r="8" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="67"/>
-      <c r="C8" s="88"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
+      <c r="B8" s="72"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
       <c r="F8" s="9">
         <v>8</v>
       </c>
@@ -3577,10 +3577,10 @@
       <c r="K8" s="15"/>
     </row>
     <row r="9" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="67"/>
-      <c r="C9" s="88"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
+      <c r="B9" s="72"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
       <c r="F9" s="9">
         <v>16</v>
       </c>
@@ -3591,10 +3591,10 @@
       <c r="K9" s="15"/>
     </row>
     <row r="10" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="67"/>
-      <c r="C10" s="88"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="83"/>
+      <c r="B10" s="72"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="74"/>
       <c r="F10" s="9">
         <v>32</v>
       </c>
@@ -3605,9 +3605,9 @@
       <c r="K10" s="15"/>
     </row>
     <row r="11" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="67"/>
-      <c r="C11" s="88"/>
-      <c r="D11" s="82"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="68"/>
       <c r="E11" s="26" t="s">
         <v>97</v>
       </c>
@@ -3623,10 +3623,10 @@
       <c r="K11" s="15"/>
     </row>
     <row r="12" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="67"/>
-      <c r="C12" s="88"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="75" t="s">
+      <c r="B12" s="72"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="89" t="s">
         <v>93</v>
       </c>
       <c r="F12" s="20">
@@ -3639,10 +3639,10 @@
       <c r="K12" s="15"/>
     </row>
     <row r="13" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="67"/>
-      <c r="C13" s="88"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="76"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="90"/>
       <c r="F13" s="20">
         <v>2</v>
       </c>
@@ -3653,10 +3653,10 @@
       <c r="K13" s="15"/>
     </row>
     <row r="14" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="67"/>
-      <c r="C14" s="88"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="77"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="91"/>
       <c r="F14" s="20">
         <v>4</v>
       </c>
@@ -3667,10 +3667,10 @@
       <c r="K14" s="15"/>
     </row>
     <row r="15" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="67"/>
-      <c r="C15" s="88"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="81" t="s">
+      <c r="B15" s="72"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="67" t="s">
         <v>92</v>
       </c>
       <c r="F15" s="20">
@@ -3682,10 +3682,10 @@
       <c r="K15" s="15"/>
     </row>
     <row r="16" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="67"/>
-      <c r="C16" s="88"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
+      <c r="B16" s="72"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
       <c r="F16" s="20">
         <v>2</v>
       </c>
@@ -3695,10 +3695,10 @@
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="67"/>
-      <c r="C17" s="88"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
+      <c r="B17" s="72"/>
+      <c r="C17" s="96"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
       <c r="F17" s="20">
         <v>4</v>
       </c>
@@ -3708,9 +3708,9 @@
       <c r="K17" s="15"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="67"/>
-      <c r="C18" s="88"/>
-      <c r="D18" s="99" t="s">
+      <c r="B18" s="72"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="66" t="s">
         <v>90</v>
       </c>
       <c r="E18" s="45"/>
@@ -3724,10 +3724,10 @@
       <c r="K18" s="15"/>
     </row>
     <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="67"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="81"/>
-      <c r="E19" s="85" t="s">
+      <c r="B19" s="72"/>
+      <c r="C19" s="96"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="69" t="s">
         <v>96</v>
       </c>
       <c r="F19" s="9">
@@ -3740,10 +3740,10 @@
       <c r="K19" s="15"/>
     </row>
     <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="67"/>
-      <c r="C20" s="88"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="85"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="69"/>
       <c r="F20" s="9">
         <v>2</v>
       </c>
@@ -3754,10 +3754,10 @@
       <c r="K20" s="16"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="67"/>
-      <c r="C21" s="88"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="85"/>
+      <c r="B21" s="72"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="69"/>
       <c r="F21" s="9">
         <v>4</v>
       </c>
@@ -3766,10 +3766,10 @@
       <c r="I21" s="10"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="67"/>
-      <c r="C22" s="88"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="85"/>
+      <c r="B22" s="72"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="69"/>
       <c r="F22" s="9">
         <v>8</v>
       </c>
@@ -3778,10 +3778,10 @@
       <c r="I22" s="10"/>
     </row>
     <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="67"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="86"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="97"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="70"/>
       <c r="F23" s="9">
         <v>16</v>
       </c>
@@ -3790,7 +3790,7 @@
       <c r="I23" s="10"/>
     </row>
     <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="67"/>
+      <c r="B24" s="72"/>
       <c r="C24" s="58" t="s">
         <v>98</v>
       </c>
@@ -3810,12 +3810,12 @@
       <c r="K24" s="15"/>
     </row>
     <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="67"/>
-      <c r="C25" s="90"/>
-      <c r="D25" s="81" t="s">
+      <c r="B25" s="72"/>
+      <c r="C25" s="98"/>
+      <c r="D25" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="81" t="s">
+      <c r="E25" s="67" t="s">
         <v>96</v>
       </c>
       <c r="F25" s="9">
@@ -3828,10 +3828,10 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="67"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="82"/>
-      <c r="E26" s="82"/>
+      <c r="B26" s="72"/>
+      <c r="C26" s="98"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
       <c r="F26" s="9">
         <v>2</v>
       </c>
@@ -3842,10 +3842,10 @@
       <c r="K26" s="15"/>
     </row>
     <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="67"/>
-      <c r="C27" s="90"/>
-      <c r="D27" s="82"/>
-      <c r="E27" s="82"/>
+      <c r="B27" s="72"/>
+      <c r="C27" s="98"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
       <c r="F27" s="9">
         <v>4</v>
       </c>
@@ -3856,10 +3856,10 @@
       <c r="K27" s="15"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="67"/>
-      <c r="C28" s="90"/>
-      <c r="D28" s="82"/>
-      <c r="E28" s="82"/>
+      <c r="B28" s="72"/>
+      <c r="C28" s="98"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
       <c r="F28" s="9">
         <v>8</v>
       </c>
@@ -3870,10 +3870,10 @@
       <c r="K28" s="15"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="67"/>
-      <c r="C29" s="90"/>
-      <c r="D29" s="82"/>
-      <c r="E29" s="82"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
       <c r="F29" s="9">
         <v>16</v>
       </c>
@@ -3884,10 +3884,10 @@
       <c r="K29" s="15"/>
     </row>
     <row r="30" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="67"/>
-      <c r="C30" s="90"/>
-      <c r="D30" s="82"/>
-      <c r="E30" s="83"/>
+      <c r="B30" s="72"/>
+      <c r="C30" s="98"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="74"/>
       <c r="F30" s="9">
         <v>32</v>
       </c>
@@ -3898,9 +3898,9 @@
       <c r="K30" s="15"/>
     </row>
     <row r="31" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="67"/>
-      <c r="C31" s="90"/>
-      <c r="D31" s="82"/>
+      <c r="B31" s="72"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="68"/>
       <c r="E31" s="26" t="s">
         <v>97</v>
       </c>
@@ -3916,10 +3916,10 @@
       <c r="K31" s="15"/>
     </row>
     <row r="32" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="67"/>
-      <c r="C32" s="90"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="75" t="s">
+      <c r="B32" s="72"/>
+      <c r="C32" s="98"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="89" t="s">
         <v>93</v>
       </c>
       <c r="F32" s="20">
@@ -3932,10 +3932,10 @@
       <c r="K32" s="15"/>
     </row>
     <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="67"/>
-      <c r="C33" s="90"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="76"/>
+      <c r="B33" s="72"/>
+      <c r="C33" s="98"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="90"/>
       <c r="F33" s="20">
         <v>2</v>
       </c>
@@ -3946,10 +3946,10 @@
       <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="67"/>
-      <c r="C34" s="90"/>
-      <c r="D34" s="82"/>
-      <c r="E34" s="77"/>
+      <c r="B34" s="72"/>
+      <c r="C34" s="98"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="91"/>
       <c r="F34" s="20">
         <v>4</v>
       </c>
@@ -3960,10 +3960,10 @@
       <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="67"/>
-      <c r="C35" s="90"/>
-      <c r="D35" s="82"/>
-      <c r="E35" s="81" t="s">
+      <c r="B35" s="72"/>
+      <c r="C35" s="98"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="67" t="s">
         <v>92</v>
       </c>
       <c r="F35" s="20">
@@ -3976,10 +3976,10 @@
       <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="67"/>
-      <c r="C36" s="90"/>
-      <c r="D36" s="82"/>
-      <c r="E36" s="82"/>
+      <c r="B36" s="72"/>
+      <c r="C36" s="98"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
       <c r="F36" s="20">
         <v>2</v>
       </c>
@@ -3990,10 +3990,10 @@
       <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="67"/>
-      <c r="C37" s="90"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="83"/>
+      <c r="B37" s="72"/>
+      <c r="C37" s="98"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="74"/>
       <c r="F37" s="20">
         <v>4</v>
       </c>
@@ -4004,9 +4004,9 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="67"/>
-      <c r="C38" s="90"/>
-      <c r="D38" s="99" t="s">
+      <c r="B38" s="72"/>
+      <c r="C38" s="98"/>
+      <c r="D38" s="66" t="s">
         <v>90</v>
       </c>
       <c r="F38" s="21" t="s">
@@ -4019,10 +4019,10 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="67"/>
-      <c r="C39" s="90"/>
-      <c r="D39" s="81"/>
-      <c r="E39" s="85" t="s">
+      <c r="B39" s="72"/>
+      <c r="C39" s="98"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="69" t="s">
         <v>96</v>
       </c>
       <c r="F39" s="9">
@@ -4035,10 +4035,10 @@
       <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="67"/>
-      <c r="C40" s="90"/>
-      <c r="D40" s="82"/>
-      <c r="E40" s="85"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="98"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="69"/>
       <c r="F40" s="9">
         <v>2</v>
       </c>
@@ -4049,10 +4049,10 @@
       <c r="K40" s="16"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="67"/>
-      <c r="C41" s="90"/>
-      <c r="D41" s="82"/>
-      <c r="E41" s="85"/>
+      <c r="B41" s="72"/>
+      <c r="C41" s="98"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="69"/>
       <c r="F41" s="9">
         <v>4</v>
       </c>
@@ -4061,10 +4061,10 @@
       <c r="I41" s="10"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="67"/>
-      <c r="C42" s="90"/>
-      <c r="D42" s="82"/>
-      <c r="E42" s="85"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="98"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="69"/>
       <c r="F42" s="9">
         <v>8</v>
       </c>
@@ -4073,10 +4073,10 @@
       <c r="I42" s="10"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="67"/>
-      <c r="C43" s="91"/>
-      <c r="D43" s="82"/>
-      <c r="E43" s="86"/>
+      <c r="B43" s="72"/>
+      <c r="C43" s="99"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="70"/>
       <c r="F43" s="9">
         <v>16</v>
       </c>
@@ -4086,7 +4086,7 @@
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
-      <c r="B44" s="67"/>
+      <c r="B44" s="72"/>
       <c r="C44" s="58" t="s">
         <v>99</v>
       </c>
@@ -4107,12 +4107,12 @@
     </row>
     <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="27"/>
-      <c r="B45" s="67"/>
-      <c r="C45" s="90"/>
-      <c r="D45" s="92" t="s">
+      <c r="B45" s="72"/>
+      <c r="C45" s="98"/>
+      <c r="D45" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="E45" s="92" t="s">
+      <c r="E45" s="76" t="s">
         <v>96</v>
       </c>
       <c r="F45" s="31">
@@ -4126,10 +4126,10 @@
     </row>
     <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
-      <c r="B46" s="67"/>
-      <c r="C46" s="90"/>
-      <c r="D46" s="93"/>
-      <c r="E46" s="93"/>
+      <c r="B46" s="72"/>
+      <c r="C46" s="98"/>
+      <c r="D46" s="77"/>
+      <c r="E46" s="77"/>
       <c r="F46" s="31">
         <v>2</v>
       </c>
@@ -4141,10 +4141,10 @@
     </row>
     <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="27"/>
-      <c r="B47" s="67"/>
-      <c r="C47" s="90"/>
-      <c r="D47" s="93"/>
-      <c r="E47" s="93"/>
+      <c r="B47" s="72"/>
+      <c r="C47" s="98"/>
+      <c r="D47" s="77"/>
+      <c r="E47" s="77"/>
       <c r="F47" s="31">
         <v>4</v>
       </c>
@@ -4156,10 +4156,10 @@
     </row>
     <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="27"/>
-      <c r="B48" s="67"/>
-      <c r="C48" s="90"/>
-      <c r="D48" s="93"/>
-      <c r="E48" s="93"/>
+      <c r="B48" s="72"/>
+      <c r="C48" s="98"/>
+      <c r="D48" s="77"/>
+      <c r="E48" s="77"/>
       <c r="F48" s="31">
         <v>8</v>
       </c>
@@ -4171,10 +4171,10 @@
     </row>
     <row r="49" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="27"/>
-      <c r="B49" s="67"/>
-      <c r="C49" s="90"/>
-      <c r="D49" s="93"/>
-      <c r="E49" s="93"/>
+      <c r="B49" s="72"/>
+      <c r="C49" s="98"/>
+      <c r="D49" s="77"/>
+      <c r="E49" s="77"/>
       <c r="F49" s="31">
         <v>16</v>
       </c>
@@ -4186,10 +4186,10 @@
     </row>
     <row r="50" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="27"/>
-      <c r="B50" s="67"/>
-      <c r="C50" s="90"/>
-      <c r="D50" s="93"/>
-      <c r="E50" s="94"/>
+      <c r="B50" s="72"/>
+      <c r="C50" s="98"/>
+      <c r="D50" s="77"/>
+      <c r="E50" s="78"/>
       <c r="F50" s="31">
         <v>32</v>
       </c>
@@ -4201,9 +4201,9 @@
     </row>
     <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="27"/>
-      <c r="B51" s="67"/>
-      <c r="C51" s="90"/>
-      <c r="D51" s="93"/>
+      <c r="B51" s="72"/>
+      <c r="C51" s="98"/>
+      <c r="D51" s="77"/>
       <c r="E51" s="34" t="s">
         <v>97</v>
       </c>
@@ -4220,10 +4220,10 @@
     </row>
     <row r="52" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="27"/>
-      <c r="B52" s="67"/>
-      <c r="C52" s="90"/>
-      <c r="D52" s="93"/>
-      <c r="E52" s="78" t="s">
+      <c r="B52" s="72"/>
+      <c r="C52" s="98"/>
+      <c r="D52" s="77"/>
+      <c r="E52" s="92" t="s">
         <v>93</v>
       </c>
       <c r="F52" s="31">
@@ -4237,10 +4237,10 @@
     </row>
     <row r="53" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="27"/>
-      <c r="B53" s="67"/>
-      <c r="C53" s="90"/>
-      <c r="D53" s="93"/>
-      <c r="E53" s="79"/>
+      <c r="B53" s="72"/>
+      <c r="C53" s="98"/>
+      <c r="D53" s="77"/>
+      <c r="E53" s="93"/>
       <c r="F53" s="31">
         <v>2</v>
       </c>
@@ -4252,10 +4252,10 @@
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="27"/>
-      <c r="B54" s="67"/>
-      <c r="C54" s="90"/>
-      <c r="D54" s="93"/>
-      <c r="E54" s="80"/>
+      <c r="B54" s="72"/>
+      <c r="C54" s="98"/>
+      <c r="D54" s="77"/>
+      <c r="E54" s="94"/>
       <c r="F54" s="31">
         <v>4</v>
       </c>
@@ -4267,10 +4267,10 @@
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="27"/>
-      <c r="B55" s="67"/>
-      <c r="C55" s="90"/>
-      <c r="D55" s="93"/>
-      <c r="E55" s="92" t="s">
+      <c r="B55" s="72"/>
+      <c r="C55" s="98"/>
+      <c r="D55" s="77"/>
+      <c r="E55" s="76" t="s">
         <v>92</v>
       </c>
       <c r="F55" s="31">
@@ -4284,10 +4284,10 @@
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="27"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="90"/>
-      <c r="D56" s="93"/>
-      <c r="E56" s="93"/>
+      <c r="B56" s="72"/>
+      <c r="C56" s="98"/>
+      <c r="D56" s="77"/>
+      <c r="E56" s="77"/>
       <c r="F56" s="31">
         <v>2</v>
       </c>
@@ -4299,10 +4299,10 @@
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="27"/>
-      <c r="B57" s="67"/>
-      <c r="C57" s="90"/>
-      <c r="D57" s="94"/>
-      <c r="E57" s="94"/>
+      <c r="B57" s="72"/>
+      <c r="C57" s="98"/>
+      <c r="D57" s="78"/>
+      <c r="E57" s="78"/>
       <c r="F57" s="31">
         <v>4</v>
       </c>
@@ -4314,9 +4314,9 @@
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="27"/>
-      <c r="B58" s="67"/>
-      <c r="C58" s="90"/>
-      <c r="D58" s="95" t="s">
+      <c r="B58" s="72"/>
+      <c r="C58" s="98"/>
+      <c r="D58" s="79" t="s">
         <v>90</v>
       </c>
       <c r="E58" s="36" t="s">
@@ -4333,10 +4333,10 @@
     </row>
     <row r="59" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="27"/>
-      <c r="B59" s="67"/>
-      <c r="C59" s="90"/>
-      <c r="D59" s="92"/>
-      <c r="E59" s="96" t="s">
+      <c r="B59" s="72"/>
+      <c r="C59" s="98"/>
+      <c r="D59" s="76"/>
+      <c r="E59" s="80" t="s">
         <v>96</v>
       </c>
       <c r="F59" s="31">
@@ -4350,10 +4350,10 @@
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="27"/>
-      <c r="B60" s="67"/>
-      <c r="C60" s="90"/>
-      <c r="D60" s="93"/>
-      <c r="E60" s="97"/>
+      <c r="B60" s="72"/>
+      <c r="C60" s="98"/>
+      <c r="D60" s="77"/>
+      <c r="E60" s="81"/>
       <c r="F60" s="31">
         <v>2</v>
       </c>
@@ -4365,10 +4365,10 @@
     </row>
     <row r="61" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="27"/>
-      <c r="B61" s="67"/>
-      <c r="C61" s="90"/>
-      <c r="D61" s="93"/>
-      <c r="E61" s="97"/>
+      <c r="B61" s="72"/>
+      <c r="C61" s="98"/>
+      <c r="D61" s="77"/>
+      <c r="E61" s="81"/>
       <c r="F61" s="31">
         <v>4</v>
       </c>
@@ -4380,10 +4380,10 @@
     </row>
     <row r="62" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="27"/>
-      <c r="B62" s="67"/>
-      <c r="C62" s="90"/>
-      <c r="D62" s="93"/>
-      <c r="E62" s="97"/>
+      <c r="B62" s="72"/>
+      <c r="C62" s="98"/>
+      <c r="D62" s="77"/>
+      <c r="E62" s="81"/>
       <c r="F62" s="31">
         <v>8</v>
       </c>
@@ -4395,10 +4395,10 @@
     </row>
     <row r="63" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="27"/>
-      <c r="B63" s="68"/>
-      <c r="C63" s="91"/>
-      <c r="D63" s="94"/>
-      <c r="E63" s="98"/>
+      <c r="B63" s="73"/>
+      <c r="C63" s="99"/>
+      <c r="D63" s="78"/>
+      <c r="E63" s="82"/>
       <c r="F63" s="31">
         <v>16</v>
       </c>
@@ -4409,7 +4409,7 @@
       <c r="K63" s="27"/>
     </row>
     <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="66" t="s">
+      <c r="B64" s="71" t="s">
         <v>82</v>
       </c>
       <c r="C64" s="20" t="s">
@@ -4435,14 +4435,14 @@
       <c r="K64" s="15"/>
     </row>
     <row r="65" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="67"/>
-      <c r="C65" s="87" t="s">
+      <c r="B65" s="72"/>
+      <c r="C65" s="95" t="s">
         <v>83</v>
       </c>
-      <c r="D65" s="81" t="s">
+      <c r="D65" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="E65" s="81" t="s">
+      <c r="E65" s="67" t="s">
         <v>100</v>
       </c>
       <c r="F65" s="9">
@@ -4455,10 +4455,10 @@
       <c r="K65" s="15"/>
     </row>
     <row r="66" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="67"/>
-      <c r="C66" s="88"/>
-      <c r="D66" s="82"/>
-      <c r="E66" s="82"/>
+      <c r="B66" s="72"/>
+      <c r="C66" s="96"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="68"/>
       <c r="F66" s="9">
         <v>2</v>
       </c>
@@ -4469,10 +4469,10 @@
       <c r="K66" s="15"/>
     </row>
     <row r="67" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="67"/>
-      <c r="C67" s="88"/>
-      <c r="D67" s="82"/>
-      <c r="E67" s="82"/>
+      <c r="B67" s="72"/>
+      <c r="C67" s="96"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="68"/>
       <c r="F67" s="9">
         <v>4</v>
       </c>
@@ -4483,10 +4483,10 @@
       <c r="K67" s="15"/>
     </row>
     <row r="68" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="67"/>
-      <c r="C68" s="88"/>
-      <c r="D68" s="82"/>
-      <c r="E68" s="82"/>
+      <c r="B68" s="72"/>
+      <c r="C68" s="96"/>
+      <c r="D68" s="68"/>
+      <c r="E68" s="68"/>
       <c r="F68" s="9">
         <v>8</v>
       </c>
@@ -4497,10 +4497,10 @@
       <c r="K68" s="15"/>
     </row>
     <row r="69" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="67"/>
-      <c r="C69" s="88"/>
-      <c r="D69" s="82"/>
-      <c r="E69" s="82"/>
+      <c r="B69" s="72"/>
+      <c r="C69" s="96"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="68"/>
       <c r="F69" s="9">
         <v>16</v>
       </c>
@@ -4511,10 +4511,10 @@
       <c r="K69" s="15"/>
     </row>
     <row r="70" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="67"/>
-      <c r="C70" s="88"/>
-      <c r="D70" s="82"/>
-      <c r="E70" s="83"/>
+      <c r="B70" s="72"/>
+      <c r="C70" s="96"/>
+      <c r="D70" s="68"/>
+      <c r="E70" s="74"/>
       <c r="F70" s="9">
         <v>32</v>
       </c>
@@ -4525,8 +4525,8 @@
       <c r="K70" s="15"/>
     </row>
     <row r="71" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="67"/>
-      <c r="C71" s="88"/>
+      <c r="B71" s="72"/>
+      <c r="C71" s="96"/>
       <c r="D71" s="42"/>
       <c r="E71" s="36" t="s">
         <v>95</v>
@@ -4541,12 +4541,12 @@
       <c r="K71" s="15"/>
     </row>
     <row r="72" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="67"/>
-      <c r="C72" s="88"/>
-      <c r="D72" s="81" t="s">
+      <c r="B72" s="72"/>
+      <c r="C72" s="96"/>
+      <c r="D72" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="E72" s="84" t="s">
+      <c r="E72" s="75" t="s">
         <v>100</v>
       </c>
       <c r="F72" s="9">
@@ -4559,10 +4559,10 @@
       <c r="K72" s="15"/>
     </row>
     <row r="73" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="67"/>
-      <c r="C73" s="88"/>
-      <c r="D73" s="82"/>
-      <c r="E73" s="85"/>
+      <c r="B73" s="72"/>
+      <c r="C73" s="96"/>
+      <c r="D73" s="68"/>
+      <c r="E73" s="69"/>
       <c r="F73" s="9">
         <v>2</v>
       </c>
@@ -4573,10 +4573,10 @@
       <c r="K73" s="16"/>
     </row>
     <row r="74" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="67"/>
-      <c r="C74" s="88"/>
-      <c r="D74" s="82"/>
-      <c r="E74" s="85"/>
+      <c r="B74" s="72"/>
+      <c r="C74" s="96"/>
+      <c r="D74" s="68"/>
+      <c r="E74" s="69"/>
       <c r="F74" s="9">
         <v>4</v>
       </c>
@@ -4585,10 +4585,10 @@
       <c r="I74" s="10"/>
     </row>
     <row r="75" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="67"/>
-      <c r="C75" s="88"/>
-      <c r="D75" s="82"/>
-      <c r="E75" s="85"/>
+      <c r="B75" s="72"/>
+      <c r="C75" s="96"/>
+      <c r="D75" s="68"/>
+      <c r="E75" s="69"/>
       <c r="F75" s="9">
         <v>8</v>
       </c>
@@ -4597,10 +4597,10 @@
       <c r="I75" s="10"/>
     </row>
     <row r="76" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="67"/>
-      <c r="C76" s="89"/>
-      <c r="D76" s="83"/>
-      <c r="E76" s="86"/>
+      <c r="B76" s="72"/>
+      <c r="C76" s="97"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="70"/>
       <c r="F76" s="9">
         <v>16</v>
       </c>
@@ -4609,14 +4609,14 @@
       <c r="I76" s="10"/>
     </row>
     <row r="77" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="67"/>
-      <c r="C77" s="87" t="s">
+      <c r="B77" s="72"/>
+      <c r="C77" s="95" t="s">
         <v>84</v>
       </c>
-      <c r="D77" s="81" t="s">
+      <c r="D77" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="E77" s="81" t="s">
+      <c r="E77" s="67" t="s">
         <v>100</v>
       </c>
       <c r="F77" s="9">
@@ -4629,10 +4629,10 @@
       <c r="K77" s="15"/>
     </row>
     <row r="78" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="67"/>
-      <c r="C78" s="88"/>
-      <c r="D78" s="82"/>
-      <c r="E78" s="82"/>
+      <c r="B78" s="72"/>
+      <c r="C78" s="96"/>
+      <c r="D78" s="68"/>
+      <c r="E78" s="68"/>
       <c r="F78" s="9">
         <v>2</v>
       </c>
@@ -4643,10 +4643,10 @@
       <c r="K78" s="15"/>
     </row>
     <row r="79" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="67"/>
-      <c r="C79" s="88"/>
-      <c r="D79" s="82"/>
-      <c r="E79" s="82"/>
+      <c r="B79" s="72"/>
+      <c r="C79" s="96"/>
+      <c r="D79" s="68"/>
+      <c r="E79" s="68"/>
       <c r="F79" s="9">
         <v>4</v>
       </c>
@@ -4657,10 +4657,10 @@
       <c r="K79" s="15"/>
     </row>
     <row r="80" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="67"/>
-      <c r="C80" s="88"/>
-      <c r="D80" s="82"/>
-      <c r="E80" s="82"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="96"/>
+      <c r="D80" s="68"/>
+      <c r="E80" s="68"/>
       <c r="F80" s="9">
         <v>8</v>
       </c>
@@ -4671,10 +4671,10 @@
       <c r="K80" s="15"/>
     </row>
     <row r="81" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="67"/>
-      <c r="C81" s="88"/>
-      <c r="D81" s="82"/>
-      <c r="E81" s="82"/>
+      <c r="B81" s="72"/>
+      <c r="C81" s="96"/>
+      <c r="D81" s="68"/>
+      <c r="E81" s="68"/>
       <c r="F81" s="9">
         <v>16</v>
       </c>
@@ -4685,10 +4685,10 @@
       <c r="K81" s="15"/>
     </row>
     <row r="82" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="67"/>
-      <c r="C82" s="88"/>
-      <c r="D82" s="82"/>
-      <c r="E82" s="83"/>
+      <c r="B82" s="72"/>
+      <c r="C82" s="96"/>
+      <c r="D82" s="68"/>
+      <c r="E82" s="74"/>
       <c r="F82" s="9">
         <v>32</v>
       </c>
@@ -4699,8 +4699,8 @@
       <c r="K82" s="15"/>
     </row>
     <row r="83" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="67"/>
-      <c r="C83" s="88"/>
+      <c r="B83" s="72"/>
+      <c r="C83" s="96"/>
       <c r="D83" s="42"/>
       <c r="E83" s="36" t="s">
         <v>95</v>
@@ -4715,12 +4715,12 @@
       <c r="K83" s="15"/>
     </row>
     <row r="84" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="67"/>
-      <c r="C84" s="88"/>
-      <c r="D84" s="81" t="s">
+      <c r="B84" s="72"/>
+      <c r="C84" s="96"/>
+      <c r="D84" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="E84" s="84" t="s">
+      <c r="E84" s="75" t="s">
         <v>100</v>
       </c>
       <c r="F84" s="9">
@@ -4733,10 +4733,10 @@
       <c r="K84" s="15"/>
     </row>
     <row r="85" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="67"/>
-      <c r="C85" s="88"/>
-      <c r="D85" s="82"/>
-      <c r="E85" s="85"/>
+      <c r="B85" s="72"/>
+      <c r="C85" s="96"/>
+      <c r="D85" s="68"/>
+      <c r="E85" s="69"/>
       <c r="F85" s="9">
         <v>2</v>
       </c>
@@ -4747,10 +4747,10 @@
       <c r="K85" s="16"/>
     </row>
     <row r="86" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="67"/>
-      <c r="C86" s="88"/>
-      <c r="D86" s="82"/>
-      <c r="E86" s="85"/>
+      <c r="B86" s="72"/>
+      <c r="C86" s="96"/>
+      <c r="D86" s="68"/>
+      <c r="E86" s="69"/>
       <c r="F86" s="9">
         <v>4</v>
       </c>
@@ -4759,10 +4759,10 @@
       <c r="I86" s="10"/>
     </row>
     <row r="87" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="67"/>
-      <c r="C87" s="88"/>
-      <c r="D87" s="82"/>
-      <c r="E87" s="85"/>
+      <c r="B87" s="72"/>
+      <c r="C87" s="96"/>
+      <c r="D87" s="68"/>
+      <c r="E87" s="69"/>
       <c r="F87" s="9">
         <v>8</v>
       </c>
@@ -4771,10 +4771,10 @@
       <c r="I87" s="10"/>
     </row>
     <row r="88" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="68"/>
-      <c r="C88" s="89"/>
-      <c r="D88" s="83"/>
-      <c r="E88" s="86"/>
+      <c r="B88" s="73"/>
+      <c r="C88" s="97"/>
+      <c r="D88" s="74"/>
+      <c r="E88" s="70"/>
       <c r="F88" s="9">
         <v>16</v>
       </c>
@@ -5671,25 +5671,6 @@
     <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="D38:D43"/>
-    <mergeCell ref="E39:E43"/>
-    <mergeCell ref="B4:B63"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="E5:E10"/>
-    <mergeCell ref="E19:E23"/>
-    <mergeCell ref="D5:D17"/>
-    <mergeCell ref="D18:D23"/>
-    <mergeCell ref="D25:D37"/>
-    <mergeCell ref="E25:E30"/>
-    <mergeCell ref="E35:E37"/>
-    <mergeCell ref="D65:D70"/>
-    <mergeCell ref="E65:E70"/>
-    <mergeCell ref="E72:E76"/>
-    <mergeCell ref="D45:D57"/>
-    <mergeCell ref="E45:E50"/>
-    <mergeCell ref="E55:E57"/>
-    <mergeCell ref="D58:D63"/>
-    <mergeCell ref="E59:E63"/>
     <mergeCell ref="B64:B88"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:F3"/>
@@ -5706,6 +5687,25 @@
     <mergeCell ref="D72:D76"/>
     <mergeCell ref="D77:D82"/>
     <mergeCell ref="E77:E82"/>
+    <mergeCell ref="D65:D70"/>
+    <mergeCell ref="E65:E70"/>
+    <mergeCell ref="E72:E76"/>
+    <mergeCell ref="D45:D57"/>
+    <mergeCell ref="E45:E50"/>
+    <mergeCell ref="E55:E57"/>
+    <mergeCell ref="D58:D63"/>
+    <mergeCell ref="E59:E63"/>
+    <mergeCell ref="D38:D43"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="B4:B63"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="E5:E10"/>
+    <mergeCell ref="E19:E23"/>
+    <mergeCell ref="D5:D17"/>
+    <mergeCell ref="D18:D23"/>
+    <mergeCell ref="D25:D37"/>
+    <mergeCell ref="E25:E30"/>
+    <mergeCell ref="E35:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/RCC-Benchmark-Report.xlsx
+++ b/RCC-Benchmark-Report.xlsx
@@ -5,17 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gustavo\OneDrive - The University of Chicago\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uchicagoedu-my.sharepoint.com/personal/grondina_uchicago_edu/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3211D17-C960-4F8E-A29D-0C308682E14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{514111F4-87A6-4BC2-86C3-83E6D938EF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="27510" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Standard Compute" sheetId="1" r:id="rId1"/>
     <sheet name="Scientific Applications" sheetId="2" r:id="rId2"/>
-    <sheet name="Storage" sheetId="3" r:id="rId3"/>
+    <sheet name="Machine Learning" sheetId="5" r:id="rId3"/>
+    <sheet name="Storage" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="121">
   <si>
     <t>Standard Compute Benchmarks</t>
   </si>
@@ -1361,6 +1362,27 @@
   </si>
   <si>
     <t>Values</t>
+  </si>
+  <si>
+    <t>Machine Learning Benchmarks</t>
+  </si>
+  <si>
+    <t>MLPerf</t>
+  </si>
+  <si>
+    <t>GPU Type</t>
+  </si>
+  <si>
+    <t>GPUs per Node</t>
+  </si>
+  <si>
+    <t>Higher Precison</t>
+  </si>
+  <si>
+    <t>Lower Precision</t>
+  </si>
+  <si>
+    <t>Time to Solution (minutes)</t>
   </si>
 </sst>
 </file>
@@ -1692,7 +1714,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1831,21 +1853,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1853,33 +1860,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1918,6 +1898,24 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1933,10 +1931,62 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3457,25 +3507,25 @@
       <c r="K1" s="15"/>
     </row>
     <row r="2" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="85"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="71"/>
       <c r="J2" s="15"/>
       <c r="K2" s="15"/>
     </row>
     <row r="3" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="86"/>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="88"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="74"/>
       <c r="G3" s="3" t="s">
         <v>1</v>
       </c>
@@ -3489,7 +3539,7 @@
       <c r="K3" s="15"/>
     </row>
     <row r="4" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="66" t="s">
         <v>81</v>
       </c>
       <c r="C4" s="20" t="s">
@@ -3515,14 +3565,14 @@
       <c r="K4" s="15"/>
     </row>
     <row r="5" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="72"/>
-      <c r="C5" s="95" t="s">
+      <c r="B5" s="67"/>
+      <c r="C5" s="87" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="67" t="s">
+      <c r="D5" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="81" t="s">
         <v>96</v>
       </c>
       <c r="F5" s="9">
@@ -3535,10 +3585,10 @@
       <c r="K5" s="15"/>
     </row>
     <row r="6" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="72"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="88"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
       <c r="F6" s="9">
         <v>2</v>
       </c>
@@ -3549,10 +3599,10 @@
       <c r="K6" s="15"/>
     </row>
     <row r="7" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="72"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="88"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
       <c r="F7" s="9">
         <v>4</v>
       </c>
@@ -3563,10 +3613,10 @@
       <c r="K7" s="15"/>
     </row>
     <row r="8" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="72"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
       <c r="F8" s="9">
         <v>8</v>
       </c>
@@ -3577,10 +3627,10 @@
       <c r="K8" s="15"/>
     </row>
     <row r="9" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="72"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="88"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
       <c r="F9" s="9">
         <v>16</v>
       </c>
@@ -3591,10 +3641,10 @@
       <c r="K9" s="15"/>
     </row>
     <row r="10" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="72"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="74"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="83"/>
       <c r="F10" s="9">
         <v>32</v>
       </c>
@@ -3605,9 +3655,9 @@
       <c r="K10" s="15"/>
     </row>
     <row r="11" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="72"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="68"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="82"/>
       <c r="E11" s="26" t="s">
         <v>97</v>
       </c>
@@ -3623,10 +3673,10 @@
       <c r="K11" s="15"/>
     </row>
     <row r="12" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="72"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="68"/>
-      <c r="E12" s="89" t="s">
+      <c r="B12" s="67"/>
+      <c r="C12" s="88"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="75" t="s">
         <v>93</v>
       </c>
       <c r="F12" s="20">
@@ -3639,10 +3689,10 @@
       <c r="K12" s="15"/>
     </row>
     <row r="13" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="72"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="90"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="76"/>
       <c r="F13" s="20">
         <v>2</v>
       </c>
@@ -3653,10 +3703,10 @@
       <c r="K13" s="15"/>
     </row>
     <row r="14" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="72"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="91"/>
+      <c r="B14" s="67"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="77"/>
       <c r="F14" s="20">
         <v>4</v>
       </c>
@@ -3667,10 +3717,10 @@
       <c r="K14" s="15"/>
     </row>
     <row r="15" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="72"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="67" t="s">
+      <c r="B15" s="67"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="81" t="s">
         <v>92</v>
       </c>
       <c r="F15" s="20">
@@ -3682,10 +3732,10 @@
       <c r="K15" s="15"/>
     </row>
     <row r="16" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="72"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
       <c r="F16" s="20">
         <v>2</v>
       </c>
@@ -3695,10 +3745,10 @@
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="72"/>
-      <c r="C17" s="96"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="88"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
       <c r="F17" s="20">
         <v>4</v>
       </c>
@@ -3708,9 +3758,9 @@
       <c r="K17" s="15"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="72"/>
-      <c r="C18" s="96"/>
-      <c r="D18" s="66" t="s">
+      <c r="B18" s="67"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="99" t="s">
         <v>90</v>
       </c>
       <c r="E18" s="45"/>
@@ -3724,10 +3774,10 @@
       <c r="K18" s="15"/>
     </row>
     <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="72"/>
-      <c r="C19" s="96"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="69" t="s">
+      <c r="B19" s="67"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="85" t="s">
         <v>96</v>
       </c>
       <c r="F19" s="9">
@@ -3740,10 +3790,10 @@
       <c r="K19" s="15"/>
     </row>
     <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="72"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="69"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="85"/>
       <c r="F20" s="9">
         <v>2</v>
       </c>
@@ -3754,10 +3804,10 @@
       <c r="K20" s="16"/>
     </row>
     <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="72"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="69"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="88"/>
+      <c r="D21" s="82"/>
+      <c r="E21" s="85"/>
       <c r="F21" s="9">
         <v>4</v>
       </c>
@@ -3766,10 +3816,10 @@
       <c r="I21" s="10"/>
     </row>
     <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="72"/>
-      <c r="C22" s="96"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="69"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="85"/>
       <c r="F22" s="9">
         <v>8</v>
       </c>
@@ -3778,10 +3828,10 @@
       <c r="I22" s="10"/>
     </row>
     <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="72"/>
-      <c r="C23" s="97"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="70"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="89"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="86"/>
       <c r="F23" s="9">
         <v>16</v>
       </c>
@@ -3790,7 +3840,7 @@
       <c r="I23" s="10"/>
     </row>
     <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="72"/>
+      <c r="B24" s="67"/>
       <c r="C24" s="58" t="s">
         <v>98</v>
       </c>
@@ -3810,12 +3860,12 @@
       <c r="K24" s="15"/>
     </row>
     <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="72"/>
-      <c r="C25" s="98"/>
-      <c r="D25" s="67" t="s">
+      <c r="B25" s="67"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="67" t="s">
+      <c r="E25" s="81" t="s">
         <v>96</v>
       </c>
       <c r="F25" s="9">
@@ -3828,10 +3878,10 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="72"/>
-      <c r="C26" s="98"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="68"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="90"/>
+      <c r="D26" s="82"/>
+      <c r="E26" s="82"/>
       <c r="F26" s="9">
         <v>2</v>
       </c>
@@ -3842,10 +3892,10 @@
       <c r="K26" s="15"/>
     </row>
     <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="72"/>
-      <c r="C27" s="98"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="68"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="90"/>
+      <c r="D27" s="82"/>
+      <c r="E27" s="82"/>
       <c r="F27" s="9">
         <v>4</v>
       </c>
@@ -3856,10 +3906,10 @@
       <c r="K27" s="15"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="72"/>
-      <c r="C28" s="98"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="68"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="82"/>
+      <c r="E28" s="82"/>
       <c r="F28" s="9">
         <v>8</v>
       </c>
@@ -3870,10 +3920,10 @@
       <c r="K28" s="15"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="72"/>
-      <c r="C29" s="98"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="68"/>
+      <c r="B29" s="67"/>
+      <c r="C29" s="90"/>
+      <c r="D29" s="82"/>
+      <c r="E29" s="82"/>
       <c r="F29" s="9">
         <v>16</v>
       </c>
@@ -3884,10 +3934,10 @@
       <c r="K29" s="15"/>
     </row>
     <row r="30" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="72"/>
-      <c r="C30" s="98"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="74"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="90"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="83"/>
       <c r="F30" s="9">
         <v>32</v>
       </c>
@@ -3898,9 +3948,9 @@
       <c r="K30" s="15"/>
     </row>
     <row r="31" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="72"/>
-      <c r="C31" s="98"/>
-      <c r="D31" s="68"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="82"/>
       <c r="E31" s="26" t="s">
         <v>97</v>
       </c>
@@ -3916,10 +3966,10 @@
       <c r="K31" s="15"/>
     </row>
     <row r="32" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="72"/>
-      <c r="C32" s="98"/>
-      <c r="D32" s="68"/>
-      <c r="E32" s="89" t="s">
+      <c r="B32" s="67"/>
+      <c r="C32" s="90"/>
+      <c r="D32" s="82"/>
+      <c r="E32" s="75" t="s">
         <v>93</v>
       </c>
       <c r="F32" s="20">
@@ -3932,10 +3982,10 @@
       <c r="K32" s="15"/>
     </row>
     <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="72"/>
-      <c r="C33" s="98"/>
-      <c r="D33" s="68"/>
-      <c r="E33" s="90"/>
+      <c r="B33" s="67"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="76"/>
       <c r="F33" s="20">
         <v>2</v>
       </c>
@@ -3946,10 +3996,10 @@
       <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="72"/>
-      <c r="C34" s="98"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="91"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="77"/>
       <c r="F34" s="20">
         <v>4</v>
       </c>
@@ -3960,10 +4010,10 @@
       <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="72"/>
-      <c r="C35" s="98"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="67" t="s">
+      <c r="B35" s="67"/>
+      <c r="C35" s="90"/>
+      <c r="D35" s="82"/>
+      <c r="E35" s="81" t="s">
         <v>92</v>
       </c>
       <c r="F35" s="20">
@@ -3976,10 +4026,10 @@
       <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="72"/>
-      <c r="C36" s="98"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="82"/>
+      <c r="E36" s="82"/>
       <c r="F36" s="20">
         <v>2</v>
       </c>
@@ -3990,10 +4040,10 @@
       <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="72"/>
-      <c r="C37" s="98"/>
-      <c r="D37" s="74"/>
-      <c r="E37" s="74"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="90"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
       <c r="F37" s="20">
         <v>4</v>
       </c>
@@ -4004,9 +4054,9 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="72"/>
-      <c r="C38" s="98"/>
-      <c r="D38" s="66" t="s">
+      <c r="B38" s="67"/>
+      <c r="C38" s="90"/>
+      <c r="D38" s="99" t="s">
         <v>90</v>
       </c>
       <c r="F38" s="21" t="s">
@@ -4019,10 +4069,10 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="72"/>
-      <c r="C39" s="98"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="69" t="s">
+      <c r="B39" s="67"/>
+      <c r="C39" s="90"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="85" t="s">
         <v>96</v>
       </c>
       <c r="F39" s="9">
@@ -4035,10 +4085,10 @@
       <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="72"/>
-      <c r="C40" s="98"/>
-      <c r="D40" s="68"/>
-      <c r="E40" s="69"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="85"/>
       <c r="F40" s="9">
         <v>2</v>
       </c>
@@ -4049,10 +4099,10 @@
       <c r="K40" s="16"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="72"/>
-      <c r="C41" s="98"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="69"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="85"/>
       <c r="F41" s="9">
         <v>4</v>
       </c>
@@ -4061,10 +4111,10 @@
       <c r="I41" s="10"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="72"/>
-      <c r="C42" s="98"/>
-      <c r="D42" s="68"/>
-      <c r="E42" s="69"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="90"/>
+      <c r="D42" s="82"/>
+      <c r="E42" s="85"/>
       <c r="F42" s="9">
         <v>8</v>
       </c>
@@ -4073,10 +4123,10 @@
       <c r="I42" s="10"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="72"/>
-      <c r="C43" s="99"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="70"/>
+      <c r="B43" s="67"/>
+      <c r="C43" s="91"/>
+      <c r="D43" s="82"/>
+      <c r="E43" s="86"/>
       <c r="F43" s="9">
         <v>16</v>
       </c>
@@ -4086,7 +4136,7 @@
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
-      <c r="B44" s="72"/>
+      <c r="B44" s="67"/>
       <c r="C44" s="58" t="s">
         <v>99</v>
       </c>
@@ -4107,12 +4157,12 @@
     </row>
     <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="27"/>
-      <c r="B45" s="72"/>
-      <c r="C45" s="98"/>
-      <c r="D45" s="76" t="s">
+      <c r="B45" s="67"/>
+      <c r="C45" s="90"/>
+      <c r="D45" s="92" t="s">
         <v>87</v>
       </c>
-      <c r="E45" s="76" t="s">
+      <c r="E45" s="92" t="s">
         <v>96</v>
       </c>
       <c r="F45" s="31">
@@ -4126,10 +4176,10 @@
     </row>
     <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
-      <c r="B46" s="72"/>
-      <c r="C46" s="98"/>
-      <c r="D46" s="77"/>
-      <c r="E46" s="77"/>
+      <c r="B46" s="67"/>
+      <c r="C46" s="90"/>
+      <c r="D46" s="93"/>
+      <c r="E46" s="93"/>
       <c r="F46" s="31">
         <v>2</v>
       </c>
@@ -4141,10 +4191,10 @@
     </row>
     <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="27"/>
-      <c r="B47" s="72"/>
-      <c r="C47" s="98"/>
-      <c r="D47" s="77"/>
-      <c r="E47" s="77"/>
+      <c r="B47" s="67"/>
+      <c r="C47" s="90"/>
+      <c r="D47" s="93"/>
+      <c r="E47" s="93"/>
       <c r="F47" s="31">
         <v>4</v>
       </c>
@@ -4156,10 +4206,10 @@
     </row>
     <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="27"/>
-      <c r="B48" s="72"/>
-      <c r="C48" s="98"/>
-      <c r="D48" s="77"/>
-      <c r="E48" s="77"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="90"/>
+      <c r="D48" s="93"/>
+      <c r="E48" s="93"/>
       <c r="F48" s="31">
         <v>8</v>
       </c>
@@ -4171,10 +4221,10 @@
     </row>
     <row r="49" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="27"/>
-      <c r="B49" s="72"/>
-      <c r="C49" s="98"/>
-      <c r="D49" s="77"/>
-      <c r="E49" s="77"/>
+      <c r="B49" s="67"/>
+      <c r="C49" s="90"/>
+      <c r="D49" s="93"/>
+      <c r="E49" s="93"/>
       <c r="F49" s="31">
         <v>16</v>
       </c>
@@ -4186,10 +4236,10 @@
     </row>
     <row r="50" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="27"/>
-      <c r="B50" s="72"/>
-      <c r="C50" s="98"/>
-      <c r="D50" s="77"/>
-      <c r="E50" s="78"/>
+      <c r="B50" s="67"/>
+      <c r="C50" s="90"/>
+      <c r="D50" s="93"/>
+      <c r="E50" s="94"/>
       <c r="F50" s="31">
         <v>32</v>
       </c>
@@ -4201,9 +4251,9 @@
     </row>
     <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="27"/>
-      <c r="B51" s="72"/>
-      <c r="C51" s="98"/>
-      <c r="D51" s="77"/>
+      <c r="B51" s="67"/>
+      <c r="C51" s="90"/>
+      <c r="D51" s="93"/>
       <c r="E51" s="34" t="s">
         <v>97</v>
       </c>
@@ -4220,10 +4270,10 @@
     </row>
     <row r="52" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="27"/>
-      <c r="B52" s="72"/>
-      <c r="C52" s="98"/>
-      <c r="D52" s="77"/>
-      <c r="E52" s="92" t="s">
+      <c r="B52" s="67"/>
+      <c r="C52" s="90"/>
+      <c r="D52" s="93"/>
+      <c r="E52" s="78" t="s">
         <v>93</v>
       </c>
       <c r="F52" s="31">
@@ -4237,10 +4287,10 @@
     </row>
     <row r="53" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="27"/>
-      <c r="B53" s="72"/>
-      <c r="C53" s="98"/>
-      <c r="D53" s="77"/>
-      <c r="E53" s="93"/>
+      <c r="B53" s="67"/>
+      <c r="C53" s="90"/>
+      <c r="D53" s="93"/>
+      <c r="E53" s="79"/>
       <c r="F53" s="31">
         <v>2</v>
       </c>
@@ -4252,10 +4302,10 @@
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="27"/>
-      <c r="B54" s="72"/>
-      <c r="C54" s="98"/>
-      <c r="D54" s="77"/>
-      <c r="E54" s="94"/>
+      <c r="B54" s="67"/>
+      <c r="C54" s="90"/>
+      <c r="D54" s="93"/>
+      <c r="E54" s="80"/>
       <c r="F54" s="31">
         <v>4</v>
       </c>
@@ -4267,10 +4317,10 @@
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="27"/>
-      <c r="B55" s="72"/>
-      <c r="C55" s="98"/>
-      <c r="D55" s="77"/>
-      <c r="E55" s="76" t="s">
+      <c r="B55" s="67"/>
+      <c r="C55" s="90"/>
+      <c r="D55" s="93"/>
+      <c r="E55" s="92" t="s">
         <v>92</v>
       </c>
       <c r="F55" s="31">
@@ -4284,10 +4334,10 @@
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="27"/>
-      <c r="B56" s="72"/>
-      <c r="C56" s="98"/>
-      <c r="D56" s="77"/>
-      <c r="E56" s="77"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="90"/>
+      <c r="D56" s="93"/>
+      <c r="E56" s="93"/>
       <c r="F56" s="31">
         <v>2</v>
       </c>
@@ -4299,10 +4349,10 @@
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="27"/>
-      <c r="B57" s="72"/>
-      <c r="C57" s="98"/>
-      <c r="D57" s="78"/>
-      <c r="E57" s="78"/>
+      <c r="B57" s="67"/>
+      <c r="C57" s="90"/>
+      <c r="D57" s="94"/>
+      <c r="E57" s="94"/>
       <c r="F57" s="31">
         <v>4</v>
       </c>
@@ -4314,9 +4364,9 @@
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="27"/>
-      <c r="B58" s="72"/>
-      <c r="C58" s="98"/>
-      <c r="D58" s="79" t="s">
+      <c r="B58" s="67"/>
+      <c r="C58" s="90"/>
+      <c r="D58" s="95" t="s">
         <v>90</v>
       </c>
       <c r="E58" s="36" t="s">
@@ -4333,10 +4383,10 @@
     </row>
     <row r="59" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="27"/>
-      <c r="B59" s="72"/>
-      <c r="C59" s="98"/>
-      <c r="D59" s="76"/>
-      <c r="E59" s="80" t="s">
+      <c r="B59" s="67"/>
+      <c r="C59" s="90"/>
+      <c r="D59" s="92"/>
+      <c r="E59" s="96" t="s">
         <v>96</v>
       </c>
       <c r="F59" s="31">
@@ -4350,10 +4400,10 @@
     </row>
     <row r="60" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="27"/>
-      <c r="B60" s="72"/>
-      <c r="C60" s="98"/>
-      <c r="D60" s="77"/>
-      <c r="E60" s="81"/>
+      <c r="B60" s="67"/>
+      <c r="C60" s="90"/>
+      <c r="D60" s="93"/>
+      <c r="E60" s="97"/>
       <c r="F60" s="31">
         <v>2</v>
       </c>
@@ -4365,10 +4415,10 @@
     </row>
     <row r="61" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="27"/>
-      <c r="B61" s="72"/>
-      <c r="C61" s="98"/>
-      <c r="D61" s="77"/>
-      <c r="E61" s="81"/>
+      <c r="B61" s="67"/>
+      <c r="C61" s="90"/>
+      <c r="D61" s="93"/>
+      <c r="E61" s="97"/>
       <c r="F61" s="31">
         <v>4</v>
       </c>
@@ -4380,10 +4430,10 @@
     </row>
     <row r="62" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="27"/>
-      <c r="B62" s="72"/>
-      <c r="C62" s="98"/>
-      <c r="D62" s="77"/>
-      <c r="E62" s="81"/>
+      <c r="B62" s="67"/>
+      <c r="C62" s="90"/>
+      <c r="D62" s="93"/>
+      <c r="E62" s="97"/>
       <c r="F62" s="31">
         <v>8</v>
       </c>
@@ -4395,10 +4445,10 @@
     </row>
     <row r="63" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="27"/>
-      <c r="B63" s="73"/>
-      <c r="C63" s="99"/>
-      <c r="D63" s="78"/>
-      <c r="E63" s="82"/>
+      <c r="B63" s="68"/>
+      <c r="C63" s="91"/>
+      <c r="D63" s="94"/>
+      <c r="E63" s="98"/>
       <c r="F63" s="31">
         <v>16</v>
       </c>
@@ -4409,7 +4459,7 @@
       <c r="K63" s="27"/>
     </row>
     <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="71" t="s">
+      <c r="B64" s="66" t="s">
         <v>82</v>
       </c>
       <c r="C64" s="20" t="s">
@@ -4435,14 +4485,14 @@
       <c r="K64" s="15"/>
     </row>
     <row r="65" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="72"/>
-      <c r="C65" s="95" t="s">
+      <c r="B65" s="67"/>
+      <c r="C65" s="87" t="s">
         <v>83</v>
       </c>
-      <c r="D65" s="67" t="s">
+      <c r="D65" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="E65" s="67" t="s">
+      <c r="E65" s="81" t="s">
         <v>100</v>
       </c>
       <c r="F65" s="9">
@@ -4455,10 +4505,10 @@
       <c r="K65" s="15"/>
     </row>
     <row r="66" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="72"/>
-      <c r="C66" s="96"/>
-      <c r="D66" s="68"/>
-      <c r="E66" s="68"/>
+      <c r="B66" s="67"/>
+      <c r="C66" s="88"/>
+      <c r="D66" s="82"/>
+      <c r="E66" s="82"/>
       <c r="F66" s="9">
         <v>2</v>
       </c>
@@ -4469,10 +4519,10 @@
       <c r="K66" s="15"/>
     </row>
     <row r="67" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="72"/>
-      <c r="C67" s="96"/>
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
+      <c r="B67" s="67"/>
+      <c r="C67" s="88"/>
+      <c r="D67" s="82"/>
+      <c r="E67" s="82"/>
       <c r="F67" s="9">
         <v>4</v>
       </c>
@@ -4483,10 +4533,10 @@
       <c r="K67" s="15"/>
     </row>
     <row r="68" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="72"/>
-      <c r="C68" s="96"/>
-      <c r="D68" s="68"/>
-      <c r="E68" s="68"/>
+      <c r="B68" s="67"/>
+      <c r="C68" s="88"/>
+      <c r="D68" s="82"/>
+      <c r="E68" s="82"/>
       <c r="F68" s="9">
         <v>8</v>
       </c>
@@ -4497,10 +4547,10 @@
       <c r="K68" s="15"/>
     </row>
     <row r="69" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="72"/>
-      <c r="C69" s="96"/>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
+      <c r="B69" s="67"/>
+      <c r="C69" s="88"/>
+      <c r="D69" s="82"/>
+      <c r="E69" s="82"/>
       <c r="F69" s="9">
         <v>16</v>
       </c>
@@ -4511,10 +4561,10 @@
       <c r="K69" s="15"/>
     </row>
     <row r="70" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="72"/>
-      <c r="C70" s="96"/>
-      <c r="D70" s="68"/>
-      <c r="E70" s="74"/>
+      <c r="B70" s="67"/>
+      <c r="C70" s="88"/>
+      <c r="D70" s="82"/>
+      <c r="E70" s="83"/>
       <c r="F70" s="9">
         <v>32</v>
       </c>
@@ -4525,8 +4575,8 @@
       <c r="K70" s="15"/>
     </row>
     <row r="71" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="72"/>
-      <c r="C71" s="96"/>
+      <c r="B71" s="67"/>
+      <c r="C71" s="88"/>
       <c r="D71" s="42"/>
       <c r="E71" s="36" t="s">
         <v>95</v>
@@ -4541,12 +4591,12 @@
       <c r="K71" s="15"/>
     </row>
     <row r="72" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="72"/>
-      <c r="C72" s="96"/>
-      <c r="D72" s="67" t="s">
+      <c r="B72" s="67"/>
+      <c r="C72" s="88"/>
+      <c r="D72" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="E72" s="75" t="s">
+      <c r="E72" s="84" t="s">
         <v>100</v>
       </c>
       <c r="F72" s="9">
@@ -4559,10 +4609,10 @@
       <c r="K72" s="15"/>
     </row>
     <row r="73" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="72"/>
-      <c r="C73" s="96"/>
-      <c r="D73" s="68"/>
-      <c r="E73" s="69"/>
+      <c r="B73" s="67"/>
+      <c r="C73" s="88"/>
+      <c r="D73" s="82"/>
+      <c r="E73" s="85"/>
       <c r="F73" s="9">
         <v>2</v>
       </c>
@@ -4573,10 +4623,10 @@
       <c r="K73" s="16"/>
     </row>
     <row r="74" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="72"/>
-      <c r="C74" s="96"/>
-      <c r="D74" s="68"/>
-      <c r="E74" s="69"/>
+      <c r="B74" s="67"/>
+      <c r="C74" s="88"/>
+      <c r="D74" s="82"/>
+      <c r="E74" s="85"/>
       <c r="F74" s="9">
         <v>4</v>
       </c>
@@ -4585,10 +4635,10 @@
       <c r="I74" s="10"/>
     </row>
     <row r="75" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="72"/>
-      <c r="C75" s="96"/>
-      <c r="D75" s="68"/>
-      <c r="E75" s="69"/>
+      <c r="B75" s="67"/>
+      <c r="C75" s="88"/>
+      <c r="D75" s="82"/>
+      <c r="E75" s="85"/>
       <c r="F75" s="9">
         <v>8</v>
       </c>
@@ -4597,10 +4647,10 @@
       <c r="I75" s="10"/>
     </row>
     <row r="76" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="72"/>
-      <c r="C76" s="97"/>
-      <c r="D76" s="74"/>
-      <c r="E76" s="70"/>
+      <c r="B76" s="67"/>
+      <c r="C76" s="89"/>
+      <c r="D76" s="83"/>
+      <c r="E76" s="86"/>
       <c r="F76" s="9">
         <v>16</v>
       </c>
@@ -4609,14 +4659,14 @@
       <c r="I76" s="10"/>
     </row>
     <row r="77" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="72"/>
-      <c r="C77" s="95" t="s">
+      <c r="B77" s="67"/>
+      <c r="C77" s="87" t="s">
         <v>84</v>
       </c>
-      <c r="D77" s="67" t="s">
+      <c r="D77" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="E77" s="67" t="s">
+      <c r="E77" s="81" t="s">
         <v>100</v>
       </c>
       <c r="F77" s="9">
@@ -4629,10 +4679,10 @@
       <c r="K77" s="15"/>
     </row>
     <row r="78" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="72"/>
-      <c r="C78" s="96"/>
-      <c r="D78" s="68"/>
-      <c r="E78" s="68"/>
+      <c r="B78" s="67"/>
+      <c r="C78" s="88"/>
+      <c r="D78" s="82"/>
+      <c r="E78" s="82"/>
       <c r="F78" s="9">
         <v>2</v>
       </c>
@@ -4643,10 +4693,10 @@
       <c r="K78" s="15"/>
     </row>
     <row r="79" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="72"/>
-      <c r="C79" s="96"/>
-      <c r="D79" s="68"/>
-      <c r="E79" s="68"/>
+      <c r="B79" s="67"/>
+      <c r="C79" s="88"/>
+      <c r="D79" s="82"/>
+      <c r="E79" s="82"/>
       <c r="F79" s="9">
         <v>4</v>
       </c>
@@ -4657,10 +4707,10 @@
       <c r="K79" s="15"/>
     </row>
     <row r="80" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="72"/>
-      <c r="C80" s="96"/>
-      <c r="D80" s="68"/>
-      <c r="E80" s="68"/>
+      <c r="B80" s="67"/>
+      <c r="C80" s="88"/>
+      <c r="D80" s="82"/>
+      <c r="E80" s="82"/>
       <c r="F80" s="9">
         <v>8</v>
       </c>
@@ -4671,10 +4721,10 @@
       <c r="K80" s="15"/>
     </row>
     <row r="81" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="72"/>
-      <c r="C81" s="96"/>
-      <c r="D81" s="68"/>
-      <c r="E81" s="68"/>
+      <c r="B81" s="67"/>
+      <c r="C81" s="88"/>
+      <c r="D81" s="82"/>
+      <c r="E81" s="82"/>
       <c r="F81" s="9">
         <v>16</v>
       </c>
@@ -4685,10 +4735,10 @@
       <c r="K81" s="15"/>
     </row>
     <row r="82" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="72"/>
-      <c r="C82" s="96"/>
-      <c r="D82" s="68"/>
-      <c r="E82" s="74"/>
+      <c r="B82" s="67"/>
+      <c r="C82" s="88"/>
+      <c r="D82" s="82"/>
+      <c r="E82" s="83"/>
       <c r="F82" s="9">
         <v>32</v>
       </c>
@@ -4699,8 +4749,8 @@
       <c r="K82" s="15"/>
     </row>
     <row r="83" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="72"/>
-      <c r="C83" s="96"/>
+      <c r="B83" s="67"/>
+      <c r="C83" s="88"/>
       <c r="D83" s="42"/>
       <c r="E83" s="36" t="s">
         <v>95</v>
@@ -4715,12 +4765,12 @@
       <c r="K83" s="15"/>
     </row>
     <row r="84" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="72"/>
-      <c r="C84" s="96"/>
-      <c r="D84" s="67" t="s">
+      <c r="B84" s="67"/>
+      <c r="C84" s="88"/>
+      <c r="D84" s="81" t="s">
         <v>90</v>
       </c>
-      <c r="E84" s="75" t="s">
+      <c r="E84" s="84" t="s">
         <v>100</v>
       </c>
       <c r="F84" s="9">
@@ -4733,10 +4783,10 @@
       <c r="K84" s="15"/>
     </row>
     <row r="85" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="72"/>
-      <c r="C85" s="96"/>
-      <c r="D85" s="68"/>
-      <c r="E85" s="69"/>
+      <c r="B85" s="67"/>
+      <c r="C85" s="88"/>
+      <c r="D85" s="82"/>
+      <c r="E85" s="85"/>
       <c r="F85" s="9">
         <v>2</v>
       </c>
@@ -4747,10 +4797,10 @@
       <c r="K85" s="16"/>
     </row>
     <row r="86" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="72"/>
-      <c r="C86" s="96"/>
-      <c r="D86" s="68"/>
-      <c r="E86" s="69"/>
+      <c r="B86" s="67"/>
+      <c r="C86" s="88"/>
+      <c r="D86" s="82"/>
+      <c r="E86" s="85"/>
       <c r="F86" s="9">
         <v>4</v>
       </c>
@@ -4759,10 +4809,10 @@
       <c r="I86" s="10"/>
     </row>
     <row r="87" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="72"/>
-      <c r="C87" s="96"/>
-      <c r="D87" s="68"/>
-      <c r="E87" s="69"/>
+      <c r="B87" s="67"/>
+      <c r="C87" s="88"/>
+      <c r="D87" s="82"/>
+      <c r="E87" s="85"/>
       <c r="F87" s="9">
         <v>8</v>
       </c>
@@ -4771,10 +4821,10 @@
       <c r="I87" s="10"/>
     </row>
     <row r="88" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="73"/>
-      <c r="C88" s="97"/>
-      <c r="D88" s="74"/>
-      <c r="E88" s="70"/>
+      <c r="B88" s="68"/>
+      <c r="C88" s="89"/>
+      <c r="D88" s="83"/>
+      <c r="E88" s="86"/>
       <c r="F88" s="9">
         <v>16</v>
       </c>
@@ -5671,6 +5721,25 @@
     <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="D38:D43"/>
+    <mergeCell ref="E39:E43"/>
+    <mergeCell ref="B4:B63"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="E5:E10"/>
+    <mergeCell ref="E19:E23"/>
+    <mergeCell ref="D5:D17"/>
+    <mergeCell ref="D18:D23"/>
+    <mergeCell ref="D25:D37"/>
+    <mergeCell ref="E25:E30"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="D65:D70"/>
+    <mergeCell ref="E65:E70"/>
+    <mergeCell ref="E72:E76"/>
+    <mergeCell ref="D45:D57"/>
+    <mergeCell ref="E45:E50"/>
+    <mergeCell ref="E55:E57"/>
+    <mergeCell ref="D58:D63"/>
+    <mergeCell ref="E59:E63"/>
     <mergeCell ref="B64:B88"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:F3"/>
@@ -5687,31 +5756,1229 @@
     <mergeCell ref="D72:D76"/>
     <mergeCell ref="D77:D82"/>
     <mergeCell ref="E77:E82"/>
-    <mergeCell ref="D65:D70"/>
-    <mergeCell ref="E65:E70"/>
-    <mergeCell ref="E72:E76"/>
-    <mergeCell ref="D45:D57"/>
-    <mergeCell ref="E45:E50"/>
-    <mergeCell ref="E55:E57"/>
-    <mergeCell ref="D58:D63"/>
-    <mergeCell ref="E59:E63"/>
-    <mergeCell ref="D38:D43"/>
-    <mergeCell ref="E39:E43"/>
-    <mergeCell ref="B4:B63"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="E5:E10"/>
-    <mergeCell ref="E19:E23"/>
-    <mergeCell ref="D5:D17"/>
-    <mergeCell ref="D18:D23"/>
-    <mergeCell ref="D25:D37"/>
-    <mergeCell ref="E25:E30"/>
-    <mergeCell ref="E35:E37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC70B3FB-8804-4F30-97CB-9BF4B32A2AAA}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="B1:H982"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4.140625" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" customWidth="1"/>
+    <col min="6" max="6" width="36.28515625" customWidth="1"/>
+    <col min="7" max="7" width="2.140625" customWidth="1"/>
+    <col min="8" max="8" width="31.5703125" customWidth="1"/>
+    <col min="9" max="26" width="14.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="103" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="103"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+    </row>
+    <row r="3" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="105"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="106" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="107"/>
+      <c r="H3" s="106" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="64" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="112" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="108" t="s">
+        <v>117</v>
+      </c>
+      <c r="F4" s="108" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="107"/>
+      <c r="H4" s="108" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="64"/>
+      <c r="C5" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="109">
+        <v>2</v>
+      </c>
+      <c r="E5" s="109">
+        <v>4</v>
+      </c>
+      <c r="F5" s="110"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="110"/>
+    </row>
+    <row r="6" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="109">
+        <v>4</v>
+      </c>
+      <c r="E6" s="109">
+        <v>4</v>
+      </c>
+      <c r="F6" s="110"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="110"/>
+    </row>
+    <row r="7" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="109">
+        <v>8</v>
+      </c>
+      <c r="E7" s="109">
+        <v>4</v>
+      </c>
+      <c r="F7" s="110"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="110"/>
+    </row>
+    <row r="8" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="109"/>
+      <c r="E8" s="109"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="107"/>
+      <c r="H8" s="110"/>
+    </row>
+    <row r="9" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="64"/>
+      <c r="C9" s="112" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="108" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9" s="108" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9" s="107"/>
+      <c r="H9" s="108" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="64"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="108">
+        <v>2</v>
+      </c>
+      <c r="E10" s="108">
+        <v>4</v>
+      </c>
+      <c r="F10" s="110"/>
+      <c r="G10" s="107"/>
+      <c r="H10" s="110"/>
+    </row>
+    <row r="11" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="64"/>
+      <c r="C11" s="111" t="s">
+        <v>119</v>
+      </c>
+      <c r="D11" s="109">
+        <v>4</v>
+      </c>
+      <c r="E11" s="109">
+        <v>4</v>
+      </c>
+      <c r="F11" s="110"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="110"/>
+    </row>
+    <row r="12" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="64"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="109">
+        <v>8</v>
+      </c>
+      <c r="E12" s="109">
+        <v>4</v>
+      </c>
+      <c r="F12" s="110"/>
+      <c r="G12" s="107"/>
+      <c r="H12" s="110"/>
+    </row>
+    <row r="13" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="64"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="109"/>
+      <c r="E13" s="109"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="110"/>
+    </row>
+    <row r="14" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="64"/>
+      <c r="C14" s="112" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="108" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="108" t="s">
+        <v>117</v>
+      </c>
+      <c r="F14" s="108" t="s">
+        <v>120</v>
+      </c>
+      <c r="G14" s="107"/>
+      <c r="H14" s="108" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="64"/>
+      <c r="C15" s="111" t="s">
+        <v>119</v>
+      </c>
+      <c r="D15" s="108">
+        <v>4</v>
+      </c>
+      <c r="E15" s="108">
+        <v>8</v>
+      </c>
+      <c r="F15" s="110"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="110"/>
+    </row>
+    <row r="16" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="64"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="113">
+        <v>8</v>
+      </c>
+      <c r="E16" s="113">
+        <v>8</v>
+      </c>
+      <c r="F16" s="110"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="110"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="B4:B16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>

--- a/RCC-Benchmark-Report.xlsx
+++ b/RCC-Benchmark-Report.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uchicagoedu-my.sharepoint.com/personal/grondina_uchicago_edu/Documents/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gustavo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{514111F4-87A6-4BC2-86C3-83E6D938EF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEF27011-A2E6-4F62-AB9A-27839C7351DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="27510" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2325" yWindow="990" windowWidth="32505" windowHeight="19275" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Standard Compute" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="117">
   <si>
     <t>Standard Compute Benchmarks</t>
   </si>
@@ -1266,15 +1266,6 @@
     <t>LAMMPS</t>
   </si>
   <si>
-    <t>MP-GADGET</t>
-  </si>
-  <si>
-    <t>dm-only</t>
-  </si>
-  <si>
-    <t>neutrinos</t>
-  </si>
-  <si>
     <t>Benchmark</t>
   </si>
   <si>
@@ -1318,12 +1309,6 @@
   </si>
   <si>
     <t>in.rhodo.scaled</t>
-  </si>
-  <si>
-    <t>MPI + OpenMP</t>
-  </si>
-  <si>
-    <t>steps/s</t>
   </si>
   <si>
     <t>Scientific Applications Benchmark</t>
@@ -1376,13 +1361,16 @@
     <t>GPUs per Node</t>
   </si>
   <si>
-    <t>Higher Precison</t>
-  </si>
-  <si>
     <t>Lower Precision</t>
   </si>
   <si>
     <t>Time to Solution (minutes)</t>
+  </si>
+  <si>
+    <t>Time to complete (s)</t>
+  </si>
+  <si>
+    <t>Walltime (s)</t>
   </si>
 </sst>
 </file>
@@ -1553,17 +1541,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF9A9A9A"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF9A9A9A"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
@@ -1627,37 +1604,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1710,283 +1656,245 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2227,276 +2135,276 @@
       <c r="F1" s="1"/>
     </row>
     <row r="2" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="57"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="43"/>
+      <c r="B3" s="19"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="44"/>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="20"/>
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="52"/>
-      <c r="C4" s="7" t="s">
+      <c r="B4" s="24"/>
+      <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="5"/>
+      <c r="F4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="64" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" s="50">
+      <c r="B5" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="22">
         <v>1</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="10"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="65"/>
-      <c r="C6" s="51">
+      <c r="B6" s="45"/>
+      <c r="C6" s="23">
         <v>2</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="10"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="65"/>
-      <c r="C7" s="51">
+      <c r="B7" s="45"/>
+      <c r="C7" s="23">
         <v>4</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="10"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="65"/>
-      <c r="C8" s="50">
+      <c r="B8" s="45"/>
+      <c r="C8" s="22">
         <v>8</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="10"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="65"/>
-      <c r="C9" s="50">
+      <c r="B9" s="45"/>
+      <c r="C9" s="22">
         <v>16</v>
       </c>
-      <c r="D9" s="10"/>
+      <c r="D9" s="7"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="10"/>
+      <c r="F9" s="7"/>
     </row>
     <row r="10" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="54"/>
-      <c r="C10" s="53" t="s">
-        <v>106</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="B10" s="26"/>
+      <c r="C10" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="7" t="s">
+      <c r="E10" s="5"/>
+      <c r="F10" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="61" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="B11" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="D11" s="10"/>
+      <c r="C11" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="7"/>
       <c r="E11" s="1"/>
-      <c r="F11" s="10"/>
+      <c r="F11" s="7"/>
     </row>
     <row r="12" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="62"/>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="42"/>
+      <c r="C12" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="42"/>
+      <c r="C13" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="43"/>
+      <c r="C14" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="9"/>
+      <c r="C15" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="62"/>
-      <c r="C13" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="63"/>
-      <c r="C14" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="12"/>
-      <c r="C15" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="7" t="s">
-        <v>113</v>
+      <c r="E15" s="5"/>
+      <c r="F15" s="4" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="10"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="17" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="59"/>
-      <c r="C17" s="14" t="s">
+      <c r="B17" s="39"/>
+      <c r="C17" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="10"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="59"/>
-      <c r="C18" s="14" t="s">
+      <c r="B18" s="39"/>
+      <c r="C18" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="10"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="7"/>
     </row>
     <row r="19" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="59"/>
-      <c r="C19" s="14" t="s">
+      <c r="B19" s="39"/>
+      <c r="C19" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="10"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="59"/>
-      <c r="C20" s="14" t="s">
+      <c r="B20" s="39"/>
+      <c r="C20" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="10"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="7"/>
     </row>
     <row r="21" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="59"/>
-      <c r="C21" s="14" t="s">
+      <c r="B21" s="39"/>
+      <c r="C21" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="10"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="7"/>
     </row>
     <row r="22" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="59"/>
-      <c r="C22" s="14" t="s">
+      <c r="B22" s="39"/>
+      <c r="C22" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="10"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="7"/>
     </row>
     <row r="23" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="59"/>
-      <c r="C23" s="14" t="s">
+      <c r="B23" s="39"/>
+      <c r="C23" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="10"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="7"/>
     </row>
     <row r="24" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="59"/>
-      <c r="C24" s="14" t="s">
+      <c r="B24" s="39"/>
+      <c r="C24" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="10"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="7"/>
     </row>
     <row r="25" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="59"/>
-      <c r="C25" s="14" t="s">
+      <c r="B25" s="39"/>
+      <c r="C25" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="10"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="7"/>
     </row>
     <row r="26" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="59"/>
-      <c r="C26" s="14" t="s">
+      <c r="B26" s="39"/>
+      <c r="C26" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="10"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="10"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="7"/>
     </row>
     <row r="27" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="59"/>
-      <c r="C27" s="14" t="s">
+      <c r="B27" s="39"/>
+      <c r="C27" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="10"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="7"/>
     </row>
     <row r="28" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="59"/>
-      <c r="C28" s="14" t="s">
+      <c r="B28" s="39"/>
+      <c r="C28" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="10"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="7"/>
     </row>
     <row r="29" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="60"/>
-      <c r="C29" s="14" t="s">
+      <c r="B29" s="40"/>
+      <c r="C29" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="10"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="7"/>
     </row>
     <row r="30" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="31" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3480,1366 +3388,1151 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K975"/>
+  <dimension ref="A1:M950"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" style="41" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" style="18" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="23" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" style="15" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="35.85546875" customWidth="1"/>
-    <col min="8" max="8" width="3" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="29" width="14.28515625" customWidth="1"/>
+    <col min="7" max="8" width="35.85546875" customWidth="1"/>
+    <col min="9" max="9" width="3" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" customWidth="1"/>
+    <col min="11" max="11" width="35.85546875" customWidth="1"/>
+    <col min="12" max="12" width="22.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="31" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E1" s="22"/>
+    <row r="1" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E1" s="14"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-    </row>
-    <row r="2" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="69" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-    </row>
-    <row r="3" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="72"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="3" t="s">
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+    </row>
+    <row r="2" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+    </row>
+    <row r="3" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="5" t="s">
+      <c r="H3" s="50"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="K3" s="15"/>
-    </row>
-    <row r="4" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="66" t="s">
+      <c r="K3" s="50"/>
+      <c r="L3" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="M3" s="12"/>
+    </row>
+    <row r="4" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="60" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="G4" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="I4" s="30"/>
+      <c r="J4" s="57" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+    </row>
+    <row r="5" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="59"/>
+      <c r="C5" s="63" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="64" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5" s="31">
+        <v>1</v>
+      </c>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+    </row>
+    <row r="6" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="59"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="31">
+        <v>2</v>
+      </c>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="59"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="31">
+        <v>4</v>
+      </c>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+    </row>
+    <row r="8" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="59"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="31">
+        <v>8</v>
+      </c>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+    </row>
+    <row r="9" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="59"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="31">
+        <v>16</v>
+      </c>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+    </row>
+    <row r="10" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="59"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="31">
+        <v>32</v>
+      </c>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+    </row>
+    <row r="11" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="59"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="65" t="s">
         <v>94</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="F11" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="M11" s="12"/>
+    </row>
+    <row r="12" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="59"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="66" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="60">
+        <v>1</v>
+      </c>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="12"/>
+    </row>
+    <row r="13" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="59"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="60">
+        <v>2</v>
+      </c>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="12"/>
+    </row>
+    <row r="14" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="59"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="60">
+        <v>4</v>
+      </c>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+    </row>
+    <row r="15" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="59"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="64" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" s="60">
+        <v>1</v>
+      </c>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="M15" s="12"/>
+    </row>
+    <row r="16" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="59"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="60">
+        <v>2</v>
+      </c>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="M16" s="12"/>
+    </row>
+    <row r="17" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="59"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="64"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="60">
+        <v>4</v>
+      </c>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="M17" s="12"/>
+    </row>
+    <row r="18" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="59"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="67"/>
+      <c r="F18" s="57" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+    </row>
+    <row r="19" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="59"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="F19" s="31">
+        <v>1</v>
+      </c>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+    </row>
+    <row r="20" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="59"/>
+      <c r="C20" s="63"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="31">
+        <v>2</v>
+      </c>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+    </row>
+    <row r="21" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="59"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="31">
+        <v>4</v>
+      </c>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+    </row>
+    <row r="22" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="59"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="31">
+        <v>8</v>
+      </c>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+    </row>
+    <row r="23" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="59"/>
+      <c r="C23" s="63"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="31">
+        <v>16</v>
+      </c>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+    </row>
+    <row r="24" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="59"/>
+      <c r="C24" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="D24" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="62" t="s">
+        <v>92</v>
+      </c>
+      <c r="F24" s="57" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+    </row>
+    <row r="25" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="59"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="64" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" s="31">
+        <v>1</v>
+      </c>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+    </row>
+    <row r="26" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="59"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
+      <c r="F26" s="31">
+        <v>2</v>
+      </c>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+    </row>
+    <row r="27" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="59"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="31">
+        <v>4</v>
+      </c>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+    </row>
+    <row r="28" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="59"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="31">
+        <v>8</v>
+      </c>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+    </row>
+    <row r="29" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="59"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="64"/>
+      <c r="F29" s="31">
+        <v>16</v>
+      </c>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+    </row>
+    <row r="30" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="59"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="64"/>
+      <c r="F30" s="31">
+        <v>32</v>
+      </c>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+    </row>
+    <row r="31" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="59"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="65" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="G4" s="49" t="s">
-        <v>105</v>
-      </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="24" t="s">
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
+      <c r="L31" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="M31" s="12"/>
+    </row>
+    <row r="32" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="59"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="66" t="s">
+        <v>90</v>
+      </c>
+      <c r="F32" s="60">
+        <v>1</v>
+      </c>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+    </row>
+    <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="59"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="66"/>
+      <c r="F33" s="60">
+        <v>2</v>
+      </c>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+    </row>
+    <row r="34" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="59"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="66"/>
+      <c r="F34" s="60">
+        <v>4</v>
+      </c>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+    </row>
+    <row r="35" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="59"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-    </row>
-    <row r="5" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="67"/>
-      <c r="C5" s="87" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="81" t="s">
+      <c r="F35" s="60">
+        <v>1</v>
+      </c>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+    </row>
+    <row r="36" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="59"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="64"/>
+      <c r="F36" s="60">
+        <v>2</v>
+      </c>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+    </row>
+    <row r="37" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="59"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="64"/>
+      <c r="F37" s="60">
+        <v>4</v>
+      </c>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="12"/>
+    </row>
+    <row r="38" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="59"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="81" t="s">
+      <c r="E38" s="67"/>
+      <c r="F38" s="57" t="s">
+        <v>3</v>
+      </c>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="12"/>
+    </row>
+    <row r="39" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="59"/>
+      <c r="C39" s="45"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="68" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" s="31">
+        <v>1</v>
+      </c>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="12"/>
+      <c r="M39" s="12"/>
+    </row>
+    <row r="40" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="59"/>
+      <c r="C40" s="45"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="31">
+        <v>2</v>
+      </c>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="13"/>
+    </row>
+    <row r="41" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="59"/>
+      <c r="C41" s="45"/>
+      <c r="D41" s="64"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="31">
+        <v>4</v>
+      </c>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="32"/>
+    </row>
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="59"/>
+      <c r="C42" s="45"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="31">
+        <v>8</v>
+      </c>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+    </row>
+    <row r="43" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="59"/>
+      <c r="C43" s="45"/>
+      <c r="D43" s="64"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="31">
+        <v>16</v>
+      </c>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
+    </row>
+    <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="16"/>
+      <c r="B44" s="59"/>
+      <c r="C44" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="F5" s="9">
+      <c r="D44" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="E44" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="F44" s="70" t="s">
+        <v>85</v>
+      </c>
+      <c r="G44" s="70"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="70"/>
+      <c r="K44" s="70"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
+    </row>
+    <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="16"/>
+      <c r="B45" s="59"/>
+      <c r="C45" s="45"/>
+      <c r="D45" s="72" t="s">
+        <v>84</v>
+      </c>
+      <c r="E45" s="72" t="s">
+        <v>93</v>
+      </c>
+      <c r="F45" s="73">
         <v>1</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-    </row>
-    <row r="6" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="67"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="9">
+      <c r="G45" s="74"/>
+      <c r="H45" s="74"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="74"/>
+      <c r="K45" s="74"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+    </row>
+    <row r="46" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="16"/>
+      <c r="B46" s="59"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="73">
         <v>2</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-    </row>
-    <row r="7" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="67"/>
-      <c r="C7" s="88"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
-      <c r="F7" s="9">
+      <c r="G46" s="74"/>
+      <c r="H46" s="74"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="74"/>
+      <c r="K46" s="74"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
+    </row>
+    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="16"/>
+      <c r="B47" s="59"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="72"/>
+      <c r="E47" s="72"/>
+      <c r="F47" s="73">
         <v>4</v>
       </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-    </row>
-    <row r="8" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="67"/>
-      <c r="C8" s="88"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="9">
+      <c r="G47" s="74"/>
+      <c r="H47" s="74"/>
+      <c r="I47" s="71"/>
+      <c r="J47" s="74"/>
+      <c r="K47" s="74"/>
+      <c r="L47" s="16"/>
+      <c r="M47" s="16"/>
+    </row>
+    <row r="48" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="16"/>
+      <c r="B48" s="59"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="72"/>
+      <c r="E48" s="72"/>
+      <c r="F48" s="73">
         <v>8</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-    </row>
-    <row r="9" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="67"/>
-      <c r="C9" s="88"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="9">
+      <c r="G48" s="74"/>
+      <c r="H48" s="74"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="74"/>
+      <c r="K48" s="74"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+    </row>
+    <row r="49" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="16"/>
+      <c r="B49" s="59"/>
+      <c r="C49" s="45"/>
+      <c r="D49" s="72"/>
+      <c r="E49" s="72"/>
+      <c r="F49" s="73">
         <v>16</v>
       </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-    </row>
-    <row r="10" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="67"/>
-      <c r="C10" s="88"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="9">
+      <c r="G49" s="74"/>
+      <c r="H49" s="74"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="74"/>
+      <c r="K49" s="74"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
+    </row>
+    <row r="50" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="16"/>
+      <c r="B50" s="59"/>
+      <c r="C50" s="45"/>
+      <c r="D50" s="72"/>
+      <c r="E50" s="72"/>
+      <c r="F50" s="73">
         <v>32</v>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-    </row>
-    <row r="11" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="67"/>
-      <c r="C11" s="88"/>
-      <c r="D11" s="82"/>
-      <c r="E11" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="46" t="s">
-        <v>104</v>
-      </c>
-      <c r="K11" s="15"/>
-    </row>
-    <row r="12" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="67"/>
-      <c r="C12" s="88"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="75" t="s">
+      <c r="G50" s="74"/>
+      <c r="H50" s="74"/>
+      <c r="I50" s="71"/>
+      <c r="J50" s="74"/>
+      <c r="K50" s="74"/>
+      <c r="L50" s="16"/>
+      <c r="M50" s="16"/>
+    </row>
+    <row r="51" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="16"/>
+      <c r="B51" s="59"/>
+      <c r="C51" s="45"/>
+      <c r="D51" s="72"/>
+      <c r="E51" s="69" t="s">
+        <v>94</v>
+      </c>
+      <c r="F51" s="70" t="s">
+        <v>88</v>
+      </c>
+      <c r="G51" s="74"/>
+      <c r="H51" s="74"/>
+      <c r="I51" s="71"/>
+      <c r="J51" s="74"/>
+      <c r="K51" s="74"/>
+      <c r="L51" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="M51" s="16"/>
+    </row>
+    <row r="52" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="16"/>
+      <c r="B52" s="59"/>
+      <c r="C52" s="45"/>
+      <c r="D52" s="72"/>
+      <c r="E52" s="75" t="s">
+        <v>90</v>
+      </c>
+      <c r="F52" s="73">
+        <v>1</v>
+      </c>
+      <c r="G52" s="74"/>
+      <c r="H52" s="74"/>
+      <c r="I52" s="71"/>
+      <c r="J52" s="74"/>
+      <c r="K52" s="74"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
+    </row>
+    <row r="53" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="16"/>
+      <c r="B53" s="59"/>
+      <c r="C53" s="45"/>
+      <c r="D53" s="72"/>
+      <c r="E53" s="75"/>
+      <c r="F53" s="73">
+        <v>2</v>
+      </c>
+      <c r="G53" s="74"/>
+      <c r="H53" s="74"/>
+      <c r="I53" s="71"/>
+      <c r="J53" s="74"/>
+      <c r="K53" s="74"/>
+      <c r="L53" s="16"/>
+      <c r="M53" s="16"/>
+    </row>
+    <row r="54" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="16"/>
+      <c r="B54" s="59"/>
+      <c r="C54" s="45"/>
+      <c r="D54" s="72"/>
+      <c r="E54" s="75"/>
+      <c r="F54" s="73">
+        <v>4</v>
+      </c>
+      <c r="G54" s="74"/>
+      <c r="H54" s="74"/>
+      <c r="I54" s="71"/>
+      <c r="J54" s="74"/>
+      <c r="K54" s="74"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
+    </row>
+    <row r="55" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="16"/>
+      <c r="B55" s="59"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="72"/>
+      <c r="E55" s="72" t="s">
+        <v>89</v>
+      </c>
+      <c r="F55" s="73">
+        <v>1</v>
+      </c>
+      <c r="G55" s="74"/>
+      <c r="H55" s="74"/>
+      <c r="I55" s="71"/>
+      <c r="J55" s="74"/>
+      <c r="K55" s="74"/>
+      <c r="L55" s="16"/>
+      <c r="M55" s="16"/>
+    </row>
+    <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="16"/>
+      <c r="B56" s="59"/>
+      <c r="C56" s="45"/>
+      <c r="D56" s="72"/>
+      <c r="E56" s="72"/>
+      <c r="F56" s="73">
+        <v>2</v>
+      </c>
+      <c r="G56" s="74"/>
+      <c r="H56" s="74"/>
+      <c r="I56" s="71"/>
+      <c r="J56" s="74"/>
+      <c r="K56" s="74"/>
+      <c r="L56" s="16"/>
+      <c r="M56" s="16"/>
+    </row>
+    <row r="57" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="16"/>
+      <c r="B57" s="59"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="72"/>
+      <c r="E57" s="72"/>
+      <c r="F57" s="73">
+        <v>4</v>
+      </c>
+      <c r="G57" s="74"/>
+      <c r="H57" s="74"/>
+      <c r="I57" s="71"/>
+      <c r="J57" s="74"/>
+      <c r="K57" s="74"/>
+      <c r="L57" s="16"/>
+      <c r="M57" s="16"/>
+    </row>
+    <row r="58" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="16"/>
+      <c r="B58" s="59"/>
+      <c r="C58" s="45"/>
+      <c r="D58" s="72" t="s">
+        <v>87</v>
+      </c>
+      <c r="E58" s="76" t="s">
+        <v>92</v>
+      </c>
+      <c r="F58" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="74"/>
+      <c r="H58" s="74"/>
+      <c r="I58" s="71"/>
+      <c r="J58" s="74"/>
+      <c r="K58" s="74"/>
+      <c r="L58" s="16"/>
+      <c r="M58" s="16"/>
+    </row>
+    <row r="59" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="16"/>
+      <c r="B59" s="59"/>
+      <c r="C59" s="45"/>
+      <c r="D59" s="72"/>
+      <c r="E59" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F59" s="73">
         <v>1</v>
       </c>
-      <c r="G12" s="10"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="15"/>
-    </row>
-    <row r="13" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="67"/>
-      <c r="C13" s="88"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="20">
+      <c r="G59" s="74"/>
+      <c r="H59" s="74"/>
+      <c r="I59" s="71"/>
+      <c r="J59" s="74"/>
+      <c r="K59" s="74"/>
+      <c r="L59" s="16"/>
+      <c r="M59" s="16"/>
+    </row>
+    <row r="60" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="16"/>
+      <c r="B60" s="59"/>
+      <c r="C60" s="45"/>
+      <c r="D60" s="72"/>
+      <c r="E60" s="77"/>
+      <c r="F60" s="73">
         <v>2</v>
       </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="15"/>
-    </row>
-    <row r="14" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="67"/>
-      <c r="C14" s="88"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="20">
+      <c r="G60" s="74"/>
+      <c r="H60" s="74"/>
+      <c r="I60" s="71"/>
+      <c r="J60" s="74"/>
+      <c r="K60" s="74"/>
+      <c r="L60" s="17"/>
+      <c r="M60" s="17"/>
+    </row>
+    <row r="61" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="16"/>
+      <c r="B61" s="59"/>
+      <c r="C61" s="45"/>
+      <c r="D61" s="72"/>
+      <c r="E61" s="77"/>
+      <c r="F61" s="73">
         <v>4</v>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-    </row>
-    <row r="15" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="67"/>
-      <c r="C15" s="88"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="81" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" s="20">
-        <v>1</v>
-      </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="10"/>
-      <c r="K15" s="15"/>
-    </row>
-    <row r="16" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="67"/>
-      <c r="C16" s="88"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="20">
-        <v>2</v>
-      </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="10"/>
-      <c r="K16" s="15"/>
-    </row>
-    <row r="17" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="67"/>
-      <c r="C17" s="88"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="20">
-        <v>4</v>
-      </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="10"/>
-      <c r="K17" s="15"/>
-    </row>
-    <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="67"/>
-      <c r="C18" s="88"/>
-      <c r="D18" s="99" t="s">
-        <v>90</v>
-      </c>
-      <c r="E18" s="45"/>
-      <c r="F18" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-    </row>
-    <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="67"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="81"/>
-      <c r="E19" s="85" t="s">
-        <v>96</v>
-      </c>
-      <c r="F19" s="9">
-        <v>1</v>
-      </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-    </row>
-    <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="67"/>
-      <c r="C20" s="88"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="9">
-        <v>2</v>
-      </c>
-      <c r="G20" s="10"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-    </row>
-    <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="67"/>
-      <c r="C21" s="88"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="9">
-        <v>4</v>
-      </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="10"/>
-    </row>
-    <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="67"/>
-      <c r="C22" s="88"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="85"/>
-      <c r="F22" s="9">
+      <c r="G61" s="74"/>
+      <c r="H61" s="74"/>
+      <c r="I61" s="71"/>
+      <c r="J61" s="74"/>
+      <c r="K61" s="74"/>
+      <c r="L61" s="16"/>
+      <c r="M61" s="16"/>
+    </row>
+    <row r="62" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="16"/>
+      <c r="B62" s="59"/>
+      <c r="C62" s="45"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="77"/>
+      <c r="F62" s="73">
         <v>8</v>
       </c>
-      <c r="G22" s="10"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="10"/>
-    </row>
-    <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="67"/>
-      <c r="C23" s="89"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="86"/>
-      <c r="F23" s="9">
+      <c r="G62" s="74"/>
+      <c r="H62" s="74"/>
+      <c r="I62" s="71"/>
+      <c r="J62" s="74"/>
+      <c r="K62" s="74"/>
+      <c r="L62" s="16"/>
+      <c r="M62" s="16"/>
+    </row>
+    <row r="63" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="16"/>
+      <c r="B63" s="59"/>
+      <c r="C63" s="45"/>
+      <c r="D63" s="72"/>
+      <c r="E63" s="77"/>
+      <c r="F63" s="73">
         <v>16</v>
       </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="10"/>
-    </row>
-    <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="67"/>
-      <c r="C24" s="58" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="G24" s="7"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-    </row>
-    <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="67"/>
-      <c r="C25" s="90"/>
-      <c r="D25" s="81" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="81" t="s">
-        <v>96</v>
-      </c>
-      <c r="F25" s="9">
-        <v>1</v>
-      </c>
-      <c r="G25" s="10"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-    </row>
-    <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="67"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="82"/>
-      <c r="E26" s="82"/>
-      <c r="F26" s="9">
-        <v>2</v>
-      </c>
-      <c r="G26" s="10"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-    </row>
-    <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="67"/>
-      <c r="C27" s="90"/>
-      <c r="D27" s="82"/>
-      <c r="E27" s="82"/>
-      <c r="F27" s="9">
-        <v>4</v>
-      </c>
-      <c r="G27" s="10"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-    </row>
-    <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="67"/>
-      <c r="C28" s="90"/>
-      <c r="D28" s="82"/>
-      <c r="E28" s="82"/>
-      <c r="F28" s="9">
-        <v>8</v>
-      </c>
-      <c r="G28" s="10"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-    </row>
-    <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="67"/>
-      <c r="C29" s="90"/>
-      <c r="D29" s="82"/>
-      <c r="E29" s="82"/>
-      <c r="F29" s="9">
-        <v>16</v>
-      </c>
-      <c r="G29" s="10"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-    </row>
-    <row r="30" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="67"/>
-      <c r="C30" s="90"/>
-      <c r="D30" s="82"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="9">
-        <v>32</v>
-      </c>
-      <c r="G30" s="10"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-    </row>
-    <row r="31" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="67"/>
-      <c r="C31" s="90"/>
-      <c r="D31" s="82"/>
-      <c r="E31" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="F31" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="G31" s="10"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="46" t="s">
-        <v>104</v>
-      </c>
-      <c r="K31" s="15"/>
-    </row>
-    <row r="32" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="67"/>
-      <c r="C32" s="90"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="75" t="s">
-        <v>93</v>
-      </c>
-      <c r="F32" s="20">
-        <v>1</v>
-      </c>
-      <c r="G32" s="10"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-    </row>
-    <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="67"/>
-      <c r="C33" s="90"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="76"/>
-      <c r="F33" s="20">
-        <v>2</v>
-      </c>
-      <c r="G33" s="10"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-    </row>
-    <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="67"/>
-      <c r="C34" s="90"/>
-      <c r="D34" s="82"/>
-      <c r="E34" s="77"/>
-      <c r="F34" s="20">
-        <v>4</v>
-      </c>
-      <c r="G34" s="10"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-    </row>
-    <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="67"/>
-      <c r="C35" s="90"/>
-      <c r="D35" s="82"/>
-      <c r="E35" s="81" t="s">
-        <v>92</v>
-      </c>
-      <c r="F35" s="20">
-        <v>1</v>
-      </c>
-      <c r="G35" s="10"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-    </row>
-    <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="67"/>
-      <c r="C36" s="90"/>
-      <c r="D36" s="82"/>
-      <c r="E36" s="82"/>
-      <c r="F36" s="20">
-        <v>2</v>
-      </c>
-      <c r="G36" s="10"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-    </row>
-    <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="67"/>
-      <c r="C37" s="90"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="20">
-        <v>4</v>
-      </c>
-      <c r="G37" s="10"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-    </row>
-    <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="67"/>
-      <c r="C38" s="90"/>
-      <c r="D38" s="99" t="s">
-        <v>90</v>
-      </c>
-      <c r="F38" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="G38" s="10"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-    </row>
-    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="67"/>
-      <c r="C39" s="90"/>
-      <c r="D39" s="81"/>
-      <c r="E39" s="85" t="s">
-        <v>96</v>
-      </c>
-      <c r="F39" s="9">
-        <v>1</v>
-      </c>
-      <c r="G39" s="10"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-    </row>
-    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="67"/>
-      <c r="C40" s="90"/>
-      <c r="D40" s="82"/>
-      <c r="E40" s="85"/>
-      <c r="F40" s="9">
-        <v>2</v>
-      </c>
-      <c r="G40" s="10"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-    </row>
-    <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="67"/>
-      <c r="C41" s="90"/>
-      <c r="D41" s="82"/>
-      <c r="E41" s="85"/>
-      <c r="F41" s="9">
-        <v>4</v>
-      </c>
-      <c r="G41" s="10"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="10"/>
-    </row>
-    <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="67"/>
-      <c r="C42" s="90"/>
-      <c r="D42" s="82"/>
-      <c r="E42" s="85"/>
-      <c r="F42" s="9">
-        <v>8</v>
-      </c>
-      <c r="G42" s="10"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="10"/>
-    </row>
-    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="67"/>
-      <c r="C43" s="91"/>
-      <c r="D43" s="82"/>
-      <c r="E43" s="86"/>
-      <c r="F43" s="9">
-        <v>16</v>
-      </c>
-      <c r="G43" s="10"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="10"/>
-    </row>
-    <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="27"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="58" t="s">
-        <v>99</v>
-      </c>
-      <c r="D44" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="E44" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="F44" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="G44" s="29"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="29"/>
-      <c r="J44" s="27"/>
-      <c r="K44" s="27"/>
-    </row>
-    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="27"/>
-      <c r="B45" s="67"/>
-      <c r="C45" s="90"/>
-      <c r="D45" s="92" t="s">
-        <v>87</v>
-      </c>
-      <c r="E45" s="92" t="s">
-        <v>96</v>
-      </c>
-      <c r="F45" s="31">
-        <v>1</v>
-      </c>
-      <c r="G45" s="32"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="32"/>
-      <c r="J45" s="27"/>
-      <c r="K45" s="27"/>
-    </row>
-    <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="27"/>
-      <c r="B46" s="67"/>
-      <c r="C46" s="90"/>
-      <c r="D46" s="93"/>
-      <c r="E46" s="93"/>
-      <c r="F46" s="31">
-        <v>2</v>
-      </c>
-      <c r="G46" s="32"/>
-      <c r="H46" s="33"/>
-      <c r="I46" s="32"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-    </row>
-    <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="27"/>
-      <c r="B47" s="67"/>
-      <c r="C47" s="90"/>
-      <c r="D47" s="93"/>
-      <c r="E47" s="93"/>
-      <c r="F47" s="31">
-        <v>4</v>
-      </c>
-      <c r="G47" s="32"/>
-      <c r="H47" s="33"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="27"/>
-      <c r="K47" s="27"/>
-    </row>
-    <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="27"/>
-      <c r="B48" s="67"/>
-      <c r="C48" s="90"/>
-      <c r="D48" s="93"/>
-      <c r="E48" s="93"/>
-      <c r="F48" s="31">
-        <v>8</v>
-      </c>
-      <c r="G48" s="32"/>
-      <c r="H48" s="33"/>
-      <c r="I48" s="32"/>
-      <c r="J48" s="27"/>
-      <c r="K48" s="27"/>
-    </row>
-    <row r="49" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="27"/>
-      <c r="B49" s="67"/>
-      <c r="C49" s="90"/>
-      <c r="D49" s="93"/>
-      <c r="E49" s="93"/>
-      <c r="F49" s="31">
-        <v>16</v>
-      </c>
-      <c r="G49" s="32"/>
-      <c r="H49" s="33"/>
-      <c r="I49" s="32"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-    </row>
-    <row r="50" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="27"/>
-      <c r="B50" s="67"/>
-      <c r="C50" s="90"/>
-      <c r="D50" s="93"/>
-      <c r="E50" s="94"/>
-      <c r="F50" s="31">
-        <v>32</v>
-      </c>
-      <c r="G50" s="32"/>
-      <c r="H50" s="33"/>
-      <c r="I50" s="32"/>
-      <c r="J50" s="27"/>
-      <c r="K50" s="27"/>
-    </row>
-    <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="27"/>
-      <c r="B51" s="67"/>
-      <c r="C51" s="90"/>
-      <c r="D51" s="93"/>
-      <c r="E51" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="F51" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="G51" s="32"/>
-      <c r="H51" s="33"/>
-      <c r="I51" s="32"/>
-      <c r="J51" s="46" t="s">
-        <v>104</v>
-      </c>
-      <c r="K51" s="27"/>
-    </row>
-    <row r="52" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="27"/>
-      <c r="B52" s="67"/>
-      <c r="C52" s="90"/>
-      <c r="D52" s="93"/>
-      <c r="E52" s="78" t="s">
-        <v>93</v>
-      </c>
-      <c r="F52" s="31">
-        <v>1</v>
-      </c>
-      <c r="G52" s="32"/>
-      <c r="H52" s="33"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="27"/>
-      <c r="K52" s="27"/>
-    </row>
-    <row r="53" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="27"/>
-      <c r="B53" s="67"/>
-      <c r="C53" s="90"/>
-      <c r="D53" s="93"/>
-      <c r="E53" s="79"/>
-      <c r="F53" s="31">
-        <v>2</v>
-      </c>
-      <c r="G53" s="32"/>
-      <c r="H53" s="33"/>
-      <c r="I53" s="32"/>
-      <c r="J53" s="27"/>
-      <c r="K53" s="27"/>
-    </row>
-    <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="27"/>
-      <c r="B54" s="67"/>
-      <c r="C54" s="90"/>
-      <c r="D54" s="93"/>
-      <c r="E54" s="80"/>
-      <c r="F54" s="31">
-        <v>4</v>
-      </c>
-      <c r="G54" s="32"/>
-      <c r="H54" s="33"/>
-      <c r="I54" s="32"/>
-      <c r="J54" s="27"/>
-      <c r="K54" s="27"/>
-    </row>
-    <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="27"/>
-      <c r="B55" s="67"/>
-      <c r="C55" s="90"/>
-      <c r="D55" s="93"/>
-      <c r="E55" s="92" t="s">
-        <v>92</v>
-      </c>
-      <c r="F55" s="31">
-        <v>1</v>
-      </c>
-      <c r="G55" s="32"/>
-      <c r="H55" s="33"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="27"/>
-      <c r="K55" s="27"/>
-    </row>
-    <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="27"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="90"/>
-      <c r="D56" s="93"/>
-      <c r="E56" s="93"/>
-      <c r="F56" s="31">
-        <v>2</v>
-      </c>
-      <c r="G56" s="32"/>
-      <c r="H56" s="33"/>
-      <c r="I56" s="32"/>
-      <c r="J56" s="27"/>
-      <c r="K56" s="27"/>
-    </row>
-    <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="27"/>
-      <c r="B57" s="67"/>
-      <c r="C57" s="90"/>
-      <c r="D57" s="94"/>
-      <c r="E57" s="94"/>
-      <c r="F57" s="31">
-        <v>4</v>
-      </c>
-      <c r="G57" s="32"/>
-      <c r="H57" s="33"/>
-      <c r="I57" s="32"/>
-      <c r="J57" s="27"/>
-      <c r="K57" s="27"/>
-    </row>
-    <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="27"/>
-      <c r="B58" s="67"/>
-      <c r="C58" s="90"/>
-      <c r="D58" s="95" t="s">
-        <v>90</v>
-      </c>
-      <c r="E58" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F58" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="32"/>
-      <c r="H58" s="33"/>
-      <c r="I58" s="32"/>
-      <c r="J58" s="27"/>
-      <c r="K58" s="27"/>
-    </row>
-    <row r="59" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="27"/>
-      <c r="B59" s="67"/>
-      <c r="C59" s="90"/>
-      <c r="D59" s="92"/>
-      <c r="E59" s="96" t="s">
-        <v>96</v>
-      </c>
-      <c r="F59" s="31">
-        <v>1</v>
-      </c>
-      <c r="G59" s="32"/>
-      <c r="H59" s="33"/>
-      <c r="I59" s="32"/>
-      <c r="J59" s="27"/>
-      <c r="K59" s="27"/>
-    </row>
-    <row r="60" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="27"/>
-      <c r="B60" s="67"/>
-      <c r="C60" s="90"/>
-      <c r="D60" s="93"/>
-      <c r="E60" s="97"/>
-      <c r="F60" s="31">
-        <v>2</v>
-      </c>
-      <c r="G60" s="32"/>
-      <c r="H60" s="33"/>
-      <c r="I60" s="32"/>
-      <c r="J60" s="38"/>
-      <c r="K60" s="38"/>
-    </row>
-    <row r="61" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="27"/>
-      <c r="B61" s="67"/>
-      <c r="C61" s="90"/>
-      <c r="D61" s="93"/>
-      <c r="E61" s="97"/>
-      <c r="F61" s="31">
-        <v>4</v>
-      </c>
-      <c r="G61" s="32"/>
-      <c r="H61" s="33"/>
-      <c r="I61" s="32"/>
-      <c r="J61" s="27"/>
-      <c r="K61" s="27"/>
-    </row>
-    <row r="62" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="27"/>
-      <c r="B62" s="67"/>
-      <c r="C62" s="90"/>
-      <c r="D62" s="93"/>
-      <c r="E62" s="97"/>
-      <c r="F62" s="31">
-        <v>8</v>
-      </c>
-      <c r="G62" s="32"/>
-      <c r="H62" s="33"/>
-      <c r="I62" s="32"/>
-      <c r="J62" s="27"/>
-      <c r="K62" s="27"/>
-    </row>
-    <row r="63" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="27"/>
-      <c r="B63" s="68"/>
-      <c r="C63" s="91"/>
-      <c r="D63" s="94"/>
-      <c r="E63" s="98"/>
-      <c r="F63" s="31">
-        <v>16</v>
-      </c>
-      <c r="G63" s="32"/>
-      <c r="H63" s="33"/>
-      <c r="I63" s="32"/>
-      <c r="J63" s="27"/>
-      <c r="K63" s="27"/>
-    </row>
-    <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="66" t="s">
-        <v>82</v>
-      </c>
-      <c r="C64" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="D64" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="E64" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="F64" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="G64" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="H64" s="11"/>
-      <c r="I64" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="J64" s="15"/>
-      <c r="K64" s="15"/>
-    </row>
-    <row r="65" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="67"/>
-      <c r="C65" s="87" t="s">
-        <v>83</v>
-      </c>
-      <c r="D65" s="81" t="s">
-        <v>87</v>
-      </c>
-      <c r="E65" s="81" t="s">
-        <v>100</v>
-      </c>
-      <c r="F65" s="9">
-        <v>1</v>
-      </c>
-      <c r="G65" s="10"/>
-      <c r="H65" s="11"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="15"/>
-      <c r="K65" s="15"/>
-    </row>
-    <row r="66" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="67"/>
-      <c r="C66" s="88"/>
-      <c r="D66" s="82"/>
-      <c r="E66" s="82"/>
-      <c r="F66" s="9">
-        <v>2</v>
-      </c>
-      <c r="G66" s="10"/>
-      <c r="H66" s="11"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="15"/>
-      <c r="K66" s="15"/>
-    </row>
-    <row r="67" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="67"/>
-      <c r="C67" s="88"/>
-      <c r="D67" s="82"/>
-      <c r="E67" s="82"/>
-      <c r="F67" s="9">
-        <v>4</v>
-      </c>
-      <c r="G67" s="10"/>
-      <c r="H67" s="11"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="15"/>
-      <c r="K67" s="15"/>
-    </row>
-    <row r="68" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="67"/>
-      <c r="C68" s="88"/>
-      <c r="D68" s="82"/>
-      <c r="E68" s="82"/>
-      <c r="F68" s="9">
-        <v>8</v>
-      </c>
-      <c r="G68" s="10"/>
-      <c r="H68" s="11"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="15"/>
-      <c r="K68" s="15"/>
-    </row>
-    <row r="69" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="67"/>
-      <c r="C69" s="88"/>
-      <c r="D69" s="82"/>
-      <c r="E69" s="82"/>
-      <c r="F69" s="9">
-        <v>16</v>
-      </c>
-      <c r="G69" s="10"/>
-      <c r="H69" s="11"/>
-      <c r="I69" s="10"/>
-      <c r="J69" s="15"/>
-      <c r="K69" s="15"/>
-    </row>
-    <row r="70" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="67"/>
-      <c r="C70" s="88"/>
-      <c r="D70" s="82"/>
-      <c r="E70" s="83"/>
-      <c r="F70" s="9">
-        <v>32</v>
-      </c>
-      <c r="G70" s="10"/>
-      <c r="H70" s="11"/>
-      <c r="I70" s="10"/>
-      <c r="J70" s="15"/>
-      <c r="K70" s="15"/>
-    </row>
-    <row r="71" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="67"/>
-      <c r="C71" s="88"/>
-      <c r="D71" s="42"/>
-      <c r="E71" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F71" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="G71" s="10"/>
-      <c r="H71" s="11"/>
-      <c r="I71" s="10"/>
-      <c r="J71" s="15"/>
-      <c r="K71" s="15"/>
-    </row>
-    <row r="72" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="67"/>
-      <c r="C72" s="88"/>
-      <c r="D72" s="81" t="s">
-        <v>90</v>
-      </c>
-      <c r="E72" s="84" t="s">
-        <v>100</v>
-      </c>
-      <c r="F72" s="9">
-        <v>1</v>
-      </c>
-      <c r="G72" s="10"/>
-      <c r="H72" s="11"/>
-      <c r="I72" s="10"/>
-      <c r="J72" s="15"/>
-      <c r="K72" s="15"/>
-    </row>
-    <row r="73" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="67"/>
-      <c r="C73" s="88"/>
-      <c r="D73" s="82"/>
-      <c r="E73" s="85"/>
-      <c r="F73" s="9">
-        <v>2</v>
-      </c>
-      <c r="G73" s="10"/>
-      <c r="H73" s="11"/>
-      <c r="I73" s="10"/>
-      <c r="J73" s="16"/>
-      <c r="K73" s="16"/>
-    </row>
-    <row r="74" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="67"/>
-      <c r="C74" s="88"/>
-      <c r="D74" s="82"/>
-      <c r="E74" s="85"/>
-      <c r="F74" s="9">
-        <v>4</v>
-      </c>
-      <c r="G74" s="10"/>
-      <c r="H74" s="11"/>
-      <c r="I74" s="10"/>
-    </row>
-    <row r="75" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="67"/>
-      <c r="C75" s="88"/>
-      <c r="D75" s="82"/>
-      <c r="E75" s="85"/>
-      <c r="F75" s="9">
-        <v>8</v>
-      </c>
-      <c r="G75" s="10"/>
-      <c r="H75" s="11"/>
-      <c r="I75" s="10"/>
-    </row>
-    <row r="76" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="67"/>
-      <c r="C76" s="89"/>
-      <c r="D76" s="83"/>
-      <c r="E76" s="86"/>
-      <c r="F76" s="9">
-        <v>16</v>
-      </c>
-      <c r="G76" s="10"/>
-      <c r="H76" s="11"/>
-      <c r="I76" s="10"/>
-    </row>
-    <row r="77" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="67"/>
-      <c r="C77" s="87" t="s">
-        <v>84</v>
-      </c>
-      <c r="D77" s="81" t="s">
-        <v>87</v>
-      </c>
-      <c r="E77" s="81" t="s">
-        <v>100</v>
-      </c>
-      <c r="F77" s="9">
-        <v>1</v>
-      </c>
-      <c r="G77" s="10"/>
-      <c r="H77" s="11"/>
-      <c r="I77" s="10"/>
-      <c r="J77" s="15"/>
-      <c r="K77" s="15"/>
-    </row>
-    <row r="78" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="67"/>
-      <c r="C78" s="88"/>
-      <c r="D78" s="82"/>
-      <c r="E78" s="82"/>
-      <c r="F78" s="9">
-        <v>2</v>
-      </c>
-      <c r="G78" s="10"/>
-      <c r="H78" s="11"/>
-      <c r="I78" s="10"/>
-      <c r="J78" s="15"/>
-      <c r="K78" s="15"/>
-    </row>
-    <row r="79" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="67"/>
-      <c r="C79" s="88"/>
-      <c r="D79" s="82"/>
-      <c r="E79" s="82"/>
-      <c r="F79" s="9">
-        <v>4</v>
-      </c>
-      <c r="G79" s="10"/>
-      <c r="H79" s="11"/>
-      <c r="I79" s="10"/>
-      <c r="J79" s="15"/>
-      <c r="K79" s="15"/>
-    </row>
-    <row r="80" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="67"/>
-      <c r="C80" s="88"/>
-      <c r="D80" s="82"/>
-      <c r="E80" s="82"/>
-      <c r="F80" s="9">
-        <v>8</v>
-      </c>
-      <c r="G80" s="10"/>
-      <c r="H80" s="11"/>
-      <c r="I80" s="10"/>
-      <c r="J80" s="15"/>
-      <c r="K80" s="15"/>
-    </row>
-    <row r="81" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="67"/>
-      <c r="C81" s="88"/>
-      <c r="D81" s="82"/>
-      <c r="E81" s="82"/>
-      <c r="F81" s="9">
-        <v>16</v>
-      </c>
-      <c r="G81" s="10"/>
-      <c r="H81" s="11"/>
-      <c r="I81" s="10"/>
-      <c r="J81" s="15"/>
-      <c r="K81" s="15"/>
-    </row>
-    <row r="82" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="67"/>
-      <c r="C82" s="88"/>
-      <c r="D82" s="82"/>
-      <c r="E82" s="83"/>
-      <c r="F82" s="9">
-        <v>32</v>
-      </c>
-      <c r="G82" s="10"/>
-      <c r="H82" s="11"/>
-      <c r="I82" s="10"/>
-      <c r="J82" s="15"/>
-      <c r="K82" s="15"/>
-    </row>
-    <row r="83" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="67"/>
-      <c r="C83" s="88"/>
-      <c r="D83" s="42"/>
-      <c r="E83" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F83" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="10"/>
-      <c r="H83" s="11"/>
-      <c r="I83" s="10"/>
-      <c r="J83" s="15"/>
-      <c r="K83" s="15"/>
-    </row>
-    <row r="84" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="67"/>
-      <c r="C84" s="88"/>
-      <c r="D84" s="81" t="s">
-        <v>90</v>
-      </c>
-      <c r="E84" s="84" t="s">
-        <v>100</v>
-      </c>
-      <c r="F84" s="9">
-        <v>1</v>
-      </c>
-      <c r="G84" s="10"/>
-      <c r="H84" s="11"/>
-      <c r="I84" s="10"/>
-      <c r="J84" s="15"/>
-      <c r="K84" s="15"/>
-    </row>
-    <row r="85" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="67"/>
-      <c r="C85" s="88"/>
-      <c r="D85" s="82"/>
-      <c r="E85" s="85"/>
-      <c r="F85" s="9">
-        <v>2</v>
-      </c>
-      <c r="G85" s="10"/>
-      <c r="H85" s="11"/>
-      <c r="I85" s="10"/>
-      <c r="J85" s="16"/>
-      <c r="K85" s="16"/>
-    </row>
-    <row r="86" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="67"/>
-      <c r="C86" s="88"/>
-      <c r="D86" s="82"/>
-      <c r="E86" s="85"/>
-      <c r="F86" s="9">
-        <v>4</v>
-      </c>
-      <c r="G86" s="10"/>
-      <c r="H86" s="11"/>
-      <c r="I86" s="10"/>
-    </row>
-    <row r="87" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B87" s="67"/>
-      <c r="C87" s="88"/>
-      <c r="D87" s="82"/>
-      <c r="E87" s="85"/>
-      <c r="F87" s="9">
-        <v>8</v>
-      </c>
-      <c r="G87" s="10"/>
-      <c r="H87" s="11"/>
-      <c r="I87" s="10"/>
-    </row>
-    <row r="88" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B88" s="68"/>
-      <c r="C88" s="89"/>
-      <c r="D88" s="83"/>
-      <c r="E88" s="86"/>
-      <c r="F88" s="9">
-        <v>16</v>
-      </c>
-      <c r="G88" s="10"/>
-      <c r="H88" s="11"/>
-      <c r="I88" s="10"/>
-    </row>
-    <row r="89" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="G63" s="74"/>
+      <c r="H63" s="74"/>
+      <c r="I63" s="71"/>
+      <c r="J63" s="74"/>
+      <c r="K63" s="74"/>
+      <c r="L63" s="16"/>
+      <c r="M63" s="16"/>
+    </row>
+    <row r="64" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C64" s="55"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5694,33 +5387,23 @@
     <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="26">
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="E52:E54"/>
+    <mergeCell ref="C5:C23"/>
+    <mergeCell ref="C24:C43"/>
+    <mergeCell ref="C44:C63"/>
+    <mergeCell ref="D45:D57"/>
+    <mergeCell ref="E45:E50"/>
+    <mergeCell ref="E55:E57"/>
+    <mergeCell ref="D58:D63"/>
+    <mergeCell ref="E59:E63"/>
     <mergeCell ref="D38:D43"/>
     <mergeCell ref="E39:E43"/>
     <mergeCell ref="B4:B63"/>
@@ -5732,30 +5415,6 @@
     <mergeCell ref="D25:D37"/>
     <mergeCell ref="E25:E30"/>
     <mergeCell ref="E35:E37"/>
-    <mergeCell ref="D65:D70"/>
-    <mergeCell ref="E65:E70"/>
-    <mergeCell ref="E72:E76"/>
-    <mergeCell ref="D45:D57"/>
-    <mergeCell ref="E45:E50"/>
-    <mergeCell ref="E55:E57"/>
-    <mergeCell ref="D58:D63"/>
-    <mergeCell ref="E59:E63"/>
-    <mergeCell ref="B64:B88"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="E52:E54"/>
-    <mergeCell ref="D84:D88"/>
-    <mergeCell ref="E84:E88"/>
-    <mergeCell ref="C5:C23"/>
-    <mergeCell ref="C24:C43"/>
-    <mergeCell ref="C44:C63"/>
-    <mergeCell ref="C65:C76"/>
-    <mergeCell ref="C77:C88"/>
-    <mergeCell ref="D72:D76"/>
-    <mergeCell ref="D77:D82"/>
-    <mergeCell ref="E77:E82"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5766,7 +5425,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="B1:H982"/>
+  <dimension ref="B1:H977"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" customWidth="1"/>
@@ -5790,216 +5449,154 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="103" t="s">
+      <c r="B2" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+    </row>
+    <row r="3" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="30"/>
+      <c r="H3" s="29" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-    </row>
-    <row r="3" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="105"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="106" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="107"/>
-      <c r="H3" s="106" t="s">
+      <c r="G4" s="30"/>
+      <c r="H4" s="27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="31">
+        <v>4</v>
+      </c>
+      <c r="E5" s="31">
+        <v>4</v>
+      </c>
+      <c r="F5" s="32"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="32"/>
+    </row>
+    <row r="6" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="32"/>
+    </row>
+    <row r="7" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="44"/>
+      <c r="C7" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="G7" s="30"/>
+      <c r="H7" s="27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="44"/>
+      <c r="C8" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="31">
+        <v>4</v>
+      </c>
+      <c r="E8" s="31">
+        <v>4</v>
+      </c>
+      <c r="F8" s="32"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="32"/>
+    </row>
+    <row r="9" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="44"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="32"/>
+    </row>
+    <row r="10" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="44"/>
+      <c r="C10" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="44"/>
+      <c r="C11" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="31">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="64" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="112" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4" s="108" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="108" t="s">
-        <v>117</v>
-      </c>
-      <c r="F4" s="108" t="s">
-        <v>120</v>
-      </c>
-      <c r="G4" s="107"/>
-      <c r="H4" s="108" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="64"/>
-      <c r="C5" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" s="109">
-        <v>2</v>
-      </c>
-      <c r="E5" s="109">
-        <v>4</v>
-      </c>
-      <c r="F5" s="110"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="110"/>
-    </row>
-    <row r="6" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="109">
-        <v>4</v>
-      </c>
-      <c r="E6" s="109">
-        <v>4</v>
-      </c>
-      <c r="F6" s="110"/>
-      <c r="G6" s="107"/>
-      <c r="H6" s="110"/>
-    </row>
-    <row r="7" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="109">
+      <c r="E11" s="31">
         <v>8</v>
       </c>
-      <c r="E7" s="109">
-        <v>4</v>
-      </c>
-      <c r="F7" s="110"/>
-      <c r="G7" s="107"/>
-      <c r="H7" s="110"/>
-    </row>
-    <row r="8" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="109"/>
-      <c r="E8" s="109"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="107"/>
-      <c r="H8" s="110"/>
-    </row>
-    <row r="9" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="64"/>
-      <c r="C9" s="112" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="108" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="108" t="s">
-        <v>117</v>
-      </c>
-      <c r="F9" s="108" t="s">
-        <v>120</v>
-      </c>
-      <c r="G9" s="107"/>
-      <c r="H9" s="108" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="64"/>
-      <c r="C10" s="102"/>
-      <c r="D10" s="108">
-        <v>2</v>
-      </c>
-      <c r="E10" s="108">
-        <v>4</v>
-      </c>
-      <c r="F10" s="110"/>
-      <c r="G10" s="107"/>
-      <c r="H10" s="110"/>
-    </row>
-    <row r="11" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="64"/>
-      <c r="C11" s="111" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" s="109">
-        <v>4</v>
-      </c>
-      <c r="E11" s="109">
-        <v>4</v>
-      </c>
-      <c r="F11" s="110"/>
-      <c r="G11" s="107"/>
-      <c r="H11" s="110"/>
-    </row>
-    <row r="12" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="64"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="109">
-        <v>8</v>
-      </c>
-      <c r="E12" s="109">
-        <v>4</v>
-      </c>
-      <c r="F12" s="110"/>
-      <c r="G12" s="107"/>
-      <c r="H12" s="110"/>
-    </row>
-    <row r="13" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="64"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="109"/>
-      <c r="E13" s="109"/>
-      <c r="F13" s="110"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="110"/>
-    </row>
-    <row r="14" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="64"/>
-      <c r="C14" s="112" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" s="108" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="108" t="s">
-        <v>117</v>
-      </c>
-      <c r="F14" s="108" t="s">
-        <v>120</v>
-      </c>
-      <c r="G14" s="107"/>
-      <c r="H14" s="108" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="64"/>
-      <c r="C15" s="111" t="s">
-        <v>119</v>
-      </c>
-      <c r="D15" s="108">
-        <v>4</v>
-      </c>
-      <c r="E15" s="108">
-        <v>8</v>
-      </c>
-      <c r="F15" s="110"/>
-      <c r="G15" s="107"/>
-      <c r="H15" s="110"/>
-    </row>
-    <row r="16" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="64"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="113">
-        <v>8</v>
-      </c>
-      <c r="E16" s="113">
-        <v>8</v>
-      </c>
-      <c r="F16" s="110"/>
-      <c r="G16" s="107"/>
-      <c r="H16" s="110"/>
-    </row>
+      <c r="F11" s="32"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="32"/>
+    </row>
+    <row r="12" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -6961,18 +6558,12 @@
     <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="B4:B16"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="B4:B11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6983,700 +6574,950 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="B1:H987"/>
+  <dimension ref="B1:L987"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
     <col min="3" max="3" width="54.140625" customWidth="1"/>
-    <col min="4" max="5" width="18.28515625" customWidth="1"/>
-    <col min="6" max="6" width="2.140625" customWidth="1"/>
-    <col min="7" max="8" width="18.28515625" customWidth="1"/>
-    <col min="9" max="22" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" customWidth="1"/>
+    <col min="8" max="8" width="2.140625" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="21.5703125" customWidth="1"/>
+    <col min="13" max="26" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
+    <row r="1" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-    </row>
-    <row r="3" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="101" t="s">
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="80"/>
+    </row>
+    <row r="3" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="56"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="101" t="s">
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="56"/>
-    </row>
-    <row r="4" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="100" t="s">
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="83"/>
+    </row>
+    <row r="4" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="47" t="s">
+      <c r="E4" s="46"/>
+      <c r="F4" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="46"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="48" t="s">
+      <c r="J4" s="52"/>
+      <c r="K4" s="52" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="7" t="s">
+      <c r="L4" s="52"/>
+    </row>
+    <row r="5" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="H5" s="49"/>
+      <c r="I5" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="J5" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="K5" s="34" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="58">
+      <c r="L5" s="27" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="45">
         <v>1</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-    </row>
-    <row r="7" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="59"/>
-      <c r="C7" s="18" t="s">
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="32"/>
+    </row>
+    <row r="7" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="47"/>
+      <c r="C7" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-    </row>
-    <row r="8" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="59"/>
-      <c r="C8" s="18" t="s">
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="32"/>
+    </row>
+    <row r="8" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="47"/>
+      <c r="C8" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-    </row>
-    <row r="9" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="59"/>
-      <c r="C9" s="18" t="s">
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="32"/>
+    </row>
+    <row r="9" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="47"/>
+      <c r="C9" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-    </row>
-    <row r="10" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="59"/>
-      <c r="C10" s="18" t="s">
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="32"/>
+    </row>
+    <row r="10" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="47"/>
+      <c r="C10" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-    </row>
-    <row r="11" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="59"/>
-      <c r="C11" s="18" t="s">
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="32"/>
+    </row>
+    <row r="11" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="47"/>
+      <c r="C11" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-    </row>
-    <row r="12" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="59"/>
-      <c r="C12" s="18" t="s">
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="32"/>
+    </row>
+    <row r="12" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="47"/>
+      <c r="C12" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-    </row>
-    <row r="13" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="59"/>
-      <c r="C13" s="18" t="s">
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="54"/>
+      <c r="L12" s="32"/>
+    </row>
+    <row r="13" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="47"/>
+      <c r="C13" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-    </row>
-    <row r="14" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="59"/>
-      <c r="C14" s="18" t="s">
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="32"/>
+    </row>
+    <row r="14" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="47"/>
+      <c r="C14" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-    </row>
-    <row r="15" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="59"/>
-      <c r="C15" s="18" t="s">
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="32"/>
+    </row>
+    <row r="15" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="47"/>
+      <c r="C15" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-    </row>
-    <row r="16" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="60"/>
-      <c r="C16" s="18" t="s">
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="54"/>
+      <c r="L15" s="32"/>
+    </row>
+    <row r="16" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="47"/>
+      <c r="C16" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-    </row>
-    <row r="17" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="58">
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="54"/>
+      <c r="L16" s="32"/>
+    </row>
+    <row r="17" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="45">
         <v>2</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-    </row>
-    <row r="18" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="59"/>
-      <c r="C18" s="18" t="s">
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="54"/>
+      <c r="L17" s="32"/>
+    </row>
+    <row r="18" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="47"/>
+      <c r="C18" s="53" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-    </row>
-    <row r="19" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="59"/>
-      <c r="C19" s="18" t="s">
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="32"/>
+    </row>
+    <row r="19" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="47"/>
+      <c r="C19" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-    </row>
-    <row r="20" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="59"/>
-      <c r="C20" s="18" t="s">
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="54"/>
+      <c r="L19" s="32"/>
+    </row>
+    <row r="20" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="47"/>
+      <c r="C20" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-    </row>
-    <row r="21" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="59"/>
-      <c r="C21" s="18" t="s">
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="54"/>
+      <c r="L20" s="32"/>
+    </row>
+    <row r="21" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="47"/>
+      <c r="C21" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-    </row>
-    <row r="22" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="59"/>
-      <c r="C22" s="18" t="s">
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="32"/>
+    </row>
+    <row r="22" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="47"/>
+      <c r="C22" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-    </row>
-    <row r="23" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="59"/>
-      <c r="C23" s="18" t="s">
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="32"/>
+    </row>
+    <row r="23" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="47"/>
+      <c r="C23" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-    </row>
-    <row r="24" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="59"/>
-      <c r="C24" s="18" t="s">
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="32"/>
+    </row>
+    <row r="24" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="47"/>
+      <c r="C24" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="59"/>
-      <c r="C25" s="18" t="s">
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="32"/>
+    </row>
+    <row r="25" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="47"/>
+      <c r="C25" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-    </row>
-    <row r="26" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="59"/>
-      <c r="C26" s="18" t="s">
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="54"/>
+      <c r="L25" s="32"/>
+    </row>
+    <row r="26" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="47"/>
+      <c r="C26" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-    </row>
-    <row r="27" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="60"/>
-      <c r="C27" s="18" t="s">
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="32"/>
+    </row>
+    <row r="27" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="47"/>
+      <c r="C27" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-    </row>
-    <row r="28" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="58">
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="49"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="32"/>
+    </row>
+    <row r="28" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="45">
         <v>4</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-    </row>
-    <row r="29" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="59"/>
-      <c r="C29" s="18" t="s">
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="54"/>
+      <c r="L28" s="32"/>
+    </row>
+    <row r="29" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="47"/>
+      <c r="C29" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-    </row>
-    <row r="30" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="59"/>
-      <c r="C30" s="18" t="s">
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="32"/>
+    </row>
+    <row r="30" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="47"/>
+      <c r="C30" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-    </row>
-    <row r="31" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="59"/>
-      <c r="C31" s="18" t="s">
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="49"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="54"/>
+      <c r="L30" s="32"/>
+    </row>
+    <row r="31" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="47"/>
+      <c r="C31" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-    </row>
-    <row r="32" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="59"/>
-      <c r="C32" s="18" t="s">
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="49"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="54"/>
+      <c r="L31" s="32"/>
+    </row>
+    <row r="32" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="47"/>
+      <c r="C32" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-    </row>
-    <row r="33" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="59"/>
-      <c r="C33" s="18" t="s">
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="49"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="54"/>
+      <c r="L32" s="32"/>
+    </row>
+    <row r="33" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="47"/>
+      <c r="C33" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-    </row>
-    <row r="34" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="59"/>
-      <c r="C34" s="18" t="s">
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="54"/>
+      <c r="L33" s="32"/>
+    </row>
+    <row r="34" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="47"/>
+      <c r="C34" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-    </row>
-    <row r="35" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="59"/>
-      <c r="C35" s="18" t="s">
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="49"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="54"/>
+      <c r="L34" s="32"/>
+    </row>
+    <row r="35" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="47"/>
+      <c r="C35" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-    </row>
-    <row r="36" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="59"/>
-      <c r="C36" s="18" t="s">
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="49"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="32"/>
+    </row>
+    <row r="36" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="47"/>
+      <c r="C36" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-    </row>
-    <row r="37" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="59"/>
-      <c r="C37" s="18" t="s">
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="54"/>
+      <c r="L36" s="32"/>
+    </row>
+    <row r="37" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="47"/>
+      <c r="C37" s="53" t="s">
         <v>57</v>
       </c>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-    </row>
-    <row r="38" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="60"/>
-      <c r="C38" s="18" t="s">
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="54"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="32"/>
+    </row>
+    <row r="38" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="47"/>
+      <c r="C38" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-    </row>
-    <row r="39" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="58">
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="32"/>
+    </row>
+    <row r="39" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="45">
         <v>8</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-    </row>
-    <row r="40" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="59"/>
-      <c r="C40" s="18" t="s">
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="54"/>
+      <c r="L39" s="32"/>
+    </row>
+    <row r="40" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" s="47"/>
+      <c r="C40" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-    </row>
-    <row r="41" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="59"/>
-      <c r="C41" s="18" t="s">
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="49"/>
+      <c r="I40" s="54"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="54"/>
+      <c r="L40" s="32"/>
+    </row>
+    <row r="41" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="47"/>
+      <c r="C41" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-    </row>
-    <row r="42" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="59"/>
-      <c r="C42" s="18" t="s">
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="49"/>
+      <c r="I41" s="54"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="54"/>
+      <c r="L41" s="32"/>
+    </row>
+    <row r="42" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="47"/>
+      <c r="C42" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-    </row>
-    <row r="43" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="59"/>
-      <c r="C43" s="18" t="s">
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="49"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="54"/>
+      <c r="L42" s="32"/>
+    </row>
+    <row r="43" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" s="47"/>
+      <c r="C43" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-    </row>
-    <row r="44" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="59"/>
-      <c r="C44" s="18" t="s">
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="54"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="54"/>
+      <c r="L43" s="32"/>
+    </row>
+    <row r="44" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="47"/>
+      <c r="C44" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-    </row>
-    <row r="45" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="59"/>
-      <c r="C45" s="18" t="s">
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="49"/>
+      <c r="I44" s="54"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="54"/>
+      <c r="L44" s="32"/>
+    </row>
+    <row r="45" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="47"/>
+      <c r="C45" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-    </row>
-    <row r="46" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="59"/>
-      <c r="C46" s="18" t="s">
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="49"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="32"/>
+      <c r="K45" s="54"/>
+      <c r="L45" s="32"/>
+    </row>
+    <row r="46" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="47"/>
+      <c r="C46" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-    </row>
-    <row r="47" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="59"/>
-      <c r="C47" s="18" t="s">
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="49"/>
+      <c r="I46" s="54"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="54"/>
+      <c r="L46" s="32"/>
+    </row>
+    <row r="47" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="47"/>
+      <c r="C47" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-    </row>
-    <row r="48" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="59"/>
-      <c r="C48" s="18" t="s">
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="49"/>
+      <c r="I47" s="54"/>
+      <c r="J47" s="32"/>
+      <c r="K47" s="54"/>
+      <c r="L47" s="32"/>
+    </row>
+    <row r="48" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="47"/>
+      <c r="C48" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-    </row>
-    <row r="49" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="60"/>
-      <c r="C49" s="18" t="s">
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="49"/>
+      <c r="I48" s="54"/>
+      <c r="J48" s="32"/>
+      <c r="K48" s="54"/>
+      <c r="L48" s="32"/>
+    </row>
+    <row r="49" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="47"/>
+      <c r="C49" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-    </row>
-    <row r="50" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="58">
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="49"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="54"/>
+      <c r="L49" s="32"/>
+    </row>
+    <row r="50" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="45">
         <v>16</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
-    </row>
-    <row r="51" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="59"/>
-      <c r="C51" s="18" t="s">
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="49"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="32"/>
+      <c r="K50" s="54"/>
+      <c r="L50" s="32"/>
+    </row>
+    <row r="51" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="47"/>
+      <c r="C51" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-    </row>
-    <row r="52" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="59"/>
-      <c r="C52" s="18" t="s">
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="49"/>
+      <c r="I51" s="54"/>
+      <c r="J51" s="32"/>
+      <c r="K51" s="54"/>
+      <c r="L51" s="32"/>
+    </row>
+    <row r="52" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="47"/>
+      <c r="C52" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-    </row>
-    <row r="53" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="59"/>
-      <c r="C53" s="18" t="s">
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="49"/>
+      <c r="I52" s="54"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="54"/>
+      <c r="L52" s="32"/>
+    </row>
+    <row r="53" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="47"/>
+      <c r="C53" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-    </row>
-    <row r="54" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="59"/>
-      <c r="C54" s="18" t="s">
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="49"/>
+      <c r="I53" s="54"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="54"/>
+      <c r="L53" s="32"/>
+    </row>
+    <row r="54" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="47"/>
+      <c r="C54" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19"/>
-    </row>
-    <row r="55" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="59"/>
-      <c r="C55" s="18" t="s">
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="49"/>
+      <c r="I54" s="54"/>
+      <c r="J54" s="32"/>
+      <c r="K54" s="54"/>
+      <c r="L54" s="32"/>
+    </row>
+    <row r="55" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="47"/>
+      <c r="C55" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="19"/>
-    </row>
-    <row r="56" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="59"/>
-      <c r="C56" s="18" t="s">
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="49"/>
+      <c r="I55" s="54"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="54"/>
+      <c r="L55" s="32"/>
+    </row>
+    <row r="56" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="47"/>
+      <c r="C56" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="19"/>
-    </row>
-    <row r="57" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="59"/>
-      <c r="C57" s="18" t="s">
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="49"/>
+      <c r="I56" s="54"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="54"/>
+      <c r="L56" s="32"/>
+    </row>
+    <row r="57" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="47"/>
+      <c r="C57" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-    </row>
-    <row r="58" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="59"/>
-      <c r="C58" s="18" t="s">
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="49"/>
+      <c r="I57" s="54"/>
+      <c r="J57" s="32"/>
+      <c r="K57" s="54"/>
+      <c r="L57" s="32"/>
+    </row>
+    <row r="58" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="47"/>
+      <c r="C58" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="D58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="19"/>
-    </row>
-    <row r="59" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="59"/>
-      <c r="C59" s="18" t="s">
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="49"/>
+      <c r="I58" s="54"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="54"/>
+      <c r="L58" s="32"/>
+    </row>
+    <row r="59" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="47"/>
+      <c r="C59" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19"/>
-    </row>
-    <row r="60" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="60"/>
-      <c r="C60" s="18" t="s">
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="49"/>
+      <c r="I59" s="54"/>
+      <c r="J59" s="32"/>
+      <c r="K59" s="54"/>
+      <c r="L59" s="32"/>
+    </row>
+    <row r="60" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="47"/>
+      <c r="C60" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="D60" s="10"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="19"/>
-    </row>
-    <row r="61" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="49"/>
+      <c r="I60" s="54"/>
+      <c r="J60" s="32"/>
+      <c r="K60" s="54"/>
+      <c r="L60" s="32"/>
+    </row>
+    <row r="61" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -8601,17 +8442,21 @@
     <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B2:H2"/>
+  <mergeCells count="14">
+    <mergeCell ref="I3:L3"/>
     <mergeCell ref="B17:B27"/>
     <mergeCell ref="B28:B38"/>
     <mergeCell ref="B39:B49"/>
     <mergeCell ref="B50:B60"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D3:E3"/>
     <mergeCell ref="B6:B16"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="D3:G3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
